--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2275,28 +2275,28 @@
     <t>NK1-7, NK1-3</t>
   </si>
   <si>
-    <t>Patient.contact.relationship:RolePerson</t>
-  </si>
-  <si>
-    <t>RolePerson</t>
+    <t>Patient.contact.relationship:Role</t>
+  </si>
+  <si>
+    <t>Role</t>
   </si>
   <si>
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-related-person-role</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RelatedPerson</t>
-  </si>
-  <si>
-    <t>RelatedPerson</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:RelationType</t>
+  </si>
+  <si>
+    <t>RelationType</t>
   </si>
   <si>
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-related-person</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
@@ -2935,7 +2935,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.12109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="75.2109375" customWidth="true" bestFit="true"/>
@@ -19657,10 +19657,10 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>81</v>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6194" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6866" uniqueCount="851">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}fr-core-1:If identityReliability status = 'VALI', then Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or both SHALL be present {(extension.where(url= 'https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension.where(url = 'identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists())}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension.where(url= 'https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension.where(url = 'identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists())}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>
@@ -1596,6 +1596,100 @@
   </si>
   <si>
     <t>Patient.identifier:INS-NIR.assigner</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-TEST</t>
+  </si>
+  <si>
+    <t>INS-NIR-TEST</t>
+  </si>
+  <si>
+    <t>Identifiant INS-NIR du patient fictif de test</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-TEST.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-TEST.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-TEST.use</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-TEST.type</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
+    &lt;code value="INS-NIR-TEST"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-TEST.system</t>
+  </si>
+  <si>
+    <t>Autorité d’affectation des INS-NIR de test</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.250.1.213.1.4.10</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-TEST.value</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-TEST.period</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-TEST.assigner</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-DEMO</t>
+  </si>
+  <si>
+    <t>INS-NIR-DEMO</t>
+  </si>
+  <si>
+    <t>Identifiant INS-NIR du patient fictif de démonstration</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-DEMO.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-DEMO.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-DEMO.use</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-DEMO.type</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
+    &lt;code value="INS-NIR-DEMO"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-DEMO.system</t>
+  </si>
+  <si>
+    <t>Autorité d’affectation des INS-NIR de démonstration</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.250.1.213.1.4.11</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-DEMO.value</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-DEMO.period</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-NIR-DEMO.assigner</t>
   </si>
   <si>
     <t>Patient.identifier:INS-NIA</t>
@@ -2913,7 +3007,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO165"/>
+  <dimension ref="A1:AO183"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.79296875" customWidth="true" bestFit="true"/>
@@ -14629,7 +14723,7 @@
         <v>82</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>507</v>
+        <v>382</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>82</v>
@@ -14700,7 +14794,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>388</v>
@@ -14748,7 +14842,7 @@
         <v>82</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>82</v>
@@ -14819,7 +14913,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>400</v>
@@ -14848,7 +14942,7 @@
         <v>134</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="M102" t="s" s="2">
         <v>402</v>
@@ -14867,7 +14961,7 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>406</v>
@@ -14938,7 +15032,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>411</v>
@@ -15055,7 +15149,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>420</v>
@@ -15172,7 +15266,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>427</v>
@@ -15289,12 +15383,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C106" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="B106" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
         <v>82</v>
       </c>
@@ -15303,38 +15399,34 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="L106" t="s" s="2">
-        <v>518</v>
-      </c>
       <c r="M106" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>521</v>
+        <v>362</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q106" t="s" s="2">
-        <v>522</v>
-      </c>
+      <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
         <v>82</v>
       </c>
@@ -15378,13 +15470,13 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>516</v>
+        <v>358</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>102</v>
@@ -15393,16 +15485,16 @@
         <v>103</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>523</v>
+        <v>365</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>110</v>
+        <v>366</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>524</v>
+        <v>367</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15410,10 +15502,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>525</v>
+        <v>373</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15421,10 +15513,10 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>82</v>
@@ -15433,23 +15525,19 @@
         <v>82</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>526</v>
+        <v>106</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>527</v>
+        <v>107</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15485,41 +15573,43 @@
         <v>82</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="AC107" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>525</v>
+        <v>109</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>532</v>
+        <v>110</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>533</v>
+        <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15527,16 +15617,14 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>536</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15552,23 +15640,21 @@
         <v>82</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>537</v>
+        <v>113</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>538</v>
+        <v>114</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>539</v>
+        <v>115</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15604,19 +15690,19 @@
         <v>82</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>525</v>
+        <v>120</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15628,19 +15714,19 @@
         <v>102</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>532</v>
+        <v>104</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>533</v>
+        <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15648,10 +15734,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>541</v>
+        <v>377</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15668,22 +15754,26 @@
         <v>82</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>107</v>
+        <v>378</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15692,7 +15782,7 @@
         <v>82</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>82</v>
@@ -15707,13 +15797,13 @@
         <v>82</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15731,7 +15821,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>109</v>
+        <v>385</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15740,13 +15830,13 @@
         <v>90</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>110</v>
+        <v>386</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>82</v>
@@ -15755,7 +15845,7 @@
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15763,21 +15853,21 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>543</v>
+        <v>388</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15786,21 +15876,23 @@
         <v>82</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>113</v>
+        <v>389</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>114</v>
+        <v>390</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>115</v>
+        <v>391</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O110" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15809,7 +15901,7 @@
         <v>82</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>82</v>
@@ -15824,46 +15916,46 @@
         <v>82</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>120</v>
+        <v>397</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>104</v>
+        <v>386</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>82</v>
@@ -15872,7 +15964,7 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15880,10 +15972,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>545</v>
+        <v>400</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15891,7 +15983,7 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>90</v>
@@ -15900,25 +15992,25 @@
         <v>82</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J111" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>546</v>
+        <v>524</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>547</v>
+        <v>402</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>548</v>
+        <v>403</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>549</v>
+        <v>404</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15928,10 +16020,10 @@
         <v>82</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>469</v>
+        <v>525</v>
       </c>
       <c r="T111" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="U111" t="s" s="2">
         <v>82</v>
@@ -15943,13 +16035,13 @@
         <v>82</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>550</v>
+        <v>82</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>551</v>
+        <v>82</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -15967,7 +16059,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>552</v>
+        <v>407</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15982,7 +16074,7 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>266</v>
+        <v>408</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
@@ -15991,7 +16083,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>553</v>
+        <v>409</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15999,10 +16091,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>554</v>
+        <v>526</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>555</v>
+        <v>411</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16010,7 +16102,7 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>90</v>
@@ -16028,17 +16120,15 @@
         <v>106</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>556</v>
+        <v>412</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>557</v>
+        <v>413</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>82</v>
       </c>
@@ -16050,7 +16140,7 @@
         <v>82</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>82</v>
@@ -16086,7 +16176,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>559</v>
+        <v>416</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16101,7 +16191,7 @@
         <v>103</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>286</v>
+        <v>417</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>82</v>
@@ -16110,7 +16200,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>560</v>
+        <v>418</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16118,14 +16208,14 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>561</v>
+        <v>527</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>562</v>
+        <v>420</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -16144,16 +16234,16 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>106</v>
+        <v>343</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>564</v>
+        <v>421</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>565</v>
+        <v>422</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>566</v>
+        <v>346</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16203,7 +16293,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>567</v>
+        <v>423</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16215,10 +16305,10 @@
         <v>102</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>103</v>
+        <v>350</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>568</v>
+        <v>424</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>82</v>
@@ -16227,7 +16317,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>569</v>
+        <v>425</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16235,21 +16325,21 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>570</v>
+        <v>528</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>571</v>
+        <v>427</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>572</v>
+        <v>82</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>82</v>
@@ -16261,16 +16351,16 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>106</v>
+        <v>428</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>573</v>
+        <v>429</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>574</v>
+        <v>430</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>575</v>
+        <v>431</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16320,22 +16410,22 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>576</v>
+        <v>432</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>103</v>
+        <v>433</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>577</v>
+        <v>434</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>82</v>
@@ -16344,7 +16434,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>578</v>
+        <v>435</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16352,12 +16442,14 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>579</v>
+        <v>529</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="C115" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="D115" t="s" s="2">
         <v>82</v>
       </c>
@@ -16378,18 +16470,18 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>106</v>
+        <v>359</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>581</v>
+        <v>531</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O115" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
       </c>
@@ -16437,7 +16529,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>583</v>
+        <v>358</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16452,16 +16544,16 @@
         <v>103</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>584</v>
+        <v>365</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>585</v>
+        <v>368</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16469,10 +16561,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>586</v>
+        <v>532</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>587</v>
+        <v>373</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16483,7 +16575,7 @@
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>82</v>
@@ -16492,20 +16584,18 @@
         <v>82</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>588</v>
+        <v>107</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>82</v>
@@ -16554,22 +16644,22 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>590</v>
+        <v>109</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>591</v>
+        <v>110</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>82</v>
@@ -16578,7 +16668,7 @@
         <v>82</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
@@ -16586,21 +16676,21 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>593</v>
+        <v>533</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>594</v>
+        <v>375</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>82</v>
@@ -16609,23 +16699,21 @@
         <v>82</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>343</v>
+        <v>113</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>595</v>
+        <v>114</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>596</v>
+        <v>115</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>82</v>
       </c>
@@ -16661,34 +16749,34 @@
         <v>82</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>598</v>
+        <v>120</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>350</v>
+        <v>121</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>351</v>
+        <v>104</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>82</v>
@@ -16697,7 +16785,7 @@
         <v>82</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>599</v>
+        <v>82</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
@@ -16705,20 +16793,18 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>600</v>
+        <v>534</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>90</v>
@@ -16727,25 +16813,25 @@
         <v>82</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J118" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>537</v>
+        <v>174</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>602</v>
+        <v>378</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>603</v>
+        <v>379</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>529</v>
+        <v>380</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>530</v>
+        <v>381</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
@@ -16755,7 +16841,7 @@
         <v>82</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>82</v>
@@ -16770,13 +16856,13 @@
         <v>82</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>82</v>
@@ -16794,13 +16880,13 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>525</v>
+        <v>385</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>102</v>
@@ -16809,16 +16895,16 @@
         <v>103</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>532</v>
+        <v>386</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>533</v>
+        <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>534</v>
+        <v>104</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
@@ -16826,10 +16912,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>604</v>
+        <v>536</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>541</v>
+        <v>388</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16837,7 +16923,7 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>90</v>
@@ -16849,19 +16935,23 @@
         <v>82</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>106</v>
+        <v>389</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>107</v>
+        <v>390</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
       </c>
@@ -16870,7 +16960,7 @@
         <v>82</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>82</v>
+        <v>537</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>82</v>
@@ -16885,13 +16975,13 @@
         <v>82</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>82</v>
@@ -16909,7 +16999,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>109</v>
+        <v>397</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16918,13 +17008,13 @@
         <v>90</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>110</v>
+        <v>386</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>82</v>
@@ -16933,7 +17023,7 @@
         <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
@@ -16941,10 +17031,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>605</v>
+        <v>538</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>543</v>
+        <v>400</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16952,10 +17042,10 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>82</v>
@@ -16964,19 +17054,23 @@
         <v>82</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>199</v>
+        <v>539</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
       </c>
@@ -16985,10 +17079,10 @@
         <v>82</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="T120" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="U120" t="s" s="2">
         <v>82</v>
@@ -17012,34 +17106,34 @@
         <v>82</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>120</v>
+        <v>407</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>82</v>
@@ -17048,7 +17142,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -17056,14 +17150,12 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>606</v>
+        <v>541</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>607</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>82</v>
       </c>
@@ -17081,18 +17173,20 @@
         <v>82</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>608</v>
+        <v>106</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>609</v>
+        <v>412</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N121" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -17105,7 +17199,7 @@
         <v>82</v>
       </c>
       <c r="T121" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="U121" t="s" s="2">
         <v>82</v>
@@ -17141,22 +17235,22 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>120</v>
+        <v>416</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>82</v>
@@ -17165,7 +17259,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -17173,10 +17267,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>611</v>
+        <v>542</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>545</v>
+        <v>420</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17184,7 +17278,7 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>90</v>
@@ -17193,26 +17287,24 @@
         <v>82</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J122" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>174</v>
+        <v>343</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>546</v>
+        <v>421</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>547</v>
+        <v>422</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>82</v>
       </c>
@@ -17221,7 +17313,7 @@
         <v>82</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>82</v>
@@ -17236,13 +17328,13 @@
         <v>82</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>550</v>
+        <v>82</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>551</v>
+        <v>82</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -17260,7 +17352,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>552</v>
+        <v>423</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17272,10 +17364,10 @@
         <v>102</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>103</v>
+        <v>350</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>266</v>
+        <v>424</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>82</v>
@@ -17284,7 +17376,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>553</v>
+        <v>425</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -17292,10 +17384,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>612</v>
+        <v>543</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>555</v>
+        <v>427</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17318,20 +17410,18 @@
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>106</v>
+        <v>428</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>556</v>
+        <v>429</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>557</v>
+        <v>430</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>82</v>
       </c>
@@ -17379,7 +17469,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>559</v>
+        <v>432</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17391,10 +17481,10 @@
         <v>102</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>103</v>
+        <v>433</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>286</v>
+        <v>434</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>82</v>
@@ -17403,7 +17493,7 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>560</v>
+        <v>435</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -17411,18 +17501,18 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>613</v>
+        <v>544</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>90</v>
@@ -17431,28 +17521,32 @@
         <v>82</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J124" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>106</v>
+        <v>545</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O124" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q124" s="2"/>
+      <c r="Q124" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="R124" t="s" s="2">
         <v>82</v>
       </c>
@@ -17496,7 +17590,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>567</v>
+        <v>544</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17511,16 +17605,16 @@
         <v>103</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>82</v>
+        <v>552</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>569</v>
+        <v>82</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17528,21 +17622,21 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>614</v>
+        <v>553</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>571</v>
+        <v>553</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>572</v>
+        <v>82</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>90</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>82</v>
@@ -17554,18 +17648,20 @@
         <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>106</v>
+        <v>554</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>615</v>
+        <v>555</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O125" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>82</v>
       </c>
@@ -17601,19 +17697,17 @@
         <v>82</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="AC125" s="2"/>
       <c r="AD125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>576</v>
+        <v>553</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17628,16 +17722,16 @@
         <v>103</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>577</v>
+        <v>560</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17645,12 +17739,14 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>616</v>
+        <v>563</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="C126" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>564</v>
+      </c>
       <c r="D126" t="s" s="2">
         <v>82</v>
       </c>
@@ -17671,18 +17767,20 @@
         <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>106</v>
+        <v>565</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>581</v>
+        <v>566</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>582</v>
+        <v>567</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
       </c>
@@ -17730,7 +17828,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>583</v>
+        <v>553</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17745,16 +17843,16 @@
         <v>103</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>584</v>
+        <v>560</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>585</v>
+        <v>562</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17762,10 +17860,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>617</v>
+        <v>568</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17776,7 +17874,7 @@
         <v>80</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>82</v>
@@ -17785,20 +17883,18 @@
         <v>82</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K127" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>588</v>
+        <v>107</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17847,22 +17943,22 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>590</v>
+        <v>109</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>591</v>
+        <v>110</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>82</v>
@@ -17871,7 +17967,7 @@
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17879,21 +17975,21 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>618</v>
+        <v>570</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>594</v>
+        <v>571</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>82</v>
@@ -17902,23 +17998,21 @@
         <v>82</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>343</v>
+        <v>113</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>595</v>
+        <v>114</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>596</v>
+        <v>115</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>82</v>
       </c>
@@ -17954,34 +18048,34 @@
         <v>82</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>598</v>
+        <v>120</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>350</v>
+        <v>121</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>351</v>
+        <v>104</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>82</v>
@@ -17990,7 +18084,7 @@
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>599</v>
+        <v>82</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -17998,10 +18092,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>619</v>
+        <v>572</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>619</v>
+        <v>573</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18009,34 +18103,34 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I129" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>620</v>
+        <v>174</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>621</v>
+        <v>574</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>622</v>
+        <v>575</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>623</v>
+        <v>576</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>624</v>
+        <v>577</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
@@ -18046,7 +18140,7 @@
         <v>82</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>82</v>
+        <v>469</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>82</v>
@@ -18061,13 +18155,13 @@
         <v>82</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>82</v>
@@ -18085,22 +18179,22 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>619</v>
+        <v>580</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>625</v>
+        <v>103</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>626</v>
+        <v>266</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>82</v>
@@ -18109,7 +18203,7 @@
         <v>82</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>627</v>
+        <v>581</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>82</v>
@@ -18117,10 +18211,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>628</v>
+        <v>582</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>628</v>
+        <v>583</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18128,7 +18222,7 @@
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>90</v>
@@ -18143,19 +18237,19 @@
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>629</v>
+        <v>584</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>630</v>
+        <v>585</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>631</v>
+        <v>586</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>632</v>
+        <v>283</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -18180,11 +18274,13 @@
         <v>82</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="Y130" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z130" t="s" s="2">
-        <v>633</v>
+        <v>82</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>82</v>
@@ -18202,7 +18298,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>628</v>
+        <v>587</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18217,16 +18313,16 @@
         <v>103</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>634</v>
+        <v>286</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>635</v>
+        <v>82</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>636</v>
+        <v>588</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -18234,18 +18330,18 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>637</v>
+        <v>589</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>637</v>
+        <v>590</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>82</v>
+        <v>591</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>90</v>
@@ -18260,20 +18356,18 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>638</v>
+        <v>106</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>639</v>
+        <v>592</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>640</v>
+        <v>593</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>642</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>82</v>
       </c>
@@ -18321,7 +18415,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>637</v>
+        <v>595</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18336,63 +18430,61 @@
         <v>103</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>643</v>
+        <v>596</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>644</v>
+        <v>82</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>645</v>
+        <v>597</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>646</v>
+        <v>82</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>647</v>
+        <v>598</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>647</v>
+        <v>599</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>82</v>
+        <v>600</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J132" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>648</v>
+        <v>106</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>649</v>
+        <v>601</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>650</v>
+        <v>602</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>652</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>82</v>
       </c>
@@ -18440,13 +18532,13 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>647</v>
+        <v>604</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>102</v>
@@ -18455,16 +18547,16 @@
         <v>103</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>653</v>
+        <v>605</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>654</v>
+        <v>606</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -18472,10 +18564,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>655</v>
+        <v>607</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>655</v>
+        <v>608</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18495,23 +18587,21 @@
         <v>82</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>239</v>
+        <v>106</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>240</v>
+        <v>609</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>241</v>
+        <v>610</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>657</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>82</v>
       </c>
@@ -18559,7 +18649,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>655</v>
+        <v>611</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18574,7 +18664,7 @@
         <v>103</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>244</v>
+        <v>612</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>82</v>
@@ -18583,7 +18673,7 @@
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>245</v>
+        <v>613</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18591,10 +18681,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>658</v>
+        <v>614</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>658</v>
+        <v>615</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18605,7 +18695,7 @@
         <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>82</v>
@@ -18614,23 +18704,21 @@
         <v>82</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>389</v>
+        <v>106</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>659</v>
+        <v>616</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>660</v>
+        <v>617</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>662</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>82</v>
       </c>
@@ -18654,11 +18742,13 @@
         <v>82</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Y134" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z134" t="s" s="2">
-        <v>663</v>
+        <v>82</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>82</v>
@@ -18676,13 +18766,13 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>658</v>
+        <v>618</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>102</v>
@@ -18691,16 +18781,16 @@
         <v>103</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>664</v>
+        <v>619</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>665</v>
+        <v>82</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>666</v>
+        <v>620</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18708,10 +18798,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>667</v>
+        <v>621</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>667</v>
+        <v>622</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18731,22 +18821,22 @@
         <v>82</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>668</v>
+        <v>343</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>669</v>
+        <v>623</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>670</v>
+        <v>624</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>671</v>
+        <v>346</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>672</v>
+        <v>625</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -18795,7 +18885,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>667</v>
+        <v>626</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18807,19 +18897,19 @@
         <v>102</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>103</v>
+        <v>350</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>673</v>
+        <v>351</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>674</v>
+        <v>627</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18827,21 +18917,23 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>675</v>
+        <v>628</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="C136" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="C136" t="s" s="2">
+        <v>629</v>
+      </c>
       <c r="D136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>82</v>
@@ -18850,22 +18942,22 @@
         <v>82</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>676</v>
+        <v>565</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>677</v>
+        <v>630</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>678</v>
+        <v>631</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>679</v>
+        <v>557</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>680</v>
+        <v>558</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -18914,7 +19006,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>675</v>
+        <v>553</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18926,19 +19018,19 @@
         <v>102</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>681</v>
+        <v>103</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>682</v>
+        <v>560</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>110</v>
+        <v>561</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>683</v>
+        <v>562</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -18946,10 +19038,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>684</v>
+        <v>632</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>684</v>
+        <v>569</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18960,7 +19052,7 @@
         <v>80</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>82</v>
@@ -18972,20 +19064,16 @@
         <v>82</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>685</v>
+        <v>106</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>686</v>
+        <v>107</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>689</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
       </c>
@@ -19033,25 +19121,25 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>684</v>
+        <v>109</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>690</v>
+        <v>82</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>691</v>
+        <v>110</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>82</v>
@@ -19065,10 +19153,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>692</v>
+        <v>633</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>692</v>
+        <v>571</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19076,10 +19164,10 @@
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>82</v>
@@ -19091,13 +19179,13 @@
         <v>82</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>107</v>
+        <v>199</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19136,34 +19224,34 @@
         <v>82</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>82</v>
@@ -19180,21 +19268,23 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>693</v>
+        <v>634</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="C139" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>635</v>
+      </c>
       <c r="D139" t="s" s="2">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>82</v>
@@ -19206,17 +19296,15 @@
         <v>82</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>113</v>
+        <v>636</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>114</v>
+        <v>637</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>116</v>
-      </c>
+        <v>638</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>82</v>
@@ -19253,16 +19341,16 @@
         <v>82</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
         <v>120</v>
@@ -19280,7 +19368,7 @@
         <v>121</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>82</v>
@@ -19297,20 +19385,18 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>694</v>
+        <v>639</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="C140" t="s" s="2">
-        <v>695</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>90</v>
@@ -19319,22 +19405,26 @@
         <v>82</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>696</v>
+        <v>174</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>697</v>
+        <v>574</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
       </c>
@@ -19343,7 +19433,7 @@
         <v>82</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>82</v>
@@ -19358,13 +19448,13 @@
         <v>82</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>82</v>
@@ -19382,22 +19472,22 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>82</v>
@@ -19406,7 +19496,7 @@
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>82</v>
+        <v>581</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>82</v>
@@ -19414,14 +19504,12 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>699</v>
+        <v>640</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="C141" t="s" s="2">
-        <v>700</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
         <v>82</v>
       </c>
@@ -19439,19 +19527,23 @@
         <v>82</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>701</v>
+        <v>106</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>702</v>
+        <v>584</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
       </c>
@@ -19499,22 +19591,22 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>120</v>
+        <v>587</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>82</v>
@@ -19523,7 +19615,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>82</v>
+        <v>588</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19531,46 +19623,44 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>704</v>
+        <v>641</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>704</v>
+        <v>590</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>705</v>
+        <v>591</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I142" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J142" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>706</v>
+        <v>592</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>707</v>
+        <v>593</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>82</v>
       </c>
@@ -19618,22 +19708,22 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>708</v>
+        <v>595</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>104</v>
+        <v>596</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>82</v>
@@ -19642,7 +19732,7 @@
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19650,21 +19740,21 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>709</v>
+        <v>642</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>709</v>
+        <v>599</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>82</v>
+        <v>600</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>82</v>
@@ -19673,23 +19763,21 @@
         <v>82</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>389</v>
+        <v>106</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>710</v>
+        <v>643</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>711</v>
+        <v>602</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>712</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>82</v>
       </c>
@@ -19713,29 +19801,31 @@
         <v>82</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>713</v>
+        <v>82</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>714</v>
+        <v>82</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="AC143" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE143" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>709</v>
+        <v>604</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19750,16 +19840,16 @@
         <v>103</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>716</v>
+        <v>605</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>717</v>
+        <v>606</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>82</v>
@@ -19767,14 +19857,12 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>718</v>
+        <v>644</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="C144" t="s" s="2">
-        <v>719</v>
-      </c>
+        <v>608</v>
+      </c>
+      <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
         <v>82</v>
       </c>
@@ -19783,7 +19871,7 @@
         <v>80</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>82</v>
@@ -19792,23 +19880,21 @@
         <v>82</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>389</v>
+        <v>106</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>720</v>
+        <v>609</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>711</v>
+        <v>610</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>712</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>82</v>
       </c>
@@ -19832,11 +19918,13 @@
         <v>82</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Y144" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z144" t="s" s="2">
-        <v>721</v>
+        <v>82</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>82</v>
@@ -19854,7 +19942,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>709</v>
+        <v>611</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19869,16 +19957,16 @@
         <v>103</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>716</v>
+        <v>612</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>717</v>
+        <v>613</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>82</v>
@@ -19886,14 +19974,12 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>722</v>
+        <v>645</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="C145" t="s" s="2">
-        <v>723</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
         <v>82</v>
       </c>
@@ -19902,7 +19988,7 @@
         <v>80</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>82</v>
@@ -19911,23 +19997,21 @@
         <v>82</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>389</v>
+        <v>106</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>724</v>
+        <v>616</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>711</v>
+        <v>617</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>712</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>82</v>
       </c>
@@ -19951,11 +20035,13 @@
         <v>82</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Y145" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z145" t="s" s="2">
-        <v>725</v>
+        <v>82</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>82</v>
@@ -19973,7 +20059,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>709</v>
+        <v>618</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -19988,16 +20074,16 @@
         <v>103</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>716</v>
+        <v>619</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>717</v>
+        <v>620</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>82</v>
@@ -20005,10 +20091,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>726</v>
+        <v>646</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>726</v>
+        <v>622</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20028,22 +20114,22 @@
         <v>82</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>526</v>
+        <v>343</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>727</v>
+        <v>623</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>728</v>
+        <v>624</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>729</v>
+        <v>346</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>730</v>
+        <v>625</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -20092,7 +20178,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>726</v>
+        <v>626</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20104,10 +20190,10 @@
         <v>102</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>103</v>
+        <v>350</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>731</v>
+        <v>351</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>82</v>
@@ -20116,7 +20202,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>732</v>
+        <v>627</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -20124,10 +20210,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>733</v>
+        <v>647</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>733</v>
+        <v>647</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20150,19 +20236,19 @@
         <v>82</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>620</v>
+        <v>648</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>621</v>
+        <v>649</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>622</v>
+        <v>650</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>734</v>
+        <v>651</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>624</v>
+        <v>652</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>82</v>
@@ -20211,7 +20297,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>733</v>
+        <v>647</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20223,10 +20309,10 @@
         <v>102</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>625</v>
+        <v>653</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>626</v>
+        <v>654</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>82</v>
@@ -20235,7 +20321,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>627</v>
+        <v>655</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
@@ -20243,10 +20329,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>735</v>
+        <v>656</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>735</v>
+        <v>656</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20254,7 +20340,7 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>90</v>
@@ -20266,22 +20352,22 @@
         <v>82</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>736</v>
+        <v>174</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>737</v>
+        <v>657</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>738</v>
+        <v>658</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>739</v>
+        <v>660</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -20306,13 +20392,11 @@
         <v>82</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="Y148" s="2"/>
       <c r="Z148" t="s" s="2">
-        <v>82</v>
+        <v>661</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>82</v>
@@ -20330,7 +20414,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>735</v>
+        <v>656</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20345,16 +20429,16 @@
         <v>103</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>740</v>
+        <v>662</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>110</v>
+        <v>663</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>741</v>
+        <v>664</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -20362,10 +20446,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>742</v>
+        <v>665</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>742</v>
+        <v>665</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20373,7 +20457,7 @@
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G149" t="s" s="2">
         <v>90</v>
@@ -20385,22 +20469,22 @@
         <v>82</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>174</v>
+        <v>666</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>743</v>
+        <v>667</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>744</v>
+        <v>668</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>292</v>
+        <v>669</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>745</v>
+        <v>670</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -20425,13 +20509,13 @@
         <v>82</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>746</v>
+        <v>82</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>747</v>
+        <v>82</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>82</v>
@@ -20449,7 +20533,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>742</v>
+        <v>665</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20464,27 +20548,27 @@
         <v>103</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>634</v>
+        <v>671</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>110</v>
+        <v>672</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>748</v>
+        <v>673</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>82</v>
+        <v>674</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>749</v>
+        <v>675</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>749</v>
+        <v>675</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20501,25 +20585,25 @@
         <v>82</v>
       </c>
       <c r="I150" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>428</v>
+        <v>676</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>750</v>
+        <v>677</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>751</v>
+        <v>678</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>752</v>
+        <v>679</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>753</v>
+        <v>680</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>82</v>
@@ -20568,7 +20652,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>749</v>
+        <v>675</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20577,13 +20661,13 @@
         <v>90</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>754</v>
+        <v>102</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>433</v>
+        <v>103</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>755</v>
+        <v>681</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>110</v>
@@ -20592,7 +20676,7 @@
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>756</v>
+        <v>682</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>82</v>
@@ -20600,10 +20684,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>757</v>
+        <v>683</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>757</v>
+        <v>683</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20614,7 +20698,7 @@
         <v>80</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>82</v>
@@ -20626,18 +20710,20 @@
         <v>82</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>343</v>
+        <v>239</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>758</v>
+        <v>240</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>759</v>
+        <v>241</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O151" s="2"/>
+        <v>684</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>685</v>
+      </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
       </c>
@@ -20685,31 +20771,31 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>757</v>
+        <v>683</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>350</v>
+        <v>103</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>760</v>
+        <v>244</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>761</v>
+        <v>245</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -20717,10 +20803,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>762</v>
+        <v>686</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>762</v>
+        <v>686</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20731,7 +20817,7 @@
         <v>80</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>82</v>
@@ -20743,19 +20829,19 @@
         <v>82</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>685</v>
+        <v>389</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>763</v>
+        <v>687</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>764</v>
+        <v>688</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>765</v>
+        <v>689</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>766</v>
+        <v>690</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -20780,13 +20866,11 @@
         <v>82</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
-        <v>82</v>
+        <v>691</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>82</v>
@@ -20804,13 +20888,13 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>762</v>
+        <v>686</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>102</v>
@@ -20819,16 +20903,16 @@
         <v>103</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>767</v>
+        <v>692</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>768</v>
+        <v>693</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>82</v>
+        <v>694</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -20836,10 +20920,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>769</v>
+        <v>695</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>769</v>
+        <v>695</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20862,16 +20946,20 @@
         <v>82</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>106</v>
+        <v>696</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>107</v>
+        <v>697</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N153" s="2"/>
-      <c r="O153" s="2"/>
+        <v>698</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>700</v>
+      </c>
       <c r="P153" t="s" s="2">
         <v>82</v>
       </c>
@@ -20919,7 +21007,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>109</v>
+        <v>695</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20928,22 +21016,22 @@
         <v>90</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK153" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AL153" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="AL153" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>82</v>
+        <v>702</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -20951,14 +21039,14 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>770</v>
+        <v>703</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>770</v>
+        <v>703</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -20977,18 +21065,20 @@
         <v>82</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>113</v>
+        <v>704</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>114</v>
+        <v>705</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>115</v>
+        <v>706</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O154" s="2"/>
+        <v>707</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>708</v>
+      </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
       </c>
@@ -21024,19 +21114,19 @@
         <v>82</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>120</v>
+        <v>703</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21048,19 +21138,19 @@
         <v>102</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>121</v>
+        <v>709</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>104</v>
+        <v>710</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>82</v>
+        <v>711</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -21068,14 +21158,14 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>771</v>
+        <v>712</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>771</v>
+        <v>712</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>705</v>
+        <v>82</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21088,25 +21178,25 @@
         <v>82</v>
       </c>
       <c r="I155" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>113</v>
+        <v>713</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>116</v>
+        <v>716</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>356</v>
+        <v>717</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -21155,7 +21245,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21167,13 +21257,13 @@
         <v>102</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>121</v>
+        <v>718</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>104</v>
+        <v>719</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>82</v>
@@ -21187,10 +21277,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>772</v>
+        <v>720</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>772</v>
+        <v>720</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21198,7 +21288,7 @@
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G156" t="s" s="2">
         <v>90</v>
@@ -21213,20 +21303,16 @@
         <v>82</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>389</v>
+        <v>106</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>773</v>
+        <v>107</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>776</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N156" s="2"/>
+      <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>82</v>
       </c>
@@ -21250,13 +21336,13 @@
         <v>82</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>82</v>
@@ -21274,31 +21360,31 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>772</v>
+        <v>109</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>777</v>
+        <v>110</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>778</v>
+        <v>82</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>779</v>
+        <v>82</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>82</v>
@@ -21306,21 +21392,21 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>780</v>
+        <v>721</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>780</v>
+        <v>721</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>82</v>
@@ -21332,20 +21418,18 @@
         <v>82</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>517</v>
+        <v>113</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>781</v>
+        <v>114</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>782</v>
+        <v>115</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>784</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>82</v>
       </c>
@@ -21381,43 +21465,43 @@
         <v>82</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>780</v>
+        <v>120</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>785</v>
+        <v>104</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>786</v>
+        <v>82</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>787</v>
+        <v>82</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>82</v>
@@ -21425,21 +21509,23 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>788</v>
+        <v>722</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="C158" s="2"/>
+        <v>721</v>
+      </c>
+      <c r="C158" t="s" s="2">
+        <v>723</v>
+      </c>
       <c r="D158" t="s" s="2">
-        <v>789</v>
+        <v>82</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>82</v>
@@ -21451,17 +21537,15 @@
         <v>82</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>790</v>
+        <v>724</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>791</v>
+        <v>725</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>793</v>
-      </c>
+        <v>726</v>
+      </c>
+      <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>82</v>
@@ -21510,7 +21594,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>788</v>
+        <v>120</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21522,19 +21606,19 @@
         <v>102</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>433</v>
+        <v>121</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>794</v>
+        <v>82</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>795</v>
+        <v>82</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>82</v>
@@ -21542,12 +21626,14 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>796</v>
+        <v>727</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>796</v>
-      </c>
-      <c r="C159" s="2"/>
+        <v>721</v>
+      </c>
+      <c r="C159" t="s" s="2">
+        <v>728</v>
+      </c>
       <c r="D159" t="s" s="2">
         <v>82</v>
       </c>
@@ -21565,23 +21651,19 @@
         <v>82</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>797</v>
+        <v>729</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>798</v>
+        <v>730</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>801</v>
-      </c>
+        <v>731</v>
+      </c>
+      <c r="N159" s="2"/>
+      <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>82</v>
       </c>
@@ -21629,25 +21711,25 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>796</v>
+        <v>120</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>433</v>
+        <v>121</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>755</v>
+        <v>82</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>802</v>
+        <v>82</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>82</v>
@@ -21661,14 +21743,14 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>803</v>
+        <v>732</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>803</v>
+        <v>732</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>82</v>
+        <v>733</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -21687,19 +21769,19 @@
         <v>91</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>685</v>
+        <v>113</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>804</v>
+        <v>734</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>805</v>
+        <v>735</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>806</v>
+        <v>116</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>807</v>
+        <v>356</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>82</v>
@@ -21748,7 +21830,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>803</v>
+        <v>736</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21760,13 +21842,13 @@
         <v>102</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>808</v>
+        <v>104</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>82</v>
@@ -21780,10 +21862,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>809</v>
+        <v>737</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>809</v>
+        <v>737</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21794,7 +21876,7 @@
         <v>80</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>82</v>
@@ -21806,16 +21888,20 @@
         <v>82</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>106</v>
+        <v>389</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>107</v>
+        <v>738</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N161" s="2"/>
-      <c r="O161" s="2"/>
+        <v>739</v>
+      </c>
+      <c r="N161" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="O161" t="s" s="2">
+        <v>740</v>
+      </c>
       <c r="P161" t="s" s="2">
         <v>82</v>
       </c>
@@ -21839,55 +21925,53 @@
         <v>82</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>82</v>
+        <v>741</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>82</v>
+        <v>742</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC161" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>743</v>
+      </c>
+      <c r="AC161" s="2"/>
       <c r="AD161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>109</v>
+        <v>737</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK161" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="AL161" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="AL161" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>82</v>
+        <v>745</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>82</v>
@@ -21895,21 +21979,23 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>810</v>
+        <v>746</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="C162" s="2"/>
+        <v>737</v>
+      </c>
+      <c r="C162" t="s" s="2">
+        <v>747</v>
+      </c>
       <c r="D162" t="s" s="2">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>82</v>
@@ -21921,18 +22007,20 @@
         <v>82</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>113</v>
+        <v>389</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>114</v>
+        <v>748</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>115</v>
+        <v>739</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O162" s="2"/>
+        <v>689</v>
+      </c>
+      <c r="O162" t="s" s="2">
+        <v>740</v>
+      </c>
       <c r="P162" t="s" s="2">
         <v>82</v>
       </c>
@@ -21956,31 +22044,29 @@
         <v>82</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y162" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Y162" s="2"/>
       <c r="Z162" t="s" s="2">
-        <v>82</v>
+        <v>749</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AC162" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AD162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE162" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>120</v>
+        <v>737</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -21992,19 +22078,19 @@
         <v>102</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>104</v>
+        <v>744</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>82</v>
+        <v>745</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
@@ -22012,45 +22098,47 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>811</v>
+        <v>750</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="C163" s="2"/>
+        <v>737</v>
+      </c>
+      <c r="C163" t="s" s="2">
+        <v>751</v>
+      </c>
       <c r="D163" t="s" s="2">
-        <v>705</v>
+        <v>82</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I163" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>113</v>
+        <v>389</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>706</v>
+        <v>752</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>707</v>
+        <v>739</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>116</v>
+        <v>689</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>356</v>
+        <v>740</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22075,13 +22163,11 @@
         <v>82</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y163" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
-        <v>82</v>
+        <v>753</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -22099,7 +22185,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>708</v>
+        <v>737</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22111,19 +22197,19 @@
         <v>102</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>104</v>
+        <v>744</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>82</v>
+        <v>745</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -22131,10 +22217,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>812</v>
+        <v>754</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>812</v>
+        <v>754</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22142,7 +22228,7 @@
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G164" t="s" s="2">
         <v>90</v>
@@ -22154,21 +22240,23 @@
         <v>82</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>813</v>
+        <v>554</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>814</v>
+        <v>755</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>815</v>
+        <v>756</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="O164" s="2"/>
+        <v>757</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>758</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
       </c>
@@ -22216,10 +22304,10 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>812</v>
+        <v>754</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>90</v>
@@ -22228,19 +22316,19 @@
         <v>102</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>433</v>
+        <v>103</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>365</v>
+        <v>759</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>817</v>
+        <v>760</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -22248,10 +22336,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>818</v>
+        <v>761</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>818</v>
+        <v>761</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22259,10 +22347,10 @@
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>82</v>
@@ -22271,21 +22359,23 @@
         <v>82</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>174</v>
+        <v>648</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>819</v>
+        <v>649</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>820</v>
+        <v>650</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O165" s="2"/>
+        <v>762</v>
+      </c>
+      <c r="O165" t="s" s="2">
+        <v>652</v>
+      </c>
       <c r="P165" t="s" s="2">
         <v>82</v>
       </c>
@@ -22309,13 +22399,13 @@
         <v>82</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>820</v>
+        <v>82</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>821</v>
+        <v>82</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -22333,33 +22423,2155 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>818</v>
+        <v>761</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH165" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI165" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AJ165" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AK165" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AL165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN165" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AO165" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="C166" s="2"/>
+      <c r="D166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E166" s="2"/>
+      <c r="F166" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G166" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K166" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="L166" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="M166" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="N166" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="O166" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="P166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q166" s="2"/>
+      <c r="R166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF166" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="AG166" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH166" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI166" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ166" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AK165" t="s" s="2">
+      <c r="AK166" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="AL166" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AM166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN166" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AO166" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="C167" s="2"/>
+      <c r="D167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E167" s="2"/>
+      <c r="F167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G167" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K167" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L167" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="N167" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O167" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="P167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q167" s="2"/>
+      <c r="R167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X167" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="Y167" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="Z167" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF167" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="AG167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH167" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI167" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ167" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK167" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AL167" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AM167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN167" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="AO167" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="C168" s="2"/>
+      <c r="D168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E168" s="2"/>
+      <c r="F168" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G168" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K168" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L168" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="O168" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="P168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q168" s="2"/>
+      <c r="R168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF168" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="AG168" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH168" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI168" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="AJ168" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AK168" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="AL168" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AM168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN168" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="AO168" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="C169" s="2"/>
+      <c r="D169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E169" s="2"/>
+      <c r="F169" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G169" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K169" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L169" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="M169" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="N169" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O169" s="2"/>
+      <c r="P169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q169" s="2"/>
+      <c r="R169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF169" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI169" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ169" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AK169" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="AL169" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AM169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN169" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="AO169" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="C170" s="2"/>
+      <c r="D170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E170" s="2"/>
+      <c r="F170" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G170" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K170" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="L170" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="M170" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="N170" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="O170" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="P170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q170" s="2"/>
+      <c r="R170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF170" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="AG170" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH170" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI170" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ170" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK170" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="AL170" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="AM170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO170" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="C171" s="2"/>
+      <c r="D171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E171" s="2"/>
+      <c r="F171" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G171" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K171" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L171" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M171" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N171" s="2"/>
+      <c r="O171" s="2"/>
+      <c r="P171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q171" s="2"/>
+      <c r="R171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF171" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK171" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AL171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO171" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="C172" s="2"/>
+      <c r="D172" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="E172" s="2"/>
+      <c r="F172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K172" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L172" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M172" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="O172" s="2"/>
+      <c r="P172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q172" s="2"/>
+      <c r="R172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB172" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AC172" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AD172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE172" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AF172" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI172" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ172" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AK172" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AL172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO172" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="C173" s="2"/>
+      <c r="D173" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="E173" s="2"/>
+      <c r="F173" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I173" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J173" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K173" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L173" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="M173" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="P173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q173" s="2"/>
+      <c r="R173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF173" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AG173" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI173" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ173" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AL173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO173" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E174" s="2"/>
+      <c r="F174" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G174" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K174" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L174" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="P174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q174" s="2"/>
+      <c r="R174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X174" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y174" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Z174" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AA174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF174" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="AG174" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH174" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI174" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ174" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK174" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="AL174" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="AM174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN174" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="AO174" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="C175" s="2"/>
+      <c r="D175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E175" s="2"/>
+      <c r="F175" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G175" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K175" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L175" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="M175" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="N175" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="O175" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="P175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q175" s="2"/>
+      <c r="R175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF175" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="AG175" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH175" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI175" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ175" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK175" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="AL175" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="AM175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN175" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="AO175" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="C176" s="2"/>
+      <c r="D176" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="E176" s="2"/>
+      <c r="F176" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K176" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="L176" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="M176" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="N176" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="O176" s="2"/>
+      <c r="P176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q176" s="2"/>
+      <c r="R176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF176" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="AG176" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI176" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ176" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AK176" t="s" s="2">
         <v>822</v>
       </c>
-      <c r="AL165" t="s" s="2">
+      <c r="AL176" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="AM165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO165" t="s" s="2">
+      <c r="AM176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN176" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="AO176" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="C177" s="2"/>
+      <c r="D177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E177" s="2"/>
+      <c r="F177" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G177" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J177" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K177" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="L177" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="M177" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="N177" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="O177" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="P177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q177" s="2"/>
+      <c r="R177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF177" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="AG177" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH177" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI177" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ177" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AK177" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="AL177" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="AM177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO177" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="C178" s="2"/>
+      <c r="D178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E178" s="2"/>
+      <c r="F178" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I178" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J178" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K178" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="L178" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="M178" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="N178" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="O178" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="P178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q178" s="2"/>
+      <c r="R178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF178" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="AG178" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI178" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ178" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK178" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="AL178" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AM178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO178" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="C179" s="2"/>
+      <c r="D179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E179" s="2"/>
+      <c r="F179" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G179" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K179" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L179" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M179" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N179" s="2"/>
+      <c r="O179" s="2"/>
+      <c r="P179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q179" s="2"/>
+      <c r="R179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF179" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG179" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH179" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK179" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AL179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO179" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="C180" s="2"/>
+      <c r="D180" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="E180" s="2"/>
+      <c r="F180" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K180" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L180" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M180" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="O180" s="2"/>
+      <c r="P180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q180" s="2"/>
+      <c r="R180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB180" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AC180" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AD180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE180" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AF180" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG180" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI180" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ180" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AK180" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AL180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO180" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="C181" s="2"/>
+      <c r="D181" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="E181" s="2"/>
+      <c r="F181" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I181" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J181" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K181" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L181" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="M181" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="N181" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="O181" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="P181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q181" s="2"/>
+      <c r="R181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF181" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AG181" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI181" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ181" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AK181" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AL181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO181" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>840</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>840</v>
+      </c>
+      <c r="C182" s="2"/>
+      <c r="D182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E182" s="2"/>
+      <c r="F182" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G182" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J182" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K182" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="L182" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="M182" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="O182" s="2"/>
+      <c r="P182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q182" s="2"/>
+      <c r="R182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF182" t="s" s="2">
+        <v>840</v>
+      </c>
+      <c r="AG182" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH182" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI182" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ182" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AK182" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AL182" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AM182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN182" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="AO182" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>846</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>846</v>
+      </c>
+      <c r="C183" s="2"/>
+      <c r="D183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E183" s="2"/>
+      <c r="F183" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G183" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J183" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K183" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L183" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="M183" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O183" s="2"/>
+      <c r="P183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q183" s="2"/>
+      <c r="R183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X183" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="Y183" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="Z183" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="AA183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF183" t="s" s="2">
+        <v>846</v>
+      </c>
+      <c r="AG183" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH183" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI183" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AJ183" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK183" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="AL183" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AM183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO183" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil FRCorePatientProfile enrichi de l'identité INS récupérée par le téléservice INSi et potentiellement qualifiée. Ce profil permet d'indiquer les contraintes fortes nécessaires pour modéliser un patient avec les traits INS et le matricule INS. Une ressource conforme au profil FRCorePatientINSProfile sera également conforme au profil FRCorePatientProfile grâce au principe d'héritage, il n'est donc pas nécessaire d'avoir une instance de chaque profil pour un même patient. Pour plus d'informations sur le contexte du patient INS, consultez le référentiel national d'identitovigilance (RNIV) et la documentation du référentiel INS de l'ANS.</t>
+    <t>Profil Fr Core Patient surspécifié pour être conforme aux exigences du référentiel d'Identité Nationale de Santé (INS).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -11181,7 +11181,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6834" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6834" uniqueCount="840">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -433,7 +433,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -453,7 +453,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -2156,9 +2156,6 @@
   </si>
   <si>
     <t>Patient.address</t>
-  </si>
-  <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
   </si>
   <si>
     <t>May need to keep track of patient addresses for contacting, billing or reporting requirements and also to help with identification.</t>
@@ -8304,7 +8301,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>90</v>
@@ -8542,7 +8539,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>90</v>
@@ -9361,7 +9358,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>90</v>
@@ -9501,7 +9498,7 @@
         <v>385</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>432</v>
+        <v>386</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>387</v>
@@ -9599,7 +9596,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>90</v>
@@ -10418,7 +10415,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>90</v>
@@ -11475,7 +11472,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>90</v>
@@ -12532,7 +12529,7 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>90</v>
@@ -13589,7 +13586,7 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>90</v>
@@ -13827,7 +13824,7 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>90</v>
@@ -14646,7 +14643,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>90</v>
@@ -14884,7 +14881,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>90</v>
@@ -15703,7 +15700,7 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>90</v>
@@ -15941,7 +15938,7 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>90</v>
@@ -16760,7 +16757,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>90</v>
@@ -16998,7 +16995,7 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>90</v>
@@ -20661,10 +20658,10 @@
         <v>239</v>
       </c>
       <c r="N151" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="O151" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -20745,10 +20742,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20774,14 +20771,14 @@
         <v>384</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -20810,7 +20807,7 @@
       </c>
       <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>82</v>
@@ -20828,7 +20825,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20843,16 +20840,16 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AL152" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="AL152" t="s" s="2">
+      <c r="AM152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN152" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -20860,10 +20857,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20886,19 +20883,19 @@
         <v>82</v>
       </c>
       <c r="K153" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="L153" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="L153" t="s" s="2">
+      <c r="M153" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="N153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>82</v>
@@ -20947,7 +20944,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20962,7 +20959,7 @@
         <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>108</v>
@@ -20971,7 +20968,7 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -20979,10 +20976,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21005,19 +21002,19 @@
         <v>82</v>
       </c>
       <c r="K154" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="L154" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="L154" t="s" s="2">
+      <c r="M154" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="N154" t="s" s="2">
+      <c r="O154" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
@@ -21066,7 +21063,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21081,7 +21078,7 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>108</v>
@@ -21090,7 +21087,7 @@
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -21098,10 +21095,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21124,19 +21121,19 @@
         <v>82</v>
       </c>
       <c r="K155" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="L155" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="L155" t="s" s="2">
+      <c r="M155" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="M155" t="s" s="2">
+      <c r="N155" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="N155" t="s" s="2">
+      <c r="O155" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -21185,7 +21182,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21197,10 +21194,10 @@
         <v>82</v>
       </c>
       <c r="AJ155" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AK155" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="AK155" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>108</v>
@@ -21217,10 +21214,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21332,10 +21329,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21445,13 +21442,13 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C158" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="C158" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="D158" t="s" s="2">
         <v>82</v>
@@ -21473,13 +21470,13 @@
         <v>82</v>
       </c>
       <c r="K158" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="L158" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="L158" t="s" s="2">
+      <c r="M158" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21562,13 +21559,13 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C159" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="C159" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>82</v>
@@ -21590,13 +21587,13 @@
         <v>82</v>
       </c>
       <c r="K159" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="L159" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="L159" t="s" s="2">
+      <c r="M159" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -21679,14 +21676,14 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -21708,10 +21705,10 @@
         <v>111</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>114</v>
@@ -21766,7 +21763,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21798,10 +21795,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21827,14 +21824,14 @@
         <v>384</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M161" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>82</v>
@@ -21862,16 +21859,16 @@
         <v>152</v>
       </c>
       <c r="Y161" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="Z161" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="Z161" t="s" s="2">
+      <c r="AA161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB161" t="s" s="2">
         <v>734</v>
-      </c>
-      <c r="AA161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB161" t="s" s="2">
-        <v>735</v>
       </c>
       <c r="AC161" s="2"/>
       <c r="AD161" t="s" s="2">
@@ -21881,7 +21878,7 @@
         <v>117</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -21896,7 +21893,7 @@
         <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AL161" t="s" s="2">
         <v>108</v>
@@ -21905,7 +21902,7 @@
         <v>82</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>82</v>
@@ -21913,13 +21910,13 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="C162" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="C162" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>82</v>
@@ -21944,14 +21941,14 @@
         <v>384</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>82</v>
@@ -21980,7 +21977,7 @@
       </c>
       <c r="Y162" s="2"/>
       <c r="Z162" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>82</v>
@@ -21998,7 +21995,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -22013,7 +22010,7 @@
         <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>108</v>
@@ -22022,7 +22019,7 @@
         <v>82</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
@@ -22030,13 +22027,13 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="C163" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="C163" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="D163" t="s" s="2">
         <v>82</v>
@@ -22061,14 +22058,14 @@
         <v>384</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22097,7 +22094,7 @@
       </c>
       <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -22115,7 +22112,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22130,7 +22127,7 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>108</v>
@@ -22139,7 +22136,7 @@
         <v>82</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -22147,10 +22144,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22176,16 +22173,16 @@
         <v>548</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>747</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="N164" t="s" s="2">
         <v>748</v>
       </c>
-      <c r="N164" t="s" s="2">
+      <c r="O164" t="s" s="2">
         <v>749</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
@@ -22234,7 +22231,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22249,16 +22246,16 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="AL164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN164" t="s" s="2">
         <v>751</v>
-      </c>
-      <c r="AL164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN164" t="s" s="2">
-        <v>752</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -22266,10 +22263,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22301,7 +22298,7 @@
         <v>644</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="O165" t="s" s="2">
         <v>646</v>
@@ -22353,7 +22350,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22385,10 +22382,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22411,17 +22408,17 @@
         <v>82</v>
       </c>
       <c r="K166" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="L166" t="s" s="2">
         <v>756</v>
       </c>
-      <c r="L166" t="s" s="2">
+      <c r="M166" t="s" s="2">
         <v>757</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>758</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -22470,7 +22467,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22485,7 +22482,7 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>108</v>
@@ -22494,7 +22491,7 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -22502,10 +22499,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22531,14 +22528,14 @@
         <v>170</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>764</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>82</v>
@@ -22566,11 +22563,11 @@
         <v>260</v>
       </c>
       <c r="Y167" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="Z167" t="s" s="2">
         <v>766</v>
       </c>
-      <c r="Z167" t="s" s="2">
-        <v>767</v>
-      </c>
       <c r="AA167" t="s" s="2">
         <v>82</v>
       </c>
@@ -22587,7 +22584,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22611,7 +22608,7 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -22619,10 +22616,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22648,14 +22645,14 @@
         <v>423</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>771</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -22704,7 +22701,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22713,13 +22710,13 @@
         <v>90</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>108</v>
@@ -22728,7 +22725,7 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -22736,10 +22733,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22765,10 +22762,10 @@
         <v>340</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>778</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -22819,7 +22816,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22834,7 +22831,7 @@
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>108</v>
@@ -22851,10 +22848,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22877,19 +22874,19 @@
         <v>82</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>781</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="N170" t="s" s="2">
+      <c r="O170" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>82</v>
@@ -22938,7 +22935,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22953,10 +22950,10 @@
         <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="AL170" t="s" s="2">
         <v>785</v>
-      </c>
-      <c r="AL170" t="s" s="2">
-        <v>786</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>82</v>
@@ -22970,10 +22967,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23085,10 +23082,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23202,14 +23199,14 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
@@ -23231,10 +23228,10 @@
         <v>111</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="N173" t="s" s="2">
         <v>114</v>
@@ -23289,7 +23286,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23321,10 +23318,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23350,16 +23347,16 @@
         <v>384</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>791</v>
       </c>
-      <c r="M174" t="s" s="2">
+      <c r="N174" t="s" s="2">
         <v>792</v>
       </c>
-      <c r="N174" t="s" s="2">
+      <c r="O174" t="s" s="2">
         <v>793</v>
-      </c>
-      <c r="O174" t="s" s="2">
-        <v>794</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>82</v>
@@ -23408,7 +23405,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>90</v>
@@ -23423,16 +23420,16 @@
         <v>102</v>
       </c>
       <c r="AK174" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="AL174" t="s" s="2">
         <v>795</v>
       </c>
-      <c r="AL174" t="s" s="2">
+      <c r="AM174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN174" t="s" s="2">
         <v>796</v>
-      </c>
-      <c r="AM174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN174" t="s" s="2">
-        <v>797</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>82</v>
@@ -23440,10 +23437,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23469,16 +23466,16 @@
         <v>539</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>799</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>800</v>
       </c>
-      <c r="N175" t="s" s="2">
+      <c r="O175" t="s" s="2">
         <v>801</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>802</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -23527,7 +23524,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23542,16 +23539,16 @@
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="AL175" t="s" s="2">
         <v>803</v>
       </c>
-      <c r="AL175" t="s" s="2">
+      <c r="AM175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN175" t="s" s="2">
         <v>804</v>
-      </c>
-      <c r="AM175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN175" t="s" s="2">
-        <v>805</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>82</v>
@@ -23559,14 +23556,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -23585,16 +23582,16 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="L176" t="s" s="2">
         <v>808</v>
       </c>
-      <c r="L176" t="s" s="2">
+      <c r="M176" t="s" s="2">
         <v>809</v>
       </c>
-      <c r="M176" t="s" s="2">
+      <c r="N176" t="s" s="2">
         <v>810</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -23644,7 +23641,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23659,7 +23656,7 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AL176" t="s" s="2">
         <v>108</v>
@@ -23668,7 +23665,7 @@
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>82</v>
@@ -23676,10 +23673,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23702,19 +23699,19 @@
         <v>91</v>
       </c>
       <c r="K177" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="L177" t="s" s="2">
         <v>815</v>
       </c>
-      <c r="L177" t="s" s="2">
+      <c r="M177" t="s" s="2">
         <v>816</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>817</v>
       </c>
-      <c r="N177" t="s" s="2">
+      <c r="O177" t="s" s="2">
         <v>818</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>819</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>82</v>
@@ -23763,7 +23760,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23778,10 +23775,10 @@
         <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>82</v>
@@ -23795,10 +23792,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23821,19 +23818,19 @@
         <v>91</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="L178" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="M178" t="s" s="2">
         <v>822</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>823</v>
       </c>
-      <c r="N178" t="s" s="2">
+      <c r="O178" t="s" s="2">
         <v>824</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>825</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>82</v>
@@ -23882,7 +23879,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23897,7 +23894,7 @@
         <v>102</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>108</v>
@@ -23914,10 +23911,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24029,10 +24026,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24146,14 +24143,14 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
@@ -24175,10 +24172,10 @@
         <v>111</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="N181" t="s" s="2">
         <v>114</v>
@@ -24233,7 +24230,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24265,10 +24262,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24291,16 +24288,16 @@
         <v>91</v>
       </c>
       <c r="K182" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="L182" t="s" s="2">
         <v>831</v>
       </c>
-      <c r="L182" t="s" s="2">
+      <c r="M182" t="s" s="2">
         <v>832</v>
       </c>
-      <c r="M182" t="s" s="2">
+      <c r="N182" t="s" s="2">
         <v>833</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>834</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -24350,7 +24347,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>90</v>
@@ -24374,7 +24371,7 @@
         <v>82</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>82</v>
@@ -24382,10 +24379,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24411,10 +24408,10 @@
         <v>170</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>837</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>838</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -24444,11 +24441,11 @@
         <v>260</v>
       </c>
       <c r="Y183" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="Z183" t="s" s="2">
         <v>838</v>
       </c>
-      <c r="Z183" t="s" s="2">
-        <v>839</v>
-      </c>
       <c r="AA183" t="s" s="2">
         <v>82</v>
       </c>
@@ -24465,7 +24462,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>90</v>
@@ -24480,7 +24477,7 @@
         <v>102</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension.where(url= 'https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension.where(url = 'identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension.where(url= 'https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension.where(url = 'identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11').exists())}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6870" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6865" uniqueCount="847">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1236,10 +1236,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1564,6 +1561,12 @@
     &lt;code value="INS-NIR"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Patient.identifier:INS-NIR.system</t>
@@ -3034,7 +3037,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.12109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.0703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="75.2109375" customWidth="true" bestFit="true"/>
@@ -8609,29 +8612,27 @@
       <c r="X48" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Y48" s="2"/>
+      <c r="Z48" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z48" t="s" s="2">
+      <c r="AA48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8655,7 +8656,7 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8663,10 +8664,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8692,16 +8693,16 @@
         <v>132</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8711,46 +8712,46 @@
         <v>82</v>
       </c>
       <c r="S49" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="T49" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="T49" t="s" s="2">
+      <c r="U49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8765,16 +8766,16 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8782,10 +8783,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8811,13 +8812,13 @@
         <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8831,43 +8832,43 @@
         <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8882,16 +8883,16 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8899,10 +8900,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8928,10 +8929,10 @@
         <v>340</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8982,7 +8983,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8997,16 +8998,16 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -9014,10 +9015,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9040,16 +9041,16 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9099,7 +9100,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -9114,16 +9115,16 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -9131,13 +9132,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>82</v>
@@ -9162,7 +9163,7 @@
         <v>354</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="M53" t="s" s="2">
         <v>356</v>
@@ -9250,7 +9251,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>368</v>
@@ -9365,7 +9366,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>370</v>
@@ -9482,7 +9483,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>372</v>
@@ -9530,7 +9531,7 @@
         <v>82</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>82</v>
@@ -9601,7 +9602,7 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>383</v>
@@ -9649,7 +9650,7 @@
         <v>82</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>82</v>
@@ -9666,29 +9667,27 @@
       <c r="X57" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Y57" t="s" s="2">
+      <c r="Y57" s="2"/>
+      <c r="Z57" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z57" t="s" s="2">
+      <c r="AA57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9712,7 +9711,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9720,10 +9719,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9749,16 +9748,16 @@
         <v>132</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9768,46 +9767,46 @@
         <v>82</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="T58" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9822,16 +9821,16 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9839,10 +9838,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9868,13 +9867,13 @@
         <v>104</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9888,43 +9887,43 @@
         <v>82</v>
       </c>
       <c r="T59" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9939,16 +9938,16 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9956,10 +9955,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9985,10 +9984,10 @@
         <v>340</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10039,7 +10038,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -10054,16 +10053,16 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -10071,10 +10070,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10097,16 +10096,16 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10156,7 +10155,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -10171,16 +10170,16 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -10188,13 +10187,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>82</v>
@@ -10219,7 +10218,7 @@
         <v>354</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="M62" t="s" s="2">
         <v>356</v>
@@ -10307,7 +10306,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>368</v>
@@ -10422,7 +10421,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>370</v>
@@ -10539,7 +10538,7 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>372</v>
@@ -10587,7 +10586,7 @@
         <v>82</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>82</v>
@@ -10658,7 +10657,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>383</v>
@@ -10706,7 +10705,7 @@
         <v>82</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>82</v>
@@ -10723,29 +10722,27 @@
       <c r="X66" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Y66" t="s" s="2">
+      <c r="Y66" s="2"/>
+      <c r="Z66" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z66" t="s" s="2">
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10769,7 +10766,7 @@
         <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10777,10 +10774,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10806,16 +10803,16 @@
         <v>132</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10825,46 +10822,46 @@
         <v>82</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="T67" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10879,16 +10876,16 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10896,10 +10893,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10925,13 +10922,13 @@
         <v>104</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10945,43 +10942,43 @@
         <v>82</v>
       </c>
       <c r="T68" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10996,16 +10993,16 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -11013,10 +11010,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11042,10 +11039,10 @@
         <v>340</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11096,7 +11093,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -11111,16 +11108,16 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -11128,10 +11125,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11154,16 +11151,16 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11213,7 +11210,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11228,16 +11225,16 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -11245,13 +11242,13 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>82</v>
@@ -11276,7 +11273,7 @@
         <v>354</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="M71" t="s" s="2">
         <v>356</v>
@@ -11364,7 +11361,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>368</v>
@@ -11479,7 +11476,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>370</v>
@@ -11596,7 +11593,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>372</v>
@@ -11644,7 +11641,7 @@
         <v>82</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>82</v>
@@ -11715,7 +11712,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>383</v>
@@ -11763,7 +11760,7 @@
         <v>82</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>82</v>
@@ -11780,29 +11777,27 @@
       <c r="X75" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Y75" t="s" s="2">
+      <c r="Y75" s="2"/>
+      <c r="Z75" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z75" t="s" s="2">
+      <c r="AA75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11826,7 +11821,7 @@
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11834,10 +11829,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11863,16 +11858,16 @@
         <v>132</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11885,43 +11880,43 @@
         <v>82</v>
       </c>
       <c r="T76" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11936,16 +11931,16 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11953,10 +11948,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11982,13 +11977,13 @@
         <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12002,43 +11997,43 @@
         <v>82</v>
       </c>
       <c r="T77" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -12053,16 +12048,16 @@
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -12070,10 +12065,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12099,10 +12094,10 @@
         <v>340</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12153,7 +12148,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12168,16 +12163,16 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -12185,10 +12180,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12211,16 +12206,16 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12270,7 +12265,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12285,16 +12280,16 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12302,13 +12297,13 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>82</v>
@@ -12333,7 +12328,7 @@
         <v>354</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="M80" t="s" s="2">
         <v>356</v>
@@ -12421,7 +12416,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>368</v>
@@ -12536,7 +12531,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>370</v>
@@ -12653,7 +12648,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>372</v>
@@ -12701,7 +12696,7 @@
         <v>82</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>82</v>
@@ -12772,7 +12767,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>383</v>
@@ -12820,7 +12815,7 @@
         <v>82</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>82</v>
@@ -12837,29 +12832,27 @@
       <c r="X84" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Y84" t="s" s="2">
+      <c r="Y84" s="2"/>
+      <c r="Z84" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z84" t="s" s="2">
+      <c r="AA84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12883,7 +12876,7 @@
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12891,10 +12884,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12920,16 +12913,16 @@
         <v>132</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12942,43 +12935,43 @@
         <v>82</v>
       </c>
       <c r="T85" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12993,16 +12986,16 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -13010,10 +13003,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13039,13 +13032,13 @@
         <v>104</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -13059,43 +13052,43 @@
         <v>82</v>
       </c>
       <c r="T86" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13110,16 +13103,16 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -13127,10 +13120,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13156,10 +13149,10 @@
         <v>340</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13210,7 +13203,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13225,16 +13218,16 @@
         <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -13242,10 +13235,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13268,16 +13261,16 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13327,7 +13320,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13342,16 +13335,16 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13359,13 +13352,13 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>82</v>
@@ -13390,7 +13383,7 @@
         <v>354</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="M89" t="s" s="2">
         <v>356</v>
@@ -13478,7 +13471,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>368</v>
@@ -13593,7 +13586,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>370</v>
@@ -13710,7 +13703,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>372</v>
@@ -13829,7 +13822,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>383</v>
@@ -13877,7 +13870,7 @@
         <v>82</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>82</v>
@@ -13895,28 +13888,28 @@
         <v>154</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>390</v>
+        <v>489</v>
       </c>
       <c r="Z93" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13940,7 +13933,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13948,10 +13941,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13977,16 +13970,16 @@
         <v>132</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M94" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13996,46 +13989,46 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="T94" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="T94" t="s" s="2">
+      <c r="U94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14050,16 +14043,16 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -14067,10 +14060,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14096,13 +14089,13 @@
         <v>104</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14116,43 +14109,43 @@
         <v>82</v>
       </c>
       <c r="T95" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14167,16 +14160,16 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -14184,10 +14177,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14213,10 +14206,10 @@
         <v>340</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14267,7 +14260,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14282,16 +14275,16 @@
         <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14299,10 +14292,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14325,16 +14318,16 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14384,7 +14377,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14399,16 +14392,16 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14416,13 +14409,13 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>82</v>
@@ -14447,7 +14440,7 @@
         <v>354</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M98" t="s" s="2">
         <v>356</v>
@@ -14535,7 +14528,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>368</v>
@@ -14650,7 +14643,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>370</v>
@@ -14767,7 +14760,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>372</v>
@@ -14886,7 +14879,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>383</v>
@@ -14934,7 +14927,7 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>82</v>
@@ -14952,28 +14945,28 @@
         <v>154</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>390</v>
+        <v>489</v>
       </c>
       <c r="Z102" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14997,7 +14990,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -15005,10 +14998,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15034,16 +15027,16 @@
         <v>132</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M103" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15053,46 +15046,46 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="T103" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15107,16 +15100,16 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN103" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15124,10 +15117,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15153,13 +15146,13 @@
         <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15173,43 +15166,43 @@
         <v>82</v>
       </c>
       <c r="T104" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15224,16 +15217,16 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15241,10 +15234,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15270,10 +15263,10 @@
         <v>340</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15324,7 +15317,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15339,16 +15332,16 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15356,10 +15349,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15382,16 +15375,16 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15441,7 +15434,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15456,16 +15449,16 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15473,13 +15466,13 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>82</v>
@@ -15504,7 +15497,7 @@
         <v>354</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M107" t="s" s="2">
         <v>356</v>
@@ -15592,7 +15585,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>368</v>
@@ -15707,7 +15700,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>370</v>
@@ -15824,7 +15817,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>372</v>
@@ -15943,7 +15936,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>383</v>
@@ -15991,7 +15984,7 @@
         <v>82</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>82</v>
@@ -16009,28 +16002,28 @@
         <v>154</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>390</v>
+        <v>489</v>
       </c>
       <c r="Z111" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF111" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16054,7 +16047,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16062,10 +16055,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16091,16 +16084,16 @@
         <v>132</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M112" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N112" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -16110,46 +16103,46 @@
         <v>82</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="T112" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF112" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16164,16 +16157,16 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN112" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16181,10 +16174,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16210,13 +16203,13 @@
         <v>104</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16230,43 +16223,43 @@
         <v>82</v>
       </c>
       <c r="T113" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF113" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16281,16 +16274,16 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16298,10 +16291,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16327,10 +16320,10 @@
         <v>340</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16381,7 +16374,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16396,16 +16389,16 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16413,10 +16406,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16439,16 +16432,16 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16498,7 +16491,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16513,16 +16506,16 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16530,13 +16523,13 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>82</v>
@@ -16561,7 +16554,7 @@
         <v>354</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>356</v>
@@ -16649,7 +16642,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>368</v>
@@ -16764,7 +16757,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>370</v>
@@ -16881,7 +16874,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>372</v>
@@ -16929,7 +16922,7 @@
         <v>82</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>82</v>
@@ -17000,7 +16993,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>383</v>
@@ -17048,7 +17041,7 @@
         <v>82</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>82</v>
@@ -17066,28 +17059,28 @@
         <v>154</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>390</v>
+        <v>489</v>
       </c>
       <c r="Z120" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF120" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17111,7 +17104,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -17119,10 +17112,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17148,16 +17141,16 @@
         <v>132</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M121" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N121" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N121" t="s" s="2">
+      <c r="O121" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -17167,46 +17160,46 @@
         <v>82</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="T121" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF121" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17221,16 +17214,16 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN121" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -17238,10 +17231,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17267,13 +17260,13 @@
         <v>104</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -17287,43 +17280,43 @@
         <v>82</v>
       </c>
       <c r="T122" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF122" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17338,16 +17331,16 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -17355,10 +17348,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17384,10 +17377,10 @@
         <v>340</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -17438,7 +17431,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17453,16 +17446,16 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -17470,10 +17463,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17496,16 +17489,16 @@
         <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L124" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L124" t="s" s="2">
+      <c r="M124" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -17555,7 +17548,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17570,16 +17563,16 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17587,10 +17580,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17613,70 +17606,70 @@
         <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q125" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="R125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF125" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="P125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q125" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="R125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17691,13 +17684,13 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>82</v>
@@ -17708,10 +17701,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17734,19 +17727,19 @@
         <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17783,7 +17776,7 @@
         <v>82</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AC126" s="2"/>
       <c r="AD126" t="s" s="2">
@@ -17793,7 +17786,7 @@
         <v>117</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17808,16 +17801,16 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17825,13 +17818,13 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>82</v>
@@ -17853,19 +17846,19 @@
         <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17914,7 +17907,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17929,16 +17922,16 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17946,10 +17939,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18061,10 +18054,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18178,10 +18171,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18207,16 +18200,16 @@
         <v>172</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -18226,7 +18219,7 @@
         <v>82</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>82</v>
@@ -18244,10 +18237,10 @@
         <v>260</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>82</v>
@@ -18265,7 +18258,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18289,7 +18282,7 @@
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -18297,10 +18290,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18326,13 +18319,13 @@
         <v>104</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O131" t="s" s="2">
         <v>281</v>
@@ -18384,7 +18377,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18408,7 +18401,7 @@
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -18416,14 +18409,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -18445,13 +18438,13 @@
         <v>104</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18501,7 +18494,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18516,7 +18509,7 @@
         <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>82</v>
@@ -18525,7 +18518,7 @@
         <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -18533,14 +18526,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18562,13 +18555,13 @@
         <v>104</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18618,7 +18611,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18633,7 +18626,7 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>82</v>
@@ -18642,7 +18635,7 @@
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18650,10 +18643,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18679,10 +18672,10 @@
         <v>104</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18733,7 +18726,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18748,7 +18741,7 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>82</v>
@@ -18757,7 +18750,7 @@
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18765,10 +18758,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18794,10 +18787,10 @@
         <v>104</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18848,7 +18841,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18863,7 +18856,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>82</v>
@@ -18872,7 +18865,7 @@
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18880,10 +18873,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18909,14 +18902,14 @@
         <v>340</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -18965,7 +18958,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18989,7 +18982,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -18997,13 +18990,13 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>82</v>
@@ -19025,19 +19018,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -19086,7 +19079,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19101,16 +19094,16 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>82</v>
@@ -19118,10 +19111,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19233,10 +19226,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19348,13 +19341,13 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D140" t="s" s="2">
         <v>82</v>
@@ -19376,13 +19369,13 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19465,10 +19458,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19494,16 +19487,16 @@
         <v>172</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19531,10 +19524,10 @@
         <v>260</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>82</v>
@@ -19552,7 +19545,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19576,7 +19569,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19584,10 +19577,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19613,13 +19606,13 @@
         <v>104</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O142" t="s" s="2">
         <v>281</v>
@@ -19671,7 +19664,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19695,7 +19688,7 @@
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19703,14 +19696,14 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -19732,13 +19725,13 @@
         <v>104</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -19788,7 +19781,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19803,7 +19796,7 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>82</v>
@@ -19812,7 +19805,7 @@
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>82</v>
@@ -19820,14 +19813,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -19849,13 +19842,13 @@
         <v>104</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19905,7 +19898,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19920,7 +19913,7 @@
         <v>102</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>82</v>
@@ -19929,7 +19922,7 @@
         <v>82</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>82</v>
@@ -19937,10 +19930,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19966,10 +19959,10 @@
         <v>104</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20020,7 +20013,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20035,7 +20028,7 @@
         <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>82</v>
@@ -20044,7 +20037,7 @@
         <v>82</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>82</v>
@@ -20052,10 +20045,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20081,10 +20074,10 @@
         <v>104</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20135,7 +20128,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20150,7 +20143,7 @@
         <v>102</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>82</v>
@@ -20159,7 +20152,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -20167,10 +20160,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20196,14 +20189,14 @@
         <v>340</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>82</v>
@@ -20252,7 +20245,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20276,7 +20269,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
@@ -20284,10 +20277,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20310,19 +20303,19 @@
         <v>91</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -20371,7 +20364,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20386,16 +20379,16 @@
         <v>102</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -20403,10 +20396,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20432,16 +20425,16 @@
         <v>172</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -20470,7 +20463,7 @@
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>82</v>
@@ -20488,7 +20481,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20503,16 +20496,16 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -20520,10 +20513,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20546,19 +20539,19 @@
         <v>91</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>82</v>
@@ -20607,7 +20600,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20622,27 +20615,27 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20665,19 +20658,19 @@
         <v>91</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -20726,7 +20719,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20741,7 +20734,7 @@
         <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>108</v>
@@ -20750,7 +20743,7 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -20758,10 +20751,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20787,16 +20780,16 @@
         <v>239</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -20845,7 +20838,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20860,16 +20853,16 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -20877,10 +20870,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20906,14 +20899,14 @@
         <v>384</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>82</v>
@@ -20942,7 +20935,7 @@
       </c>
       <c r="Y153" s="2"/>
       <c r="Z153" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>82</v>
@@ -20960,7 +20953,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20975,16 +20968,16 @@
         <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -20992,10 +20985,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21018,19 +21011,19 @@
         <v>82</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
@@ -21079,7 +21072,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21094,7 +21087,7 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>108</v>
@@ -21103,7 +21096,7 @@
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -21111,10 +21104,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21137,19 +21130,19 @@
         <v>82</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -21198,7 +21191,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21213,7 +21206,7 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>108</v>
@@ -21222,7 +21215,7 @@
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -21230,10 +21223,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21256,19 +21249,19 @@
         <v>82</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -21317,7 +21310,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21329,10 +21322,10 @@
         <v>82</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>108</v>
@@ -21349,10 +21342,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21464,10 +21457,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21577,13 +21570,13 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="B159" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="B159" t="s" s="2">
-        <v>718</v>
-      </c>
       <c r="C159" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>82</v>
@@ -21605,13 +21598,13 @@
         <v>82</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -21694,13 +21687,13 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>82</v>
@@ -21722,13 +21715,13 @@
         <v>82</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21811,14 +21804,14 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -21840,10 +21833,10 @@
         <v>111</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N161" t="s" s="2">
         <v>114</v>
@@ -21898,7 +21891,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -21930,10 +21923,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21959,14 +21952,14 @@
         <v>384</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>82</v>
@@ -21994,16 +21987,16 @@
         <v>154</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AC162" s="2"/>
       <c r="AD162" t="s" s="2">
@@ -22013,7 +22006,7 @@
         <v>117</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -22028,7 +22021,7 @@
         <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>108</v>
@@ -22037,7 +22030,7 @@
         <v>82</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
@@ -22045,13 +22038,13 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D163" t="s" s="2">
         <v>82</v>
@@ -22076,14 +22069,14 @@
         <v>384</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22112,7 +22105,7 @@
       </c>
       <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -22130,7 +22123,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22145,7 +22138,7 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>108</v>
@@ -22154,7 +22147,7 @@
         <v>82</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -22162,13 +22155,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>82</v>
@@ -22193,14 +22186,14 @@
         <v>384</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
@@ -22229,7 +22222,7 @@
       </c>
       <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>82</v>
@@ -22247,7 +22240,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22262,7 +22255,7 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>108</v>
@@ -22271,7 +22264,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -22279,10 +22272,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22305,17 +22298,17 @@
         <v>82</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>82</v>
@@ -22364,7 +22357,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22379,7 +22372,7 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>108</v>
@@ -22388,7 +22381,7 @@
         <v>82</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -22396,10 +22389,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22422,19 +22415,19 @@
         <v>82</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -22483,7 +22476,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22498,7 +22491,7 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>108</v>
@@ -22507,7 +22500,7 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -22515,10 +22508,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22541,17 +22534,17 @@
         <v>82</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>82</v>
@@ -22600,7 +22593,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22615,7 +22608,7 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>108</v>
@@ -22624,7 +22617,7 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -22632,10 +22625,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22661,14 +22654,14 @@
         <v>172</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -22696,10 +22689,10 @@
         <v>260</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>82</v>
@@ -22717,7 +22710,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22732,7 +22725,7 @@
         <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>108</v>
@@ -22741,7 +22734,7 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -22749,10 +22742,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22775,17 +22768,17 @@
         <v>82</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>82</v>
@@ -22834,7 +22827,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22843,13 +22836,13 @@
         <v>90</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>108</v>
@@ -22858,7 +22851,7 @@
         <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
@@ -22866,10 +22859,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22895,10 +22888,10 @@
         <v>340</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -22949,7 +22942,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22964,7 +22957,7 @@
         <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>108</v>
@@ -22981,10 +22974,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23007,19 +23000,19 @@
         <v>82</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>82</v>
@@ -23068,7 +23061,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -23083,10 +23076,10 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>82</v>
@@ -23100,10 +23093,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23215,10 +23208,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23332,14 +23325,14 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
@@ -23361,10 +23354,10 @@
         <v>111</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N174" t="s" s="2">
         <v>114</v>
@@ -23419,7 +23412,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23451,10 +23444,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23480,16 +23473,16 @@
         <v>384</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -23538,7 +23531,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>90</v>
@@ -23553,16 +23546,16 @@
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>82</v>
@@ -23570,10 +23563,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23596,19 +23589,19 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>82</v>
@@ -23657,7 +23650,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23672,16 +23665,16 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AM176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>82</v>
@@ -23689,14 +23682,14 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
@@ -23715,16 +23708,16 @@
         <v>82</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23774,7 +23767,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23789,7 +23782,7 @@
         <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AL177" t="s" s="2">
         <v>108</v>
@@ -23798,7 +23791,7 @@
         <v>82</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>82</v>
@@ -23806,10 +23799,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23832,19 +23825,19 @@
         <v>91</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>82</v>
@@ -23893,7 +23886,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23908,10 +23901,10 @@
         <v>102</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>82</v>
@@ -23925,10 +23918,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23951,19 +23944,19 @@
         <v>91</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>82</v>
@@ -24012,7 +24005,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24027,7 +24020,7 @@
         <v>102</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AL179" t="s" s="2">
         <v>108</v>
@@ -24044,10 +24037,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24159,10 +24152,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24276,14 +24269,14 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
@@ -24305,10 +24298,10 @@
         <v>111</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N182" t="s" s="2">
         <v>114</v>
@@ -24363,7 +24356,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24395,10 +24388,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24421,16 +24414,16 @@
         <v>91</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
@@ -24480,7 +24473,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>90</v>
@@ -24504,7 +24497,7 @@
         <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>
@@ -24512,10 +24505,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24541,10 +24534,10 @@
         <v>172</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -24574,10 +24567,10 @@
         <v>260</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>82</v>
@@ -24595,7 +24588,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>90</v>
@@ -24610,7 +24603,7 @@
         <v>102</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AL184" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6865" uniqueCount="847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6865" uniqueCount="846">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,7 +676,9 @@
     <t>Reliabilility of the identity | Fiabilité de l'identité</t>
   </si>
   <si>
-    <t>Reliabilility of the patient's identity | Précision sur le degré de fiabilité de l'identité du patient (si provisoire, validé... avec la justification : quelle type de pièce d'identité ?) avec la méthode de collection</t>
+    <t>Précision sur le degré de fiabilité de l'identité du patient (si provisoire, validé... avec la justification : quelle type de pièce d'identité ?) accompagné de la méthode de collection.
++Reliabilility of the patient's identity</t>
   </si>
   <si>
     <t>Patient.extension:deathPlace</t>
@@ -692,7 +694,9 @@
     <t>FR Core Patient Death Place Extension</t>
   </si>
   <si>
-    <t>Carries the death place of the patient |Précise le lieu de décès du patient (hôpital, sur la voie publique, au domicile, etc.).</t>
+    <t>Précise le lieu de décès du patient (hôpital, sur la voie publique, au domicile, etc.).
++Carries the death place of the patient</t>
   </si>
   <si>
     <t>Patient.extension:birthdateUpdateIndicator</t>
@@ -805,7 +809,8 @@
     <t>FR Core Address Insee Code Extension</t>
   </si>
   <si>
-    <t>This extension adds the insee code (5 digits) to the address | Ajout du code insee (5 chiffres) à l'adresse postale</t>
+    <t>Extension d'ajout du code insee (5 chiffres) à l'adresse postale.
+This extension adds the insee code (5 digits) to the address</t>
   </si>
   <si>
     <t>Patient.extension:birthPlace.value[x].use</t>
@@ -2301,10 +2306,12 @@
 </t>
   </si>
   <si>
-    <t>Contact identifier in the patient resource | Identifiant de contact dans la ressource Patient</t>
-  </si>
-  <si>
-    <t>This extension carries the contact identifier in the patient resource | Ajout d'un identifiant de contact dans la ressource Patient</t>
+    <t>FR Core Patient Contact Identifier Extension</t>
+  </si>
+  <si>
+    <t>Identifiant de contact dans la ressource Patient
++This extension carries the contact identifier in the patient resource</t>
   </si>
   <si>
     <t>Patient.contact.extension:comment</t>
@@ -2320,7 +2327,8 @@
     <t>Comment on a dataElement | Commentaire sur un dataElement</t>
   </si>
   <si>
-    <t>add a comment on a dataElement  of a resource | Ajout d'un commentaire sur un dataElement d'une ressource</t>
+    <t>Ajout d'un commentaire sur un dataElement d'une ressource.
+Add a comment on a dataElement  of a resource</t>
   </si>
   <si>
     <t>Patient.contact.modifierExtension</t>
@@ -2356,10 +2364,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:coding.system}
-</t>
   </si>
   <si>
     <t>code</t>
@@ -21996,7 +22000,7 @@
         <v>82</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>741</v>
+        <v>142</v>
       </c>
       <c r="AC162" s="2"/>
       <c r="AD162" t="s" s="2">
@@ -22021,7 +22025,7 @@
         <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>108</v>
@@ -22030,7 +22034,7 @@
         <v>82</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
@@ -22038,13 +22042,13 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>735</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D163" t="s" s="2">
         <v>82</v>
@@ -22069,7 +22073,7 @@
         <v>384</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="M163" t="s" s="2">
         <v>737</v>
@@ -22105,7 +22109,7 @@
       </c>
       <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -22138,7 +22142,7 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>108</v>
@@ -22147,7 +22151,7 @@
         <v>82</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -22155,13 +22159,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>735</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>82</v>
@@ -22186,7 +22190,7 @@
         <v>384</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="M164" t="s" s="2">
         <v>737</v>
@@ -22222,7 +22226,7 @@
       </c>
       <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>82</v>
@@ -22255,7 +22259,7 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>108</v>
@@ -22264,7 +22268,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -22272,10 +22276,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22301,14 +22305,14 @@
         <v>549</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>82</v>
@@ -22357,7 +22361,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22381,7 +22385,7 @@
         <v>82</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -22389,10 +22393,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22418,13 +22422,13 @@
         <v>643</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>758</v>
       </c>
-      <c r="M166" t="s" s="2">
+      <c r="N166" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="O166" t="s" s="2">
         <v>647</v>
@@ -22476,7 +22480,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22500,7 +22504,7 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -22508,10 +22512,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22534,17 +22538,17 @@
         <v>82</v>
       </c>
       <c r="K167" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="L167" t="s" s="2">
         <v>763</v>
       </c>
-      <c r="L167" t="s" s="2">
+      <c r="M167" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>82</v>
@@ -22593,7 +22597,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22617,7 +22621,7 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -22625,10 +22629,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22654,14 +22658,14 @@
         <v>172</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>770</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -22689,11 +22693,11 @@
         <v>260</v>
       </c>
       <c r="Y168" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="Z168" t="s" s="2">
         <v>772</v>
       </c>
-      <c r="Z168" t="s" s="2">
-        <v>773</v>
-      </c>
       <c r="AA168" t="s" s="2">
         <v>82</v>
       </c>
@@ -22710,7 +22714,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22734,7 +22738,7 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -22742,10 +22746,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22771,14 +22775,14 @@
         <v>422</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>776</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>777</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>82</v>
@@ -22827,7 +22831,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22836,13 +22840,13 @@
         <v>90</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>108</v>
@@ -22851,7 +22855,7 @@
         <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
@@ -22859,10 +22863,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22888,10 +22892,10 @@
         <v>340</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -22942,7 +22946,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22957,7 +22961,7 @@
         <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>108</v>
@@ -22974,10 +22978,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23003,16 +23007,16 @@
         <v>711</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>787</v>
       </c>
-      <c r="M171" t="s" s="2">
+      <c r="N171" t="s" s="2">
         <v>788</v>
       </c>
-      <c r="N171" t="s" s="2">
+      <c r="O171" t="s" s="2">
         <v>789</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>790</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>82</v>
@@ -23061,7 +23065,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -23076,10 +23080,10 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="AL171" t="s" s="2">
         <v>791</v>
-      </c>
-      <c r="AL171" t="s" s="2">
-        <v>792</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>82</v>
@@ -23093,10 +23097,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23208,10 +23212,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23325,10 +23329,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23444,10 +23448,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23473,16 +23477,16 @@
         <v>384</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>797</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>798</v>
       </c>
-      <c r="N175" t="s" s="2">
+      <c r="O175" t="s" s="2">
         <v>799</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>800</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -23531,7 +23535,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>90</v>
@@ -23546,16 +23550,16 @@
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="AL175" t="s" s="2">
         <v>801</v>
       </c>
-      <c r="AL175" t="s" s="2">
+      <c r="AM175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN175" t="s" s="2">
         <v>802</v>
-      </c>
-      <c r="AM175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN175" t="s" s="2">
-        <v>803</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>82</v>
@@ -23563,10 +23567,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23592,16 +23596,16 @@
         <v>540</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>805</v>
       </c>
-      <c r="M176" t="s" s="2">
+      <c r="N176" t="s" s="2">
         <v>806</v>
       </c>
-      <c r="N176" t="s" s="2">
+      <c r="O176" t="s" s="2">
         <v>807</v>
-      </c>
-      <c r="O176" t="s" s="2">
-        <v>808</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>82</v>
@@ -23650,7 +23654,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23665,16 +23669,16 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="AL176" t="s" s="2">
         <v>809</v>
       </c>
-      <c r="AL176" t="s" s="2">
+      <c r="AM176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN176" t="s" s="2">
         <v>810</v>
-      </c>
-      <c r="AM176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN176" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>82</v>
@@ -23682,14 +23686,14 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
@@ -23708,16 +23712,16 @@
         <v>82</v>
       </c>
       <c r="K177" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="L177" t="s" s="2">
         <v>814</v>
       </c>
-      <c r="L177" t="s" s="2">
+      <c r="M177" t="s" s="2">
         <v>815</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>816</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>817</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23767,7 +23771,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23782,7 +23786,7 @@
         <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="AL177" t="s" s="2">
         <v>108</v>
@@ -23791,7 +23795,7 @@
         <v>82</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>82</v>
@@ -23799,10 +23803,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23825,19 +23829,19 @@
         <v>91</v>
       </c>
       <c r="K178" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="L178" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="L178" t="s" s="2">
+      <c r="M178" t="s" s="2">
         <v>822</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>823</v>
       </c>
-      <c r="N178" t="s" s="2">
+      <c r="O178" t="s" s="2">
         <v>824</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>825</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>82</v>
@@ -23886,7 +23890,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23901,10 +23905,10 @@
         <v>102</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>82</v>
@@ -23918,10 +23922,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23947,16 +23951,16 @@
         <v>711</v>
       </c>
       <c r="L179" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="M179" t="s" s="2">
         <v>828</v>
       </c>
-      <c r="M179" t="s" s="2">
+      <c r="N179" t="s" s="2">
         <v>829</v>
       </c>
-      <c r="N179" t="s" s="2">
+      <c r="O179" t="s" s="2">
         <v>830</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>831</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>82</v>
@@ -24005,7 +24009,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24020,7 +24024,7 @@
         <v>102</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AL179" t="s" s="2">
         <v>108</v>
@@ -24037,10 +24041,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24152,10 +24156,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24269,10 +24273,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24388,10 +24392,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24414,16 +24418,16 @@
         <v>91</v>
       </c>
       <c r="K183" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="L183" t="s" s="2">
         <v>837</v>
       </c>
-      <c r="L183" t="s" s="2">
+      <c r="M183" t="s" s="2">
         <v>838</v>
       </c>
-      <c r="M183" t="s" s="2">
+      <c r="N183" t="s" s="2">
         <v>839</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>840</v>
       </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
@@ -24473,7 +24477,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>90</v>
@@ -24497,7 +24501,7 @@
         <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>
@@ -24505,10 +24509,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24534,10 +24538,10 @@
         <v>172</v>
       </c>
       <c r="L184" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="M184" t="s" s="2">
         <v>843</v>
-      </c>
-      <c r="M184" t="s" s="2">
-        <v>844</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -24567,11 +24571,11 @@
         <v>260</v>
       </c>
       <c r="Y184" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="Z184" t="s" s="2">
         <v>844</v>
       </c>
-      <c r="Z184" t="s" s="2">
-        <v>845</v>
-      </c>
       <c r="AA184" t="s" s="2">
         <v>82</v>
       </c>
@@ -24588,7 +24592,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>90</v>
@@ -24603,7 +24607,7 @@
         <v>102</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AL184" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil Fr Core Patient surspécifié pour être conforme aux exigences du référentiel d'Identité Nationale de Santé (INS).</t>
+    <t>Profil Fr Core Patient surspécifié pour être conforme aux exigences du référentiel d'Identité Nationale de Santé (INS). Les identifiants INS-NIR ne peuvent être véhiculés uniquement dans le cas d'un patient qualifié, raison pour laquelle les slices identifier sont définies au niveau du FrCorePatientINS et non au niveau du FrCorePatient.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6902" uniqueCount="851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6902" uniqueCount="852">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension.where(url= 'https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension.where(url = 'identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11').exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11').exists())}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>
@@ -712,13 +712,16 @@
     <t>FR Core Patient Birthdate Update Indicator Extension</t>
   </si>
   <si>
+    <t>Indicateur booléen de mise à jour de la date de naissance</t>
+  </si>
+  <si>
     <t>Patient.extension:birthPlace</t>
   </si>
   <si>
     <t>birthPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-birthPlace}
+    <t xml:space="preserve">Extension {patient-birthPlace|5.2.0}
 </t>
   </si>
   <si>
@@ -2340,7 +2343,7 @@
 </t>
   </si>
   <si>
-    <t>Comment on a dataElement | Commentaire sur un dataElement</t>
+    <t>Comment on element Patient.contact | Commentaire sur l'élément Patient.contact</t>
   </si>
   <si>
     <t>Ajout d'un commentaire sur un dataElement d'une ressource.
@@ -5686,7 +5689,7 @@
         <v>220</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5769,13 +5772,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>82</v>
@@ -5797,13 +5800,13 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5886,10 +5889,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -6001,10 +6004,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -6116,10 +6119,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6145,13 +6148,13 @@
         <v>132</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -6159,7 +6162,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>82</v>
@@ -6201,7 +6204,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>90</v>
@@ -6233,10 +6236,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6259,13 +6262,13 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -6316,7 +6319,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -6325,7 +6328,7 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>102</v>
@@ -6348,10 +6351,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6463,10 +6466,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6578,13 +6581,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="B31" t="s" s="2">
-        <v>247</v>
-      </c>
       <c r="C31" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>82</v>
@@ -6606,13 +6609,13 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6695,10 +6698,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6724,16 +6727,16 @@
         <v>172</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6746,7 +6749,7 @@
         <v>82</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>82</v>
@@ -6758,13 +6761,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -6782,7 +6785,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6797,7 +6800,7 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
@@ -6806,7 +6809,7 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6814,10 +6817,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6843,13 +6846,13 @@
         <v>172</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6863,7 +6866,7 @@
         <v>82</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>82</v>
@@ -6875,13 +6878,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6899,7 +6902,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6914,7 +6917,7 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
@@ -6923,7 +6926,7 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6931,10 +6934,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6960,16 +6963,16 @@
         <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6982,7 +6985,7 @@
         <v>82</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>82</v>
@@ -7018,7 +7021,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -7033,7 +7036,7 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
@@ -7042,7 +7045,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -7050,10 +7053,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7079,10 +7082,10 @@
         <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7097,7 +7100,7 @@
         <v>82</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>82</v>
@@ -7133,7 +7136,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -7148,7 +7151,7 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>82</v>
@@ -7157,7 +7160,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -7165,14 +7168,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -7194,10 +7197,10 @@
         <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7212,7 +7215,7 @@
         <v>82</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>82</v>
@@ -7248,7 +7251,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -7263,7 +7266,7 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
@@ -7272,7 +7275,7 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -7280,14 +7283,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -7309,13 +7312,13 @@
         <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -7329,7 +7332,7 @@
         <v>82</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>82</v>
@@ -7365,7 +7368,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -7380,7 +7383,7 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>82</v>
@@ -7389,7 +7392,7 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -7397,14 +7400,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -7426,10 +7429,10 @@
         <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7480,7 +7483,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7495,7 +7498,7 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>82</v>
@@ -7504,7 +7507,7 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7512,14 +7515,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7541,10 +7544,10 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7559,7 +7562,7 @@
         <v>82</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>82</v>
@@ -7595,7 +7598,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7610,7 +7613,7 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>82</v>
@@ -7619,7 +7622,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7627,10 +7630,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7656,13 +7659,13 @@
         <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7712,7 +7715,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7727,7 +7730,7 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
@@ -7736,7 +7739,7 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7744,10 +7747,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7770,17 +7773,17 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7793,7 +7796,7 @@
         <v>82</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>82</v>
@@ -7829,7 +7832,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7844,7 +7847,7 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
@@ -7853,7 +7856,7 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7861,13 +7864,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>82</v>
@@ -7889,13 +7892,13 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7978,10 +7981,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8007,16 +8010,16 @@
         <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -8065,7 +8068,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -8097,10 +8100,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8123,17 +8126,17 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -8170,10 +8173,10 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
@@ -8182,7 +8185,7 @@
         <v>117</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -8197,16 +8200,16 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -8214,13 +8217,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>82</v>
@@ -8242,17 +8245,17 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -8301,7 +8304,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8316,16 +8319,16 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -8333,10 +8336,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8448,10 +8451,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8565,10 +8568,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8594,16 +8597,16 @@
         <v>172</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8613,7 +8616,7 @@
         <v>82</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>82</v>
@@ -8628,13 +8631,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8652,7 +8655,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8667,7 +8670,7 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>82</v>
@@ -8684,10 +8687,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8710,19 +8713,19 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8732,7 +8735,7 @@
         <v>82</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>82</v>
@@ -8751,7 +8754,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8769,7 +8772,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8784,7 +8787,7 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
@@ -8793,7 +8796,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8801,10 +8804,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8830,16 +8833,16 @@
         <v>132</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8849,10 +8852,10 @@
         <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>82</v>
@@ -8888,7 +8891,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8903,7 +8906,7 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
@@ -8912,7 +8915,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8920,10 +8923,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8949,13 +8952,13 @@
         <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8969,7 +8972,7 @@
         <v>82</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>82</v>
@@ -9005,7 +9008,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -9020,7 +9023,7 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
@@ -9029,7 +9032,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -9037,10 +9040,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9063,13 +9066,13 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9120,7 +9123,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -9135,7 +9138,7 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
@@ -9144,7 +9147,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -9152,10 +9155,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9178,16 +9181,16 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9237,7 +9240,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -9252,7 +9255,7 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
@@ -9261,7 +9264,7 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -9269,13 +9272,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>82</v>
@@ -9297,17 +9300,17 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9356,7 +9359,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9371,16 +9374,16 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -9388,10 +9391,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9503,10 +9506,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9620,10 +9623,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9649,16 +9652,16 @@
         <v>172</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9668,7 +9671,7 @@
         <v>82</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>82</v>
@@ -9683,13 +9686,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9707,7 +9710,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9722,7 +9725,7 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
@@ -9739,10 +9742,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9765,19 +9768,19 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9787,7 +9790,7 @@
         <v>82</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>82</v>
@@ -9806,7 +9809,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9824,7 +9827,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9839,7 +9842,7 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
@@ -9848,7 +9851,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9856,10 +9859,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9885,16 +9888,16 @@
         <v>132</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9904,10 +9907,10 @@
         <v>82</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>82</v>
@@ -9943,7 +9946,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9958,7 +9961,7 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
@@ -9967,7 +9970,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9975,10 +9978,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10004,13 +10007,13 @@
         <v>104</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -10024,7 +10027,7 @@
         <v>82</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>82</v>
@@ -10060,7 +10063,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -10075,7 +10078,7 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
@@ -10084,7 +10087,7 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -10092,10 +10095,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10118,13 +10121,13 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10175,7 +10178,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -10190,7 +10193,7 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
@@ -10199,7 +10202,7 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -10207,10 +10210,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10233,16 +10236,16 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10292,7 +10295,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10307,7 +10310,7 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
@@ -10316,7 +10319,7 @@
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -10324,13 +10327,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>82</v>
@@ -10352,17 +10355,17 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10411,7 +10414,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10426,16 +10429,16 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10443,10 +10446,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10558,10 +10561,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10675,10 +10678,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10704,16 +10707,16 @@
         <v>172</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10723,7 +10726,7 @@
         <v>82</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>82</v>
@@ -10738,13 +10741,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10762,7 +10765,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10777,7 +10780,7 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>82</v>
@@ -10794,10 +10797,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10820,19 +10823,19 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10842,7 +10845,7 @@
         <v>82</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>82</v>
@@ -10861,7 +10864,7 @@
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10879,7 +10882,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10894,7 +10897,7 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>82</v>
@@ -10903,7 +10906,7 @@
         <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10911,10 +10914,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10940,16 +10943,16 @@
         <v>132</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10959,10 +10962,10 @@
         <v>82</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>82</v>
@@ -10998,7 +11001,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -11013,7 +11016,7 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
@@ -11022,7 +11025,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -11030,10 +11033,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11059,13 +11062,13 @@
         <v>104</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11079,7 +11082,7 @@
         <v>82</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>82</v>
@@ -11115,7 +11118,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -11130,7 +11133,7 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
@@ -11139,7 +11142,7 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -11147,10 +11150,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11173,13 +11176,13 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11230,7 +11233,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11245,7 +11248,7 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
@@ -11254,7 +11257,7 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -11262,10 +11265,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11288,16 +11291,16 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11347,7 +11350,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11362,7 +11365,7 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
@@ -11371,7 +11374,7 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11379,13 +11382,13 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>82</v>
@@ -11407,17 +11410,17 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11466,7 +11469,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11481,16 +11484,16 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11498,10 +11501,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11613,10 +11616,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11730,10 +11733,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11759,16 +11762,16 @@
         <v>172</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11778,7 +11781,7 @@
         <v>82</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>82</v>
@@ -11793,13 +11796,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11817,7 +11820,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11832,7 +11835,7 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>82</v>
@@ -11849,10 +11852,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11875,19 +11878,19 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11897,7 +11900,7 @@
         <v>82</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>82</v>
@@ -11916,7 +11919,7 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11934,7 +11937,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11949,7 +11952,7 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>82</v>
@@ -11958,7 +11961,7 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11966,10 +11969,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11995,16 +11998,16 @@
         <v>132</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -12017,7 +12020,7 @@
         <v>82</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>82</v>
@@ -12053,7 +12056,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -12068,7 +12071,7 @@
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>82</v>
@@ -12077,7 +12080,7 @@
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -12085,10 +12088,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12114,13 +12117,13 @@
         <v>104</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12134,7 +12137,7 @@
         <v>82</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>82</v>
@@ -12170,7 +12173,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12185,7 +12188,7 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>82</v>
@@ -12194,7 +12197,7 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -12202,10 +12205,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12228,13 +12231,13 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12285,7 +12288,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12300,7 +12303,7 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>82</v>
@@ -12309,7 +12312,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12317,10 +12320,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12343,16 +12346,16 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12402,7 +12405,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12417,7 +12420,7 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>82</v>
@@ -12426,7 +12429,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12434,13 +12437,13 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>82</v>
@@ -12462,17 +12465,17 @@
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12521,7 +12524,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12536,16 +12539,16 @@
         <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12553,10 +12556,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12668,10 +12671,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12785,10 +12788,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12814,16 +12817,16 @@
         <v>172</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12833,7 +12836,7 @@
         <v>82</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>82</v>
@@ -12848,13 +12851,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12872,7 +12875,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12887,7 +12890,7 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>82</v>
@@ -12904,10 +12907,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12930,19 +12933,19 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12952,7 +12955,7 @@
         <v>82</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>82</v>
@@ -12971,7 +12974,7 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
@@ -12989,7 +12992,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13004,7 +13007,7 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>82</v>
@@ -13013,7 +13016,7 @@
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -13021,10 +13024,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13050,16 +13053,16 @@
         <v>132</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -13072,7 +13075,7 @@
         <v>82</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>82</v>
@@ -13108,7 +13111,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13123,7 +13126,7 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>82</v>
@@ -13132,7 +13135,7 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -13140,10 +13143,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13169,13 +13172,13 @@
         <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13189,7 +13192,7 @@
         <v>82</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>82</v>
@@ -13225,7 +13228,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13240,7 +13243,7 @@
         <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>82</v>
@@ -13249,7 +13252,7 @@
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -13257,10 +13260,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13283,13 +13286,13 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13340,7 +13343,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13355,7 +13358,7 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>82</v>
@@ -13364,7 +13367,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13372,10 +13375,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13398,16 +13401,16 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13457,7 +13460,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13472,7 +13475,7 @@
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>82</v>
@@ -13481,7 +13484,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13489,13 +13492,13 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>82</v>
@@ -13517,17 +13520,17 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13576,7 +13579,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13591,16 +13594,16 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13608,10 +13611,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13723,10 +13726,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13840,10 +13843,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13869,16 +13872,16 @@
         <v>172</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13888,7 +13891,7 @@
         <v>82</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>82</v>
@@ -13903,13 +13906,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13927,7 +13930,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13942,7 +13945,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>82</v>
@@ -13959,10 +13962,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13985,19 +13988,19 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -14007,7 +14010,7 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>82</v>
@@ -14025,10 +14028,10 @@
         <v>154</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -14046,7 +14049,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14061,7 +14064,7 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>82</v>
@@ -14070,7 +14073,7 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -14078,10 +14081,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14107,16 +14110,16 @@
         <v>132</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -14126,10 +14129,10 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="T95" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="U95" t="s" s="2">
         <v>82</v>
@@ -14165,7 +14168,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14180,7 +14183,7 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>82</v>
@@ -14189,7 +14192,7 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -14197,10 +14200,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14226,13 +14229,13 @@
         <v>104</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14246,7 +14249,7 @@
         <v>82</v>
       </c>
       <c r="T96" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U96" t="s" s="2">
         <v>82</v>
@@ -14282,7 +14285,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14297,7 +14300,7 @@
         <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>82</v>
@@ -14306,7 +14309,7 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14314,10 +14317,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14340,13 +14343,13 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14397,7 +14400,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14412,7 +14415,7 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>82</v>
@@ -14421,7 +14424,7 @@
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14429,10 +14432,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14455,16 +14458,16 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14514,7 +14517,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14529,7 +14532,7 @@
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>82</v>
@@ -14538,7 +14541,7 @@
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14546,13 +14549,13 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>82</v>
@@ -14574,17 +14577,17 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14633,7 +14636,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14648,16 +14651,16 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14665,10 +14668,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14780,10 +14783,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14897,10 +14900,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14926,16 +14929,16 @@
         <v>172</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14945,7 +14948,7 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>82</v>
@@ -14960,13 +14963,13 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14984,7 +14987,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14999,7 +15002,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -15016,10 +15019,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15042,19 +15045,19 @@
         <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15064,7 +15067,7 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>82</v>
@@ -15082,10 +15085,10 @@
         <v>154</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -15103,7 +15106,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15118,7 +15121,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
@@ -15127,7 +15130,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15135,10 +15138,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15164,16 +15167,16 @@
         <v>132</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -15183,10 +15186,10 @@
         <v>82</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="T104" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="U104" t="s" s="2">
         <v>82</v>
@@ -15222,7 +15225,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15237,7 +15240,7 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>82</v>
@@ -15246,7 +15249,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15254,10 +15257,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15283,13 +15286,13 @@
         <v>104</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15303,7 +15306,7 @@
         <v>82</v>
       </c>
       <c r="T105" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U105" t="s" s="2">
         <v>82</v>
@@ -15339,7 +15342,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15354,7 +15357,7 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>82</v>
@@ -15363,7 +15366,7 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15371,10 +15374,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15397,13 +15400,13 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15454,7 +15457,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15469,7 +15472,7 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>82</v>
@@ -15478,7 +15481,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15486,10 +15489,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15512,16 +15515,16 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15571,7 +15574,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15586,7 +15589,7 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>82</v>
@@ -15595,7 +15598,7 @@
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15603,13 +15606,13 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>82</v>
@@ -15631,17 +15634,17 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15690,7 +15693,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15705,16 +15708,16 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15722,10 +15725,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15837,10 +15840,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15954,10 +15957,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15983,16 +15986,16 @@
         <v>172</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -16002,7 +16005,7 @@
         <v>82</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>82</v>
@@ -16017,13 +16020,13 @@
         <v>82</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -16041,7 +16044,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16056,7 +16059,7 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
@@ -16073,10 +16076,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16099,19 +16102,19 @@
         <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -16121,7 +16124,7 @@
         <v>82</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>82</v>
@@ -16139,10 +16142,10 @@
         <v>154</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -16160,7 +16163,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16175,7 +16178,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>82</v>
@@ -16184,7 +16187,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16192,10 +16195,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16221,16 +16224,16 @@
         <v>132</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16240,10 +16243,10 @@
         <v>82</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="T113" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="U113" t="s" s="2">
         <v>82</v>
@@ -16279,7 +16282,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16294,7 +16297,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>82</v>
@@ -16303,7 +16306,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16311,10 +16314,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16340,13 +16343,13 @@
         <v>104</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16360,7 +16363,7 @@
         <v>82</v>
       </c>
       <c r="T114" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U114" t="s" s="2">
         <v>82</v>
@@ -16396,7 +16399,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16411,7 +16414,7 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>82</v>
@@ -16420,7 +16423,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16428,10 +16431,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16454,13 +16457,13 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16511,7 +16514,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16526,7 +16529,7 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>82</v>
@@ -16535,7 +16538,7 @@
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16543,10 +16546,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16569,16 +16572,16 @@
         <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16628,7 +16631,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16643,7 +16646,7 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>82</v>
@@ -16652,7 +16655,7 @@
         <v>82</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
@@ -16660,13 +16663,13 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>82</v>
@@ -16688,17 +16691,17 @@
         <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16747,7 +16750,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16762,16 +16765,16 @@
         <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
@@ -16779,10 +16782,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16894,10 +16897,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17011,10 +17014,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17040,16 +17043,16 @@
         <v>172</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -17059,7 +17062,7 @@
         <v>82</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>82</v>
@@ -17074,13 +17077,13 @@
         <v>82</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>82</v>
@@ -17098,7 +17101,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17113,7 +17116,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>82</v>
@@ -17130,10 +17133,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17156,19 +17159,19 @@
         <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -17178,7 +17181,7 @@
         <v>82</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>82</v>
@@ -17196,10 +17199,10 @@
         <v>154</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -17217,7 +17220,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17232,7 +17235,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>82</v>
@@ -17241,7 +17244,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -17249,10 +17252,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17278,16 +17281,16 @@
         <v>132</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -17297,10 +17300,10 @@
         <v>82</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="T122" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="U122" t="s" s="2">
         <v>82</v>
@@ -17336,7 +17339,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17351,7 +17354,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>82</v>
@@ -17360,7 +17363,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -17368,10 +17371,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17397,13 +17400,13 @@
         <v>104</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17417,7 +17420,7 @@
         <v>82</v>
       </c>
       <c r="T123" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U123" t="s" s="2">
         <v>82</v>
@@ -17453,7 +17456,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17468,7 +17471,7 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>82</v>
@@ -17477,7 +17480,7 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -17485,10 +17488,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17511,13 +17514,13 @@
         <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17568,7 +17571,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17583,7 +17586,7 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>82</v>
@@ -17592,7 +17595,7 @@
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17600,10 +17603,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17626,16 +17629,16 @@
         <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17685,7 +17688,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17700,7 +17703,7 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>82</v>
@@ -17709,7 +17712,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17717,10 +17720,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17743,70 +17746,70 @@
         <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q126" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="R126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF126" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q126" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="R126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17821,13 +17824,13 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>82</v>
@@ -17838,10 +17841,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17864,19 +17867,19 @@
         <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17913,7 +17916,7 @@
         <v>82</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AC127" s="2"/>
       <c r="AD127" t="s" s="2">
@@ -17923,7 +17926,7 @@
         <v>117</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17938,16 +17941,16 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17955,13 +17958,13 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>82</v>
@@ -17983,19 +17986,19 @@
         <v>91</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -18044,7 +18047,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18059,16 +18062,16 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -18076,10 +18079,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18191,10 +18194,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18308,10 +18311,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18337,16 +18340,16 @@
         <v>172</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
@@ -18356,7 +18359,7 @@
         <v>82</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>82</v>
@@ -18371,13 +18374,13 @@
         <v>82</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -18395,7 +18398,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18410,7 +18413,7 @@
         <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>82</v>
@@ -18419,7 +18422,7 @@
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -18427,10 +18430,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18456,16 +18459,16 @@
         <v>104</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>82</v>
@@ -18514,7 +18517,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18529,7 +18532,7 @@
         <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>82</v>
@@ -18538,7 +18541,7 @@
         <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -18546,14 +18549,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18575,13 +18578,13 @@
         <v>104</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18631,7 +18634,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18646,7 +18649,7 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>82</v>
@@ -18655,7 +18658,7 @@
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18663,14 +18666,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -18692,13 +18695,13 @@
         <v>104</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18748,7 +18751,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18763,7 +18766,7 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>82</v>
@@ -18772,7 +18775,7 @@
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18780,10 +18783,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18809,10 +18812,10 @@
         <v>104</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18863,7 +18866,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18878,7 +18881,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>82</v>
@@ -18887,7 +18890,7 @@
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18895,10 +18898,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18924,10 +18927,10 @@
         <v>104</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18978,7 +18981,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18993,7 +18996,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>82</v>
@@ -19002,7 +19005,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -19010,10 +19013,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19036,17 +19039,17 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -19095,7 +19098,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19110,7 +19113,7 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>82</v>
@@ -19119,7 +19122,7 @@
         <v>82</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>82</v>
@@ -19127,13 +19130,13 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>82</v>
@@ -19155,19 +19158,19 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -19216,7 +19219,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19231,16 +19234,16 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
@@ -19248,10 +19251,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19363,10 +19366,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19478,13 +19481,13 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>82</v>
@@ -19506,13 +19509,13 @@
         <v>82</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19595,10 +19598,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19624,16 +19627,16 @@
         <v>172</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -19643,7 +19646,7 @@
         <v>82</v>
       </c>
       <c r="S142" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="T142" t="s" s="2">
         <v>82</v>
@@ -19658,13 +19661,13 @@
         <v>82</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -19682,7 +19685,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19697,7 +19700,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>82</v>
@@ -19706,7 +19709,7 @@
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19714,10 +19717,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19743,16 +19746,16 @@
         <v>104</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -19801,7 +19804,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19816,7 +19819,7 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>82</v>
@@ -19825,7 +19828,7 @@
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>82</v>
@@ -19833,14 +19836,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -19862,13 +19865,13 @@
         <v>104</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19918,7 +19921,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19933,7 +19936,7 @@
         <v>102</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>82</v>
@@ -19942,7 +19945,7 @@
         <v>82</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>82</v>
@@ -19950,14 +19953,14 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -19979,13 +19982,13 @@
         <v>104</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -20035,7 +20038,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20050,7 +20053,7 @@
         <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>82</v>
@@ -20059,7 +20062,7 @@
         <v>82</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>82</v>
@@ -20067,10 +20070,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20096,10 +20099,10 @@
         <v>104</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20150,7 +20153,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20165,7 +20168,7 @@
         <v>102</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>82</v>
@@ -20174,7 +20177,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -20182,10 +20185,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20211,10 +20214,10 @@
         <v>104</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -20265,7 +20268,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20280,7 +20283,7 @@
         <v>102</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>82</v>
@@ -20289,7 +20292,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
@@ -20297,10 +20300,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20323,17 +20326,17 @@
         <v>91</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -20382,7 +20385,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20397,7 +20400,7 @@
         <v>102</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>82</v>
@@ -20406,7 +20409,7 @@
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -20414,10 +20417,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20440,19 +20443,19 @@
         <v>91</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -20501,7 +20504,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20516,16 +20519,16 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -20533,10 +20536,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20562,16 +20565,16 @@
         <v>172</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>82</v>
@@ -20596,11 +20599,11 @@
         <v>82</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>82</v>
@@ -20618,7 +20621,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20633,16 +20636,16 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>82</v>
@@ -20650,10 +20653,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20676,19 +20679,19 @@
         <v>91</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -20737,7 +20740,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20752,27 +20755,27 @@
         <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20795,19 +20798,19 @@
         <v>91</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -20856,7 +20859,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20871,7 +20874,7 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>108</v>
@@ -20880,7 +20883,7 @@
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -20888,10 +20891,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20914,19 +20917,19 @@
         <v>91</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>82</v>
@@ -20975,7 +20978,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20990,16 +20993,16 @@
         <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -21007,10 +21010,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21033,17 +21036,17 @@
         <v>82</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
@@ -21072,7 +21075,7 @@
       </c>
       <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>82</v>
@@ -21090,7 +21093,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21105,16 +21108,16 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -21122,10 +21125,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21148,19 +21151,19 @@
         <v>82</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -21209,7 +21212,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21224,7 +21227,7 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>108</v>
@@ -21233,7 +21236,7 @@
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -21241,10 +21244,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21267,19 +21270,19 @@
         <v>82</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -21328,7 +21331,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21343,7 +21346,7 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>108</v>
@@ -21352,7 +21355,7 @@
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>82</v>
@@ -21360,10 +21363,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21386,19 +21389,19 @@
         <v>82</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>82</v>
@@ -21447,7 +21450,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21459,10 +21462,10 @@
         <v>82</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AL157" t="s" s="2">
         <v>108</v>
@@ -21479,10 +21482,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21594,10 +21597,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21707,13 +21710,13 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="B160" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="B160" t="s" s="2">
-        <v>724</v>
-      </c>
       <c r="C160" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>82</v>
@@ -21735,13 +21738,13 @@
         <v>82</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21824,13 +21827,13 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>82</v>
@@ -21852,13 +21855,13 @@
         <v>82</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -21941,14 +21944,14 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -21970,16 +21973,16 @@
         <v>111</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="N162" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>82</v>
@@ -22028,7 +22031,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -22060,10 +22063,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22086,17 +22089,17 @@
         <v>82</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22124,10 +22127,10 @@
         <v>154</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -22143,7 +22146,7 @@
         <v>117</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22158,7 +22161,7 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>108</v>
@@ -22167,7 +22170,7 @@
         <v>82</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -22175,13 +22178,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>82</v>
@@ -22203,17 +22206,17 @@
         <v>82</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
@@ -22242,7 +22245,7 @@
       </c>
       <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>82</v>
@@ -22260,7 +22263,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22275,7 +22278,7 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>108</v>
@@ -22284,7 +22287,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -22292,13 +22295,13 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>82</v>
@@ -22320,17 +22323,17 @@
         <v>82</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>82</v>
@@ -22359,7 +22362,7 @@
       </c>
       <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -22377,7 +22380,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22392,7 +22395,7 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>108</v>
@@ -22401,7 +22404,7 @@
         <v>82</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -22409,10 +22412,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22435,17 +22438,17 @@
         <v>82</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -22494,7 +22497,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22509,7 +22512,7 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>108</v>
@@ -22518,7 +22521,7 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -22526,10 +22529,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22552,19 +22555,19 @@
         <v>82</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>82</v>
@@ -22613,7 +22616,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22628,7 +22631,7 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>108</v>
@@ -22637,7 +22640,7 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -22645,10 +22648,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22671,17 +22674,17 @@
         <v>82</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -22730,7 +22733,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22745,7 +22748,7 @@
         <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>108</v>
@@ -22754,7 +22757,7 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -22762,10 +22765,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22791,14 +22794,14 @@
         <v>172</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>82</v>
@@ -22823,13 +22826,13 @@
         <v>82</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>82</v>
@@ -22847,7 +22850,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22862,7 +22865,7 @@
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>108</v>
@@ -22871,7 +22874,7 @@
         <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
@@ -22879,10 +22882,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22905,17 +22908,17 @@
         <v>82</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>82</v>
@@ -22964,7 +22967,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22973,13 +22976,13 @@
         <v>90</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>108</v>
@@ -22988,7 +22991,7 @@
         <v>82</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>82</v>
@@ -22996,10 +22999,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23022,13 +23025,13 @@
         <v>82</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -23079,7 +23082,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -23094,7 +23097,7 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>108</v>
@@ -23111,10 +23114,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23137,19 +23140,19 @@
         <v>82</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>82</v>
@@ -23198,7 +23201,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23213,10 +23216,10 @@
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>82</v>
@@ -23230,10 +23233,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23345,10 +23348,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23462,14 +23465,14 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -23491,16 +23494,16 @@
         <v>111</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="N175" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -23549,7 +23552,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23581,10 +23584,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23607,19 +23610,19 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>82</v>
@@ -23668,7 +23671,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>90</v>
@@ -23683,16 +23686,16 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AM176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>82</v>
@@ -23700,10 +23703,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23726,19 +23729,19 @@
         <v>82</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>82</v>
@@ -23787,7 +23790,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23802,16 +23805,16 @@
         <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>82</v>
@@ -23819,14 +23822,14 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
@@ -23845,16 +23848,16 @@
         <v>82</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23904,7 +23907,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23919,7 +23922,7 @@
         <v>102</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>108</v>
@@ -23928,7 +23931,7 @@
         <v>82</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>82</v>
@@ -23936,10 +23939,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23962,19 +23965,19 @@
         <v>91</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>82</v>
@@ -24023,7 +24026,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24038,10 +24041,10 @@
         <v>102</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>82</v>
@@ -24055,10 +24058,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24081,19 +24084,19 @@
         <v>91</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -24142,7 +24145,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -24157,7 +24160,7 @@
         <v>102</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AL180" t="s" s="2">
         <v>108</v>
@@ -24174,10 +24177,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24289,10 +24292,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24406,14 +24409,14 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -24435,16 +24438,16 @@
         <v>111</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24493,7 +24496,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24525,10 +24528,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24551,16 +24554,16 @@
         <v>91</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -24610,7 +24613,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>90</v>
@@ -24625,7 +24628,7 @@
         <v>102</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL184" t="s" s="2">
         <v>108</v>
@@ -24634,7 +24637,7 @@
         <v>82</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>82</v>
@@ -24642,10 +24645,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24671,10 +24674,10 @@
         <v>172</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -24701,13 +24704,13 @@
         <v>82</v>
       </c>
       <c r="X185" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>82</v>
@@ -24725,7 +24728,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>90</v>
@@ -24740,7 +24743,7 @@
         <v>102</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AL185" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil Fr Core Patient surspécifié pour être conforme aux exigences du référentiel d'Identité Nationale de Santé (INS). Les identifiants INS-NIR ne peuvent être véhiculés uniquement dans le cas d'un patient qualifié, raison pour laquelle les slices identifier sont définies au niveau du FrCorePatientINS et non au niveau du FrCorePatient.</t>
+    <t>Profil Fr Core Patient surspécifié pour être conforme aux exigences du référentiel d'Identité Nationale de Santé (INS).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6902" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6901" uniqueCount="854">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil Fr Core Patient surspécifié pour être conforme aux exigences du référentiel d'Identité Nationale de Santé (INS).</t>
+    <t>Profil Fr Core Patient surspécifié pour être conforme aux exigences du référentiel d'Identité Nationale de Santé (INS). Le matricule INS ne peut être véhiculé que dans le cas d'une identité qualifiée, raison pour laquelle les slices identifier sont définies au niveau du FRCorePatientINS et non au niveau du FRCorePatient.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1122,7 +1122,7 @@
     <t>Rang Gémellaire</t>
   </si>
   <si>
-    <t>Extension crée pour exprimer le rang gémellaire, notamment utle dans le cadre des attestations de droits à l'assurance maladie. Cette extension implemente l'élément PatientMultipleBirth de R5 https://www.hl7.org/fhir/patient-definitions.html#Patient.multipleBirth_x.</t>
+    <t>Extension créée pour exprimer le rang gémellaire, notamment utile dans le cadre des attestations de droits à l'assurance maladie. Cette extension implemente l'élément PatientMultipleBirth de R5 https://www.hl7.org/fhir/patient-definitions.html#Patient.multipleBirth_x.</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -1148,7 +1148,7 @@
 </t>
   </si>
   <si>
-    <t>An identifier for this patient | Identifiant patient. Pour modéliser un patient avec une INS validée, il est nécessaire de respecter la conformité au profil FrCorePatientINS. Les identifiants NIR et NIA ne sont définis uniquement dans le cas du FRCorePatientINS.</t>
+    <t>An identifier for this patient | Identifiant patient. Pour modéliser un patient avec une INS au statut qualifié, il est nécessaire de respecter la conformité au profil FRCorePatientINS. Les identifiants NIR et NIA ne sont définis que dans le cas du FRCorePatientINS.</t>
   </si>
   <si>
     <t>An identifier for this patient.</t>
@@ -1161,7 +1161,7 @@
 </t>
   </si>
   <si>
-    <t>slicing de l'identifiant Patient sur le type d'identifiant (IPP, INS-NIR, INS-NIA, etc.)</t>
+    <t>Slicing de l'identifiant Patient sur le type d'identifiant (IPP, INS-NIR, INS-NIA, etc.)</t>
   </si>
   <si>
     <t>id</t>
@@ -1477,7 +1477,7 @@
     <t>PI</t>
   </si>
   <si>
-    <t>Hospital assigned patient identifier | IPP</t>
+    <t>Hospital assigned patient identifier | Identifiant Patient Permanent (IPP).</t>
   </si>
   <si>
     <t>Patient.identifier:PI.id</t>
@@ -1489,7 +1489,10 @@
     <t>Patient.identifier:PI.use</t>
   </si>
   <si>
-    <t>usual</t>
+    <t>La valeur old permet d'identifier des IPP désactivés (en cas de fusion d'identité pour résoudre des problèmes de doublonnage par exemple)</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-use</t>
   </si>
   <si>
     <t>Patient.identifier:PI.type</t>
@@ -1859,6 +1862,9 @@
   </si>
   <si>
     <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>usual</t>
   </si>
   <si>
     <t>The use of a human name.</t>
@@ -3063,7 +3069,7 @@
     <col min="26" max="26" width="53.21484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="64.48046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="64.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -11768,7 +11774,7 @@
         <v>380</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>381</v>
+        <v>468</v>
       </c>
       <c r="O75" t="s" s="2">
         <v>382</v>
@@ -11781,7 +11787,7 @@
         <v>82</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>468</v>
+        <v>82</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>82</v>
@@ -11798,11 +11804,9 @@
       <c r="X75" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="Y75" t="s" s="2">
-        <v>384</v>
-      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>385</v>
+        <v>469</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11852,7 +11856,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>389</v>
@@ -11900,7 +11904,7 @@
         <v>82</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>82</v>
@@ -11969,7 +11973,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>400</v>
@@ -12088,7 +12092,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>411</v>
@@ -12205,7 +12209,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>420</v>
@@ -12320,7 +12324,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>427</v>
@@ -12437,13 +12441,13 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>359</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>82</v>
@@ -12468,7 +12472,7 @@
         <v>360</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M81" t="s" s="2">
         <v>362</v>
@@ -12556,7 +12560,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>374</v>
@@ -12671,7 +12675,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>376</v>
@@ -12788,7 +12792,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>378</v>
@@ -12907,7 +12911,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>389</v>
@@ -12955,7 +12959,7 @@
         <v>82</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>82</v>
@@ -13024,7 +13028,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>400</v>
@@ -13143,7 +13147,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>411</v>
@@ -13260,7 +13264,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>420</v>
@@ -13375,7 +13379,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>427</v>
@@ -13492,13 +13496,13 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>359</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>82</v>
@@ -13523,7 +13527,7 @@
         <v>360</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M90" t="s" s="2">
         <v>362</v>
@@ -13611,7 +13615,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>374</v>
@@ -13726,7 +13730,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>376</v>
@@ -13843,7 +13847,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>378</v>
@@ -13962,7 +13966,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>389</v>
@@ -14010,7 +14014,7 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>82</v>
@@ -14028,10 +14032,10 @@
         <v>154</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -14081,7 +14085,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>400</v>
@@ -14110,7 +14114,7 @@
         <v>132</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M95" t="s" s="2">
         <v>402</v>
@@ -14200,7 +14204,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>411</v>
@@ -14317,7 +14321,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>420</v>
@@ -14432,7 +14436,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>427</v>
@@ -14549,13 +14553,13 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>359</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>82</v>
@@ -14580,7 +14584,7 @@
         <v>360</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M99" t="s" s="2">
         <v>362</v>
@@ -14668,7 +14672,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>374</v>
@@ -14783,7 +14787,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>376</v>
@@ -14900,7 +14904,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>378</v>
@@ -15019,7 +15023,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>389</v>
@@ -15067,7 +15071,7 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>82</v>
@@ -15085,10 +15089,10 @@
         <v>154</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -15138,7 +15142,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>400</v>
@@ -15167,7 +15171,7 @@
         <v>132</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M104" t="s" s="2">
         <v>402</v>
@@ -15186,7 +15190,7 @@
         <v>82</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>406</v>
@@ -15257,7 +15261,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>411</v>
@@ -15374,7 +15378,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>420</v>
@@ -15489,7 +15493,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>427</v>
@@ -15606,13 +15610,13 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>359</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>82</v>
@@ -15637,7 +15641,7 @@
         <v>360</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>362</v>
@@ -15725,7 +15729,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>374</v>
@@ -15840,7 +15844,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>376</v>
@@ -15957,7 +15961,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>378</v>
@@ -16076,7 +16080,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>389</v>
@@ -16124,7 +16128,7 @@
         <v>82</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>82</v>
@@ -16142,10 +16146,10 @@
         <v>154</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -16195,7 +16199,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>400</v>
@@ -16224,7 +16228,7 @@
         <v>132</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M113" t="s" s="2">
         <v>402</v>
@@ -16243,7 +16247,7 @@
         <v>82</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>406</v>
@@ -16314,7 +16318,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>411</v>
@@ -16431,7 +16435,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>420</v>
@@ -16546,7 +16550,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>427</v>
@@ -16663,13 +16667,13 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>359</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>82</v>
@@ -16694,7 +16698,7 @@
         <v>360</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M117" t="s" s="2">
         <v>362</v>
@@ -16782,7 +16786,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>374</v>
@@ -16897,7 +16901,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>376</v>
@@ -17014,7 +17018,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>378</v>
@@ -17062,7 +17066,7 @@
         <v>82</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>82</v>
@@ -17133,7 +17137,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>389</v>
@@ -17181,7 +17185,7 @@
         <v>82</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>82</v>
@@ -17199,10 +17203,10 @@
         <v>154</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -17252,7 +17256,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>400</v>
@@ -17281,7 +17285,7 @@
         <v>132</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M122" t="s" s="2">
         <v>402</v>
@@ -17300,7 +17304,7 @@
         <v>82</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>406</v>
@@ -17371,7 +17375,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>411</v>
@@ -17488,7 +17492,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>420</v>
@@ -17603,7 +17607,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>427</v>
@@ -17720,10 +17724,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17746,70 +17750,70 @@
         <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q126" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="R126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF126" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q126" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="R126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17824,13 +17828,13 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>82</v>
@@ -17841,10 +17845,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17867,19 +17871,19 @@
         <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17916,7 +17920,7 @@
         <v>82</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AC127" s="2"/>
       <c r="AD127" t="s" s="2">
@@ -17926,7 +17930,7 @@
         <v>117</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17941,16 +17945,16 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17958,13 +17962,13 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>82</v>
@@ -17986,19 +17990,19 @@
         <v>91</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -18047,7 +18051,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18062,16 +18066,16 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -18079,10 +18083,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18194,10 +18198,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18311,10 +18315,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18340,16 +18344,16 @@
         <v>172</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
@@ -18359,7 +18363,7 @@
         <v>82</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>468</v>
+        <v>580</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>82</v>
@@ -18377,10 +18381,10 @@
         <v>261</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -18398,7 +18402,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18422,7 +18426,7 @@
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -18430,10 +18434,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18459,13 +18463,13 @@
         <v>104</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="O132" t="s" s="2">
         <v>282</v>
@@ -18517,7 +18521,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18541,7 +18545,7 @@
         <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -18549,14 +18553,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18578,13 +18582,13 @@
         <v>104</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18634,7 +18638,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18649,7 +18653,7 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>82</v>
@@ -18658,7 +18662,7 @@
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18666,14 +18670,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -18695,13 +18699,13 @@
         <v>104</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18751,7 +18755,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18766,7 +18770,7 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>82</v>
@@ -18775,7 +18779,7 @@
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18783,10 +18787,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18812,10 +18816,10 @@
         <v>104</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18866,7 +18870,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18881,7 +18885,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>82</v>
@@ -18890,7 +18894,7 @@
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18898,10 +18902,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18927,10 +18931,10 @@
         <v>104</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18981,7 +18985,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18996,7 +19000,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>82</v>
@@ -19005,7 +19009,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -19013,10 +19017,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19042,14 +19046,14 @@
         <v>341</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -19098,7 +19102,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19122,7 +19126,7 @@
         <v>82</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>82</v>
@@ -19130,13 +19134,13 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>82</v>
@@ -19158,19 +19162,19 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -19219,7 +19223,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19234,16 +19238,16 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
@@ -19251,10 +19255,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19366,10 +19370,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19481,13 +19485,13 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>82</v>
@@ -19509,13 +19513,13 @@
         <v>82</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19598,10 +19602,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19627,16 +19631,16 @@
         <v>172</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -19664,10 +19668,10 @@
         <v>261</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -19685,7 +19689,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19709,7 +19713,7 @@
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19717,10 +19721,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19746,13 +19750,13 @@
         <v>104</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="O143" t="s" s="2">
         <v>282</v>
@@ -19804,7 +19808,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19828,7 +19832,7 @@
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>82</v>
@@ -19836,14 +19840,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -19865,13 +19869,13 @@
         <v>104</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19921,7 +19925,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19936,7 +19940,7 @@
         <v>102</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>82</v>
@@ -19945,7 +19949,7 @@
         <v>82</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>82</v>
@@ -19953,14 +19957,14 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -19982,13 +19986,13 @@
         <v>104</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -20038,7 +20042,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20053,7 +20057,7 @@
         <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>82</v>
@@ -20062,7 +20066,7 @@
         <v>82</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>82</v>
@@ -20070,10 +20074,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20099,10 +20103,10 @@
         <v>104</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20153,7 +20157,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20168,7 +20172,7 @@
         <v>102</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>82</v>
@@ -20177,7 +20181,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -20185,10 +20189,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20214,10 +20218,10 @@
         <v>104</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -20268,7 +20272,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20283,7 +20287,7 @@
         <v>102</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>82</v>
@@ -20292,7 +20296,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
@@ -20300,10 +20304,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20329,14 +20333,14 @@
         <v>341</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -20385,7 +20389,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20409,7 +20413,7 @@
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -20417,10 +20421,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20443,19 +20447,19 @@
         <v>91</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -20504,7 +20508,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20519,16 +20523,16 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -20536,10 +20540,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20565,16 +20569,16 @@
         <v>172</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>82</v>
@@ -20603,7 +20607,7 @@
       </c>
       <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>82</v>
@@ -20621,7 +20625,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20636,16 +20640,16 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>82</v>
@@ -20653,10 +20657,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20679,19 +20683,19 @@
         <v>91</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -20740,7 +20744,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20755,27 +20759,27 @@
         <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20798,19 +20802,19 @@
         <v>91</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -20859,7 +20863,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20874,7 +20878,7 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>108</v>
@@ -20883,7 +20887,7 @@
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -20891,10 +20895,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20920,16 +20924,16 @@
         <v>240</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>82</v>
@@ -20978,7 +20982,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20993,16 +20997,16 @@
         <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -21010,10 +21014,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21039,14 +21043,14 @@
         <v>390</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
@@ -21075,7 +21079,7 @@
       </c>
       <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>82</v>
@@ -21093,7 +21097,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21108,16 +21112,16 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -21125,10 +21129,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21151,19 +21155,19 @@
         <v>82</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -21212,7 +21216,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21227,7 +21231,7 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>108</v>
@@ -21236,7 +21240,7 @@
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -21244,10 +21248,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21270,19 +21274,19 @@
         <v>82</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -21331,7 +21335,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21346,7 +21350,7 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>108</v>
@@ -21355,7 +21359,7 @@
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>82</v>
@@ -21363,10 +21367,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21389,19 +21393,19 @@
         <v>82</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>82</v>
@@ -21450,7 +21454,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21462,10 +21466,10 @@
         <v>82</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="AL157" t="s" s="2">
         <v>108</v>
@@ -21482,10 +21486,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21597,10 +21601,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21710,13 +21714,13 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>82</v>
@@ -21738,13 +21742,13 @@
         <v>82</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21827,13 +21831,13 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>82</v>
@@ -21855,13 +21859,13 @@
         <v>82</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -21944,14 +21948,14 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -21973,10 +21977,10 @@
         <v>111</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="N162" t="s" s="2">
         <v>114</v>
@@ -22031,7 +22035,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -22063,10 +22067,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22092,14 +22096,14 @@
         <v>390</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22127,10 +22131,10 @@
         <v>154</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -22146,7 +22150,7 @@
         <v>117</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22161,7 +22165,7 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>108</v>
@@ -22170,7 +22174,7 @@
         <v>82</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -22178,13 +22182,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>82</v>
@@ -22209,14 +22213,14 @@
         <v>390</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
@@ -22245,7 +22249,7 @@
       </c>
       <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>82</v>
@@ -22263,7 +22267,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22278,7 +22282,7 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>108</v>
@@ -22287,7 +22291,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -22295,13 +22299,13 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>82</v>
@@ -22326,14 +22330,14 @@
         <v>390</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>82</v>
@@ -22362,7 +22366,7 @@
       </c>
       <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -22380,7 +22384,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22395,7 +22399,7 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>108</v>
@@ -22404,7 +22408,7 @@
         <v>82</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -22412,10 +22416,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22438,17 +22442,17 @@
         <v>82</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -22497,7 +22501,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22512,7 +22516,7 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>108</v>
@@ -22521,7 +22525,7 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -22529,10 +22533,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22555,19 +22559,19 @@
         <v>82</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>82</v>
@@ -22616,7 +22620,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22631,7 +22635,7 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>108</v>
@@ -22640,7 +22644,7 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -22648,10 +22652,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22674,17 +22678,17 @@
         <v>82</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -22733,7 +22737,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22748,7 +22752,7 @@
         <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>108</v>
@@ -22757,7 +22761,7 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -22765,10 +22769,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22794,14 +22798,14 @@
         <v>172</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>82</v>
@@ -22829,10 +22833,10 @@
         <v>261</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>82</v>
@@ -22850,7 +22854,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22865,7 +22869,7 @@
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>108</v>
@@ -22874,7 +22878,7 @@
         <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
@@ -22882,10 +22886,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22911,14 +22915,14 @@
         <v>428</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>82</v>
@@ -22967,7 +22971,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22976,13 +22980,13 @@
         <v>90</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>108</v>
@@ -22991,7 +22995,7 @@
         <v>82</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>82</v>
@@ -22999,10 +23003,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23028,10 +23032,10 @@
         <v>341</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -23082,7 +23086,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -23097,7 +23101,7 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>108</v>
@@ -23114,10 +23118,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23140,19 +23144,19 @@
         <v>82</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>82</v>
@@ -23201,7 +23205,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23216,10 +23220,10 @@
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>82</v>
@@ -23233,10 +23237,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23348,10 +23352,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23465,14 +23469,14 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -23494,10 +23498,10 @@
         <v>111</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="N175" t="s" s="2">
         <v>114</v>
@@ -23552,7 +23556,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23584,10 +23588,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23613,16 +23617,16 @@
         <v>390</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>82</v>
@@ -23671,7 +23675,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>90</v>
@@ -23686,16 +23690,16 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AM176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>82</v>
@@ -23703,10 +23707,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23729,19 +23733,19 @@
         <v>82</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>82</v>
@@ -23790,7 +23794,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23805,16 +23809,16 @@
         <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>82</v>
@@ -23822,14 +23826,14 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
@@ -23848,16 +23852,16 @@
         <v>82</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23907,7 +23911,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23922,7 +23926,7 @@
         <v>102</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>108</v>
@@ -23931,7 +23935,7 @@
         <v>82</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>82</v>
@@ -23939,10 +23943,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23965,19 +23969,19 @@
         <v>91</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>82</v>
@@ -24026,7 +24030,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24041,10 +24045,10 @@
         <v>102</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>82</v>
@@ -24058,10 +24062,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24084,19 +24088,19 @@
         <v>91</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -24145,7 +24149,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -24160,7 +24164,7 @@
         <v>102</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="AL180" t="s" s="2">
         <v>108</v>
@@ -24177,10 +24181,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24292,10 +24296,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24409,14 +24413,14 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -24438,10 +24442,10 @@
         <v>111</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>114</v>
@@ -24496,7 +24500,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24528,10 +24532,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24554,16 +24558,16 @@
         <v>91</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -24613,7 +24617,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>90</v>
@@ -24637,7 +24641,7 @@
         <v>82</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>82</v>
@@ -24645,10 +24649,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24674,10 +24678,10 @@
         <v>172</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -24707,28 +24711,28 @@
         <v>261</v>
       </c>
       <c r="Y185" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="Z185" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="AA185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF185" t="s" s="2">
         <v>849</v>
-      </c>
-      <c r="Z185" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="AA185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF185" t="s" s="2">
-        <v>847</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>90</v>
@@ -24743,7 +24747,7 @@
         <v>102</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="AL185" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2259,7 +2259,7 @@
     <t>male | female | unknown</t>
   </si>
   <si>
-    <t>French patient's gender checked with the INSi teleservice | Genre du patient. Dans le cas d'une identité récupérée par le téléservice INSi, les valeurs sont M ou F</t>
+    <t>French patient's gender checked with the INSi teleservice | Genre administratif du patient. Dans le cas d'une identité récupérée par le téléservice INSi, les valeurs M ou F issues du téléservice sont à adapter à FHIR (male | female | unknown).</t>
   </si>
   <si>
     <t>The gender might not match the biological sex as determined by genetics or the individual's preferred identification. Note that for both humans and particularly animals, there are other legitimate possibilities than male and female, though the vast majority of systems and contexts only support male and female.  Systems providing decision support or enforcing business rules should ideally do this on the basis of Observations dealing with the specific sex or gender aspect of interest (anatomical, chromosomal, social, etc.)  However, because these observations are infrequently recorded, defaulting to the administrative gender is common practice.  Where such defaulting occurs, rule enforcement should allow for the variation between administrative and biological, chromosomal and other gender aspects.  For example, an alert about a hysterectomy on a male should be handled as a warning or overridable error, not a "hard" error.  See the Patient Gender and Sex section for additional information about communicating patient gender and sex.</t>
@@ -2268,7 +2268,7 @@
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-gender-INS</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-gender</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/administrativeGender</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -878,10 +878,10 @@
 Carries the death place of the patient</t>
   </si>
   <si>
-    <t>Patient.extension:birthdateUpdateIndicator</t>
-  </si>
-  <si>
-    <t>birthdateUpdateIndicator</t>
+    <t>Patient.extension:birthDateUpdateIndicator</t>
+  </si>
+  <si>
+    <t>birthDateUpdateIndicator</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birthdate-update-indicator}
@@ -2541,10 +2541,10 @@
     <t>NK1-7, NK1-3</t>
   </si>
   <si>
-    <t>Patient.contact.relationship:Role</t>
-  </si>
-  <si>
-    <t>Role</t>
+    <t>Patient.contact.relationship:role</t>
+  </si>
+  <si>
+    <t>role</t>
   </si>
   <si>
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
@@ -2553,10 +2553,10 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
   </si>
   <si>
-    <t>Patient.contact.relationship:RelationType</t>
-  </si>
-  <si>
-    <t>RelationType</t>
+    <t>Patient.contact.relationship:relationType</t>
+  </si>
+  <si>
+    <t>relationType</t>
   </si>
   <si>
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
@@ -2778,7 +2778,7 @@
     <t>Patient.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|Organization)
 </t>
   </si>
   <si>
@@ -3187,7 +3187,7 @@
   <cols>
     <col min="1" max="1" width="59.65625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.83984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.76953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="20.984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -280,7 +280,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST] or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11' and use = 'official').exists())}fr-core-2:If identityReliability status = 'VALI', then only one identifier of type official SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(use = 'official').count() = 1)}fr-core-3:If identityReliability status = 'VALI', then the municipality of birth COG code cannot be 99999 because this code cannot be sent by the INSI online service. {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies extension('http://hl7.org/fhir/StructureDefinition/patient-birthPlace').value.extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address-insee-code').value.code != '99999')}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST] or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8' and use = 'official' and type.coding.exists(code = 'INS-NIR')).exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11' and use = 'official').exists())}fr-core-2:If identityReliability status = 'VALI', then only one identifier of type official SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(use = 'official').count() = 1)}fr-core-3:If identityReliability status = 'VALI', then the municipality of birth COG code cannot be 99999 because this code cannot be sent by the INSI online service. {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies extension('http://hl7.org/fhir/StructureDefinition/patient-birthPlace').value.extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address-insee-code').value.code != '99999'}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$231</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7915" uniqueCount="900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8573" uniqueCount="947">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2530,6 +2530,10 @@
     <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
   </si>
   <si>
+    <t xml:space="preserve">value:extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-relationship-category').value}
+</t>
+  </si>
+  <si>
     <t>code</t>
   </si>
   <si>
@@ -2548,6 +2552,118 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role|2.2.0</t>
   </si>
   <si>
+    <t>Patient.contact.relationship:role.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-relationship-category|2.2.0}
+</t>
+  </si>
+  <si>
+    <t>FR Core Patient Contact Relationship Category Extension</t>
+  </si>
+  <si>
+    <t>Catégorie de la relation du contact patient : indique si le CodeableConcept représente un rôle (ex : personne à prévenir) ou un type de relation (ex : mère)</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category.url</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension.url</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-relationship-category</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category.value[x]</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension.value[x]</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-relationship-category|2.2.0</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.coding</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.text</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>Patient.contact.relationship:relationType</t>
   </si>
   <si>
@@ -2558,6 +2674,33 @@
   </si>
   <si>
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type|2.2.0</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category.url</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category.value[x]</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.coding</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.text</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
@@ -3177,11 +3320,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO213"/>
+  <dimension ref="A1:AO231"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.65625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.83984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.97265625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -3205,9 +3348,9 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="62.59765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="69.84765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="91.3359375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="64.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -25511,7 +25654,7 @@
         <v>82</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>142</v>
+        <v>795</v>
       </c>
       <c r="AC191" s="2"/>
       <c r="AD191" t="s" s="2">
@@ -25536,7 +25679,7 @@
         <v>102</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AL191" t="s" s="2">
         <v>108</v>
@@ -25545,7 +25688,7 @@
         <v>82</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AO191" t="s" s="2">
         <v>82</v>
@@ -25553,13 +25696,13 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>789</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>82</v>
@@ -25584,7 +25727,7 @@
         <v>434</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="M192" t="s" s="2">
         <v>791</v>
@@ -25620,7 +25763,7 @@
       </c>
       <c r="Y192" s="2"/>
       <c r="Z192" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>82</v>
@@ -25653,7 +25796,7 @@
         <v>102</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AL192" t="s" s="2">
         <v>108</v>
@@ -25662,7 +25805,7 @@
         <v>82</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>82</v>
@@ -25670,14 +25813,12 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="C193" t="s" s="2">
-        <v>802</v>
-      </c>
+        <v>803</v>
+      </c>
+      <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
         <v>82</v>
       </c>
@@ -25698,18 +25839,16 @@
         <v>82</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>434</v>
+        <v>104</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>803</v>
+        <v>105</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>791</v>
+        <v>106</v>
       </c>
       <c r="N193" s="2"/>
-      <c r="O193" t="s" s="2">
-        <v>792</v>
-      </c>
+      <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
         <v>82</v>
       </c>
@@ -25733,11 +25872,13 @@
         <v>82</v>
       </c>
       <c r="X193" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y193" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y193" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z193" t="s" s="2">
-        <v>804</v>
+        <v>82</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>82</v>
@@ -25755,31 +25896,31 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>789</v>
+        <v>107</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI193" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK193" t="s" s="2">
-        <v>795</v>
+        <v>108</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>796</v>
+        <v>82</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>82</v>
@@ -25787,7 +25928,7 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>805</v>
@@ -25798,10 +25939,10 @@
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>82</v>
@@ -25813,18 +25954,16 @@
         <v>82</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>603</v>
+        <v>111</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>806</v>
+        <v>198</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>807</v>
+        <v>199</v>
       </c>
       <c r="N194" s="2"/>
-      <c r="O194" t="s" s="2">
-        <v>808</v>
-      </c>
+      <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
         <v>82</v>
       </c>
@@ -25860,43 +25999,43 @@
         <v>82</v>
       </c>
       <c r="AB194" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC194" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD194" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE194" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>805</v>
+        <v>118</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI194" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>609</v>
+        <v>82</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>809</v>
+        <v>82</v>
       </c>
       <c r="AO194" t="s" s="2">
         <v>82</v>
@@ -25904,21 +26043,23 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="C195" s="2"/>
+        <v>805</v>
+      </c>
+      <c r="C195" t="s" s="2">
+        <v>807</v>
+      </c>
       <c r="D195" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H195" t="s" s="2">
         <v>82</v>
@@ -25930,20 +26071,16 @@
         <v>82</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>698</v>
+        <v>808</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="O195" t="s" s="2">
-        <v>702</v>
-      </c>
+        <v>810</v>
+      </c>
+      <c r="N195" s="2"/>
+      <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
         <v>82</v>
       </c>
@@ -25991,7 +26128,7 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>810</v>
+        <v>118</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -26003,19 +26140,19 @@
         <v>82</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>703</v>
+        <v>82</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM195" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>814</v>
+        <v>82</v>
       </c>
       <c r="AO195" t="s" s="2">
         <v>82</v>
@@ -26023,10 +26160,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26049,18 +26186,16 @@
         <v>82</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>816</v>
+        <v>104</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>817</v>
+        <v>105</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>818</v>
+        <v>106</v>
       </c>
       <c r="N196" s="2"/>
-      <c r="O196" t="s" s="2">
-        <v>819</v>
-      </c>
+      <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
         <v>82</v>
       </c>
@@ -26108,7 +26243,7 @@
         <v>82</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>815</v>
+        <v>107</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -26120,19 +26255,19 @@
         <v>82</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>737</v>
+        <v>108</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>820</v>
+        <v>82</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>82</v>
@@ -26140,10 +26275,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26154,7 +26289,7 @@
         <v>80</v>
       </c>
       <c r="G197" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H197" t="s" s="2">
         <v>82</v>
@@ -26166,18 +26301,16 @@
         <v>82</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>173</v>
+        <v>111</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>822</v>
+        <v>198</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>823</v>
+        <v>199</v>
       </c>
       <c r="N197" s="2"/>
-      <c r="O197" t="s" s="2">
-        <v>824</v>
-      </c>
+      <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
         <v>82</v>
       </c>
@@ -26201,55 +26334,55 @@
         <v>82</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>825</v>
+        <v>82</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>826</v>
+        <v>82</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB197" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC197" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD197" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE197" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>821</v>
+        <v>118</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH197" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI197" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ197" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>712</v>
+        <v>82</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM197" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>827</v>
+        <v>82</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>82</v>
@@ -26257,10 +26390,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26268,7 +26401,7 @@
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G198" t="s" s="2">
         <v>90</v>
@@ -26283,24 +26416,24 @@
         <v>82</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>472</v>
+        <v>132</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>829</v>
+        <v>225</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="N198" s="2"/>
-      <c r="O198" t="s" s="2">
-        <v>831</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N198" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q198" s="2"/>
       <c r="R198" t="s" s="2">
-        <v>82</v>
+        <v>817</v>
       </c>
       <c r="S198" t="s" s="2">
         <v>82</v>
@@ -26342,31 +26475,31 @@
         <v>82</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>828</v>
+        <v>228</v>
       </c>
       <c r="AG198" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH198" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI198" t="s" s="2">
-        <v>832</v>
+        <v>82</v>
       </c>
       <c r="AJ198" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK198" t="s" s="2">
-        <v>833</v>
+        <v>196</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM198" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN198" t="s" s="2">
-        <v>834</v>
+        <v>82</v>
       </c>
       <c r="AO198" t="s" s="2">
         <v>82</v>
@@ -26374,10 +26507,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>835</v>
+        <v>818</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>835</v>
+        <v>819</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26400,13 +26533,13 @@
         <v>82</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>390</v>
+        <v>173</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>836</v>
+        <v>231</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>837</v>
+        <v>232</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -26418,7 +26551,7 @@
         <v>82</v>
       </c>
       <c r="S199" t="s" s="2">
-        <v>82</v>
+        <v>799</v>
       </c>
       <c r="T199" t="s" s="2">
         <v>82</v>
@@ -26433,13 +26566,11 @@
         <v>82</v>
       </c>
       <c r="X199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y199" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="Y199" s="2"/>
       <c r="Z199" t="s" s="2">
-        <v>82</v>
+        <v>820</v>
       </c>
       <c r="AA199" t="s" s="2">
         <v>82</v>
@@ -26457,7 +26588,7 @@
         <v>82</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>835</v>
+        <v>234</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -26472,10 +26603,10 @@
         <v>102</v>
       </c>
       <c r="AK199" t="s" s="2">
-        <v>838</v>
+        <v>196</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM199" t="s" s="2">
         <v>82</v>
@@ -26489,10 +26620,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>839</v>
+        <v>821</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>839</v>
+        <v>822</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26512,22 +26643,22 @@
         <v>82</v>
       </c>
       <c r="J200" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>765</v>
+        <v>151</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>840</v>
+        <v>823</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>841</v>
+        <v>824</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>842</v>
+        <v>825</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>843</v>
+        <v>826</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>82</v>
@@ -26576,7 +26707,7 @@
         <v>82</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>839</v>
+        <v>827</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -26591,16 +26722,16 @@
         <v>102</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>844</v>
+        <v>828</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>845</v>
+        <v>82</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>82</v>
+        <v>829</v>
       </c>
       <c r="AO200" t="s" s="2">
         <v>82</v>
@@ -26608,10 +26739,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>846</v>
+        <v>830</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>846</v>
+        <v>831</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26631,19 +26762,23 @@
         <v>82</v>
       </c>
       <c r="J201" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K201" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>105</v>
+        <v>832</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N201" s="2"/>
-      <c r="O201" s="2"/>
+        <v>833</v>
+      </c>
+      <c r="N201" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="O201" t="s" s="2">
+        <v>835</v>
+      </c>
       <c r="P201" t="s" s="2">
         <v>82</v>
       </c>
@@ -26691,7 +26826,7 @@
         <v>82</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>107</v>
+        <v>836</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -26703,10 +26838,10 @@
         <v>82</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>108</v>
+        <v>837</v>
       </c>
       <c r="AL201" t="s" s="2">
         <v>82</v>
@@ -26715,7 +26850,7 @@
         <v>82</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>82</v>
+        <v>838</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>82</v>
@@ -26723,21 +26858,23 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="C202" s="2"/>
+        <v>789</v>
+      </c>
+      <c r="C202" t="s" s="2">
+        <v>840</v>
+      </c>
       <c r="D202" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E202" s="2"/>
       <c r="F202" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G202" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H202" t="s" s="2">
         <v>82</v>
@@ -26749,18 +26886,18 @@
         <v>82</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>111</v>
+        <v>434</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>112</v>
+        <v>841</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N202" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O202" s="2"/>
+        <v>791</v>
+      </c>
+      <c r="N202" s="2"/>
+      <c r="O202" t="s" s="2">
+        <v>792</v>
+      </c>
       <c r="P202" t="s" s="2">
         <v>82</v>
       </c>
@@ -26784,13 +26921,11 @@
         <v>82</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y202" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y202" s="2"/>
       <c r="Z202" t="s" s="2">
-        <v>82</v>
+        <v>842</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>82</v>
@@ -26808,7 +26943,7 @@
         <v>82</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>118</v>
+        <v>789</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
@@ -26820,19 +26955,19 @@
         <v>82</v>
       </c>
       <c r="AJ202" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK202" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="AL202" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AL202" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM202" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>82</v>
+        <v>797</v>
       </c>
       <c r="AO202" t="s" s="2">
         <v>82</v>
@@ -26840,46 +26975,42 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>848</v>
+        <v>803</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
-        <v>785</v>
+        <v>82</v>
       </c>
       <c r="E203" s="2"/>
       <c r="F203" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G203" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H203" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I203" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J203" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>786</v>
+        <v>105</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="N203" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O203" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N203" s="2"/>
+      <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
         <v>82</v>
       </c>
@@ -26927,22 +27058,22 @@
         <v>82</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>788</v>
+        <v>107</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH203" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI203" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>196</v>
+        <v>108</v>
       </c>
       <c r="AL203" t="s" s="2">
         <v>82</v>
@@ -26959,10 +27090,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -26973,7 +27104,7 @@
         <v>90</v>
       </c>
       <c r="G204" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H204" t="s" s="2">
         <v>82</v>
@@ -26985,20 +27116,16 @@
         <v>82</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>434</v>
+        <v>111</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>850</v>
+        <v>198</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>851</v>
-      </c>
-      <c r="N204" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="O204" t="s" s="2">
-        <v>853</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N204" s="2"/>
+      <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
         <v>82</v>
       </c>
@@ -27022,55 +27149,55 @@
         <v>82</v>
       </c>
       <c r="X204" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y204" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="Z204" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AA204" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB204" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC204" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD204" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE204" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>849</v>
+        <v>118</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH204" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI204" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>854</v>
+        <v>82</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>855</v>
+        <v>82</v>
       </c>
       <c r="AM204" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>856</v>
+        <v>82</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>82</v>
@@ -27078,18 +27205,20 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="C205" s="2"/>
+        <v>805</v>
+      </c>
+      <c r="C205" t="s" s="2">
+        <v>807</v>
+      </c>
       <c r="D205" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E205" s="2"/>
       <c r="F205" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G205" t="s" s="2">
         <v>90</v>
@@ -27104,20 +27233,16 @@
         <v>82</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>594</v>
+        <v>808</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>858</v>
+        <v>809</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N205" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="O205" t="s" s="2">
-        <v>861</v>
-      </c>
+        <v>810</v>
+      </c>
+      <c r="N205" s="2"/>
+      <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
         <v>82</v>
       </c>
@@ -27165,31 +27290,31 @@
         <v>82</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>857</v>
+        <v>118</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI205" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ205" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>862</v>
+        <v>82</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>863</v>
+        <v>82</v>
       </c>
       <c r="AM205" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>864</v>
+        <v>82</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>82</v>
@@ -27197,21 +27322,21 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>865</v>
+        <v>846</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>865</v>
+        <v>812</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
-        <v>866</v>
+        <v>82</v>
       </c>
       <c r="E206" s="2"/>
       <c r="F206" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G206" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H206" t="s" s="2">
         <v>82</v>
@@ -27223,17 +27348,15 @@
         <v>82</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>867</v>
+        <v>104</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>868</v>
+        <v>105</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="N206" t="s" s="2">
-        <v>870</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N206" s="2"/>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
         <v>82</v>
@@ -27282,31 +27405,31 @@
         <v>82</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>865</v>
+        <v>107</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI206" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>871</v>
+        <v>108</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM206" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>872</v>
+        <v>82</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>82</v>
@@ -27314,10 +27437,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>873</v>
+        <v>847</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>873</v>
+        <v>814</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27328,7 +27451,7 @@
         <v>80</v>
       </c>
       <c r="G207" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H207" t="s" s="2">
         <v>82</v>
@@ -27337,23 +27460,19 @@
         <v>82</v>
       </c>
       <c r="J207" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>874</v>
+        <v>111</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>875</v>
+        <v>198</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="O207" t="s" s="2">
-        <v>878</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N207" s="2"/>
+      <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
         <v>82</v>
       </c>
@@ -27389,37 +27508,37 @@
         <v>82</v>
       </c>
       <c r="AB207" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC207" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD207" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE207" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>873</v>
+        <v>118</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH207" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI207" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>833</v>
+        <v>82</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>879</v>
+        <v>82</v>
       </c>
       <c r="AM207" t="s" s="2">
         <v>82</v>
@@ -27433,10 +27552,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>880</v>
+        <v>848</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>880</v>
+        <v>816</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27444,41 +27563,39 @@
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G208" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H208" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I208" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J208" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>765</v>
+        <v>132</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>881</v>
+        <v>225</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>882</v>
+        <v>226</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>883</v>
-      </c>
-      <c r="O208" t="s" s="2">
-        <v>884</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q208" s="2"/>
       <c r="R208" t="s" s="2">
-        <v>82</v>
+        <v>817</v>
       </c>
       <c r="S208" t="s" s="2">
         <v>82</v>
@@ -27520,25 +27637,25 @@
         <v>82</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>880</v>
+        <v>228</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH208" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI208" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK208" t="s" s="2">
-        <v>885</v>
+        <v>196</v>
       </c>
       <c r="AL208" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM208" t="s" s="2">
         <v>82</v>
@@ -27552,10 +27669,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>886</v>
+        <v>849</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>886</v>
+        <v>819</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27578,13 +27695,13 @@
         <v>82</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>105</v>
+        <v>231</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>106</v>
+        <v>232</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -27596,7 +27713,7 @@
         <v>82</v>
       </c>
       <c r="S209" t="s" s="2">
-        <v>82</v>
+        <v>840</v>
       </c>
       <c r="T209" t="s" s="2">
         <v>82</v>
@@ -27611,13 +27728,11 @@
         <v>82</v>
       </c>
       <c r="X209" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y209" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="Y209" s="2"/>
       <c r="Z209" t="s" s="2">
-        <v>82</v>
+        <v>820</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>82</v>
@@ -27635,7 +27750,7 @@
         <v>82</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>107</v>
+        <v>234</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
@@ -27647,10 +27762,10 @@
         <v>82</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK209" t="s" s="2">
-        <v>108</v>
+        <v>196</v>
       </c>
       <c r="AL209" t="s" s="2">
         <v>82</v>
@@ -27667,14 +27782,14 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>887</v>
+        <v>850</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>887</v>
+        <v>822</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
@@ -27690,21 +27805,23 @@
         <v>82</v>
       </c>
       <c r="J210" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>112</v>
+        <v>823</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>113</v>
+        <v>824</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O210" s="2"/>
+        <v>825</v>
+      </c>
+      <c r="O210" t="s" s="2">
+        <v>826</v>
+      </c>
       <c r="P210" t="s" s="2">
         <v>82</v>
       </c>
@@ -27752,7 +27869,7 @@
         <v>82</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>118</v>
+        <v>827</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
@@ -27764,10 +27881,10 @@
         <v>82</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK210" t="s" s="2">
-        <v>108</v>
+        <v>828</v>
       </c>
       <c r="AL210" t="s" s="2">
         <v>82</v>
@@ -27776,7 +27893,7 @@
         <v>82</v>
       </c>
       <c r="AN210" t="s" s="2">
-        <v>82</v>
+        <v>829</v>
       </c>
       <c r="AO210" t="s" s="2">
         <v>82</v>
@@ -27784,45 +27901,45 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>888</v>
+        <v>851</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>888</v>
+        <v>831</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>785</v>
+        <v>82</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I211" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J211" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>786</v>
+        <v>832</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>787</v>
+        <v>833</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>114</v>
+        <v>834</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>401</v>
+        <v>835</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>82</v>
@@ -27871,22 +27988,22 @@
         <v>82</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>788</v>
+        <v>836</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK211" t="s" s="2">
-        <v>196</v>
+        <v>837</v>
       </c>
       <c r="AL211" t="s" s="2">
         <v>82</v>
@@ -27895,7 +28012,7 @@
         <v>82</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>82</v>
+        <v>838</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>82</v>
@@ -27903,10 +28020,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>889</v>
+        <v>852</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>889</v>
+        <v>852</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -27914,7 +28031,7 @@
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G212" t="s" s="2">
         <v>90</v>
@@ -27926,21 +28043,21 @@
         <v>82</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>890</v>
+        <v>603</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>891</v>
+        <v>853</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="O212" s="2"/>
+        <v>854</v>
+      </c>
+      <c r="N212" s="2"/>
+      <c r="O212" t="s" s="2">
+        <v>855</v>
+      </c>
       <c r="P212" t="s" s="2">
         <v>82</v>
       </c>
@@ -27988,10 +28105,10 @@
         <v>82</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>889</v>
+        <v>852</v>
       </c>
       <c r="AG212" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH212" t="s" s="2">
         <v>90</v>
@@ -28003,7 +28120,7 @@
         <v>102</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>410</v>
+        <v>609</v>
       </c>
       <c r="AL212" t="s" s="2">
         <v>108</v>
@@ -28012,7 +28129,7 @@
         <v>82</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>894</v>
+        <v>856</v>
       </c>
       <c r="AO212" t="s" s="2">
         <v>82</v>
@@ -28020,10 +28137,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>895</v>
+        <v>857</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>895</v>
+        <v>857</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28031,10 +28148,10 @@
       </c>
       <c r="E213" s="2"/>
       <c r="F213" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G213" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H213" t="s" s="2">
         <v>82</v>
@@ -28043,19 +28160,23 @@
         <v>82</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>173</v>
+        <v>698</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>896</v>
+        <v>858</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>897</v>
-      </c>
-      <c r="N213" s="2"/>
-      <c r="O213" s="2"/>
+        <v>859</v>
+      </c>
+      <c r="N213" t="s" s="2">
+        <v>860</v>
+      </c>
+      <c r="O213" t="s" s="2">
+        <v>702</v>
+      </c>
       <c r="P213" t="s" s="2">
         <v>82</v>
       </c>
@@ -28079,13 +28200,13 @@
         <v>82</v>
       </c>
       <c r="X213" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>897</v>
+        <v>82</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>898</v>
+        <v>82</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>82</v>
@@ -28103,13 +28224,13 @@
         <v>82</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>895</v>
+        <v>857</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH213" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI213" t="s" s="2">
         <v>82</v>
@@ -28118,7 +28239,7 @@
         <v>102</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>899</v>
+        <v>703</v>
       </c>
       <c r="AL213" t="s" s="2">
         <v>108</v>
@@ -28127,14 +28248,2126 @@
         <v>82</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>82</v>
+        <v>861</v>
       </c>
       <c r="AO213" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="214" hidden="true">
+      <c r="A214" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="B214" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="C214" s="2"/>
+      <c r="D214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E214" s="2"/>
+      <c r="F214" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G214" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K214" t="s" s="2">
+        <v>863</v>
+      </c>
+      <c r="L214" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="M214" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="N214" s="2"/>
+      <c r="O214" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="P214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q214" s="2"/>
+      <c r="R214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF214" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="AG214" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH214" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ214" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK214" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AL214" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN214" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="AO214" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="215" hidden="true">
+      <c r="A215" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="B215" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="C215" s="2"/>
+      <c r="D215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E215" s="2"/>
+      <c r="F215" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G215" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K215" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L215" t="s" s="2">
+        <v>869</v>
+      </c>
+      <c r="M215" t="s" s="2">
+        <v>870</v>
+      </c>
+      <c r="N215" s="2"/>
+      <c r="O215" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="P215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q215" s="2"/>
+      <c r="R215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X215" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Y215" t="s" s="2">
+        <v>872</v>
+      </c>
+      <c r="Z215" t="s" s="2">
+        <v>873</v>
+      </c>
+      <c r="AA215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF215" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="AG215" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH215" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ215" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK215" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AL215" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN215" t="s" s="2">
+        <v>874</v>
+      </c>
+      <c r="AO215" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="216" hidden="true">
+      <c r="A216" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="C216" s="2"/>
+      <c r="D216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E216" s="2"/>
+      <c r="F216" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G216" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K216" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L216" t="s" s="2">
+        <v>876</v>
+      </c>
+      <c r="M216" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="N216" s="2"/>
+      <c r="O216" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="P216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q216" s="2"/>
+      <c r="R216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF216" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="AG216" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH216" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI216" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="AJ216" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK216" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="AL216" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN216" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="AO216" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="217" hidden="true">
+      <c r="A217" t="s" s="2">
+        <v>882</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>882</v>
+      </c>
+      <c r="C217" s="2"/>
+      <c r="D217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E217" s="2"/>
+      <c r="F217" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G217" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K217" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L217" t="s" s="2">
+        <v>883</v>
+      </c>
+      <c r="M217" t="s" s="2">
+        <v>884</v>
+      </c>
+      <c r="N217" s="2"/>
+      <c r="O217" s="2"/>
+      <c r="P217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q217" s="2"/>
+      <c r="R217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF217" t="s" s="2">
+        <v>882</v>
+      </c>
+      <c r="AG217" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH217" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ217" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK217" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="AL217" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO217" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="218" hidden="true">
+      <c r="A218" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="C218" s="2"/>
+      <c r="D218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E218" s="2"/>
+      <c r="F218" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G218" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K218" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="L218" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="M218" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="N218" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="O218" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="P218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q218" s="2"/>
+      <c r="R218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF218" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="AG218" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH218" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ218" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK218" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="AL218" t="s" s="2">
+        <v>892</v>
+      </c>
+      <c r="AM218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO218" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="219" hidden="true">
+      <c r="A219" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="C219" s="2"/>
+      <c r="D219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E219" s="2"/>
+      <c r="F219" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G219" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K219" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L219" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M219" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N219" s="2"/>
+      <c r="O219" s="2"/>
+      <c r="P219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q219" s="2"/>
+      <c r="R219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF219" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG219" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH219" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK219" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO219" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="220" hidden="true">
+      <c r="A220" t="s" s="2">
+        <v>894</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>894</v>
+      </c>
+      <c r="C220" s="2"/>
+      <c r="D220" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E220" s="2"/>
+      <c r="F220" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G220" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K220" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L220" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M220" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N220" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O220" s="2"/>
+      <c r="P220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q220" s="2"/>
+      <c r="R220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF220" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG220" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH220" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ220" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK220" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO220" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="221" hidden="true">
+      <c r="A221" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="C221" s="2"/>
+      <c r="D221" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="E221" s="2"/>
+      <c r="F221" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G221" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I221" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J221" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K221" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L221" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="M221" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="N221" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O221" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="P221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q221" s="2"/>
+      <c r="R221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF221" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="AG221" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH221" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ221" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK221" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AL221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO221" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="222" hidden="true">
+      <c r="A222" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="C222" s="2"/>
+      <c r="D222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E222" s="2"/>
+      <c r="F222" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G222" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K222" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L222" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="M222" t="s" s="2">
+        <v>898</v>
+      </c>
+      <c r="N222" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="O222" t="s" s="2">
+        <v>900</v>
+      </c>
+      <c r="P222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q222" s="2"/>
+      <c r="R222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X222" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y222" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z222" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AA222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF222" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="AG222" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH222" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ222" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK222" t="s" s="2">
+        <v>901</v>
+      </c>
+      <c r="AL222" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="AM222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN222" t="s" s="2">
+        <v>903</v>
+      </c>
+      <c r="AO222" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="223" hidden="true">
+      <c r="A223" t="s" s="2">
+        <v>904</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>904</v>
+      </c>
+      <c r="C223" s="2"/>
+      <c r="D223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E223" s="2"/>
+      <c r="F223" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G223" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K223" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="L223" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="M223" t="s" s="2">
+        <v>906</v>
+      </c>
+      <c r="N223" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="O223" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="P223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q223" s="2"/>
+      <c r="R223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF223" t="s" s="2">
+        <v>904</v>
+      </c>
+      <c r="AG223" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH223" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ223" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK223" t="s" s="2">
+        <v>909</v>
+      </c>
+      <c r="AL223" t="s" s="2">
+        <v>910</v>
+      </c>
+      <c r="AM223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN223" t="s" s="2">
+        <v>911</v>
+      </c>
+      <c r="AO223" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="224" hidden="true">
+      <c r="A224" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="B224" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="C224" s="2"/>
+      <c r="D224" t="s" s="2">
+        <v>913</v>
+      </c>
+      <c r="E224" s="2"/>
+      <c r="F224" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G224" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K224" t="s" s="2">
+        <v>914</v>
+      </c>
+      <c r="L224" t="s" s="2">
+        <v>915</v>
+      </c>
+      <c r="M224" t="s" s="2">
+        <v>916</v>
+      </c>
+      <c r="N224" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="O224" s="2"/>
+      <c r="P224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q224" s="2"/>
+      <c r="R224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF224" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="AG224" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH224" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ224" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK224" t="s" s="2">
+        <v>918</v>
+      </c>
+      <c r="AL224" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM224" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN224" t="s" s="2">
+        <v>919</v>
+      </c>
+      <c r="AO224" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="225" hidden="true">
+      <c r="A225" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="C225" s="2"/>
+      <c r="D225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E225" s="2"/>
+      <c r="F225" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G225" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J225" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K225" t="s" s="2">
+        <v>921</v>
+      </c>
+      <c r="L225" t="s" s="2">
+        <v>922</v>
+      </c>
+      <c r="M225" t="s" s="2">
+        <v>923</v>
+      </c>
+      <c r="N225" t="s" s="2">
+        <v>924</v>
+      </c>
+      <c r="O225" t="s" s="2">
+        <v>925</v>
+      </c>
+      <c r="P225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q225" s="2"/>
+      <c r="R225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF225" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="AG225" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH225" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ225" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK225" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="AL225" t="s" s="2">
+        <v>926</v>
+      </c>
+      <c r="AM225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN225" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO225" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="226" hidden="true">
+      <c r="A226" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="C226" s="2"/>
+      <c r="D226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E226" s="2"/>
+      <c r="F226" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G226" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I226" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J226" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K226" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="L226" t="s" s="2">
+        <v>928</v>
+      </c>
+      <c r="M226" t="s" s="2">
+        <v>929</v>
+      </c>
+      <c r="N226" t="s" s="2">
+        <v>930</v>
+      </c>
+      <c r="O226" t="s" s="2">
+        <v>931</v>
+      </c>
+      <c r="P226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q226" s="2"/>
+      <c r="R226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF226" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="AG226" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH226" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ226" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK226" t="s" s="2">
+        <v>932</v>
+      </c>
+      <c r="AL226" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN226" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO226" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="227" hidden="true">
+      <c r="A227" t="s" s="2">
+        <v>933</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>933</v>
+      </c>
+      <c r="C227" s="2"/>
+      <c r="D227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E227" s="2"/>
+      <c r="F227" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G227" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K227" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L227" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M227" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N227" s="2"/>
+      <c r="O227" s="2"/>
+      <c r="P227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q227" s="2"/>
+      <c r="R227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF227" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG227" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH227" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK227" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN227" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO227" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="228" hidden="true">
+      <c r="A228" t="s" s="2">
+        <v>934</v>
+      </c>
+      <c r="B228" t="s" s="2">
+        <v>934</v>
+      </c>
+      <c r="C228" s="2"/>
+      <c r="D228" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E228" s="2"/>
+      <c r="F228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G228" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K228" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L228" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M228" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N228" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O228" s="2"/>
+      <c r="P228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q228" s="2"/>
+      <c r="R228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF228" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH228" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ228" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK228" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN228" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO228" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="229" hidden="true">
+      <c r="A229" t="s" s="2">
+        <v>935</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>935</v>
+      </c>
+      <c r="C229" s="2"/>
+      <c r="D229" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="E229" s="2"/>
+      <c r="F229" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G229" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I229" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J229" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K229" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L229" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="M229" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="N229" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O229" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="P229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q229" s="2"/>
+      <c r="R229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF229" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="AG229" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH229" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ229" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK229" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AL229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO229" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="230" hidden="true">
+      <c r="A230" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B230" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="C230" s="2"/>
+      <c r="D230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E230" s="2"/>
+      <c r="F230" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G230" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J230" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K230" t="s" s="2">
+        <v>937</v>
+      </c>
+      <c r="L230" t="s" s="2">
+        <v>938</v>
+      </c>
+      <c r="M230" t="s" s="2">
+        <v>939</v>
+      </c>
+      <c r="N230" t="s" s="2">
+        <v>940</v>
+      </c>
+      <c r="O230" s="2"/>
+      <c r="P230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q230" s="2"/>
+      <c r="R230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF230" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="AG230" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH230" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ230" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK230" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AL230" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM230" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN230" t="s" s="2">
+        <v>941</v>
+      </c>
+      <c r="AO230" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="231" hidden="true">
+      <c r="A231" t="s" s="2">
+        <v>942</v>
+      </c>
+      <c r="B231" t="s" s="2">
+        <v>942</v>
+      </c>
+      <c r="C231" s="2"/>
+      <c r="D231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E231" s="2"/>
+      <c r="F231" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G231" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J231" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K231" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L231" t="s" s="2">
+        <v>943</v>
+      </c>
+      <c r="M231" t="s" s="2">
+        <v>944</v>
+      </c>
+      <c r="N231" s="2"/>
+      <c r="O231" s="2"/>
+      <c r="P231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q231" s="2"/>
+      <c r="R231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X231" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Y231" t="s" s="2">
+        <v>944</v>
+      </c>
+      <c r="Z231" t="s" s="2">
+        <v>945</v>
+      </c>
+      <c r="AA231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF231" t="s" s="2">
+        <v>942</v>
+      </c>
+      <c r="AG231" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH231" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ231" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK231" t="s" s="2">
+        <v>946</v>
+      </c>
+      <c r="AL231" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO231" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO213">
+  <autoFilter ref="A1:AO231">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -28144,7 +30377,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI212">
+  <conditionalFormatting sqref="A2:AI230">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$240</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8573" uniqueCount="947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8907" uniqueCount="962">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1310,28 +1310,28 @@
     <t>PID-3</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS</t>
-  </si>
-  <si>
-    <t>NSS</t>
+    <t>Patient.identifier:NSS-NIR</t>
+  </si>
+  <si>
+    <t>NSS-NIR</t>
   </si>
   <si>
     <t>National Health Plan Identifier | Le Numéro d'Inscription au Répertoire (NIR) de facturation permet de faire transiter le numéro de sécurité social de l’ayant droit ou du bénéfiaire (patient) / le numéro de sécurité sociale de l’ouvrant droit (assuré).</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.id</t>
+    <t>Patient.identifier:NSS-NIR.id</t>
   </si>
   <si>
     <t>Patient.identifier.id</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.extension</t>
+    <t>Patient.identifier:NSS-NIR.extension</t>
   </si>
   <si>
     <t>Patient.identifier.extension</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.use</t>
+    <t>Patient.identifier:NSS-NIR.use</t>
   </si>
   <si>
     <t>Patient.identifier.use</t>
@@ -1364,7 +1364,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.type</t>
+    <t>Patient.identifier:NSS-NIR.type</t>
   </si>
   <si>
     <t>Patient.identifier.type</t>
@@ -1403,13 +1403,13 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.system</t>
+    <t>Patient.identifier:NSS-NIR.system</t>
   </si>
   <si>
     <t>Patient.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
+    <t>Autorité d’affectation du NIR utilisé en tant que numéro de sécurité sociale</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -1421,7 +1421,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.250.1.213.1.4.8</t>
+    <t>urn:oid:1.2.250.1.213.1.4.13</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1436,7 +1436,7 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.value</t>
+    <t>Patient.identifier:NSS-NIR.value</t>
   </si>
   <si>
     <t>Patient.identifier.value</t>
@@ -1463,7 +1463,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.period</t>
+    <t>Patient.identifier:NSS-NIR.period</t>
   </si>
   <si>
     <t>Patient.identifier.period</t>
@@ -1484,7 +1484,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.assigner</t>
+    <t>Patient.identifier:NSS-NIR.assigner</t>
   </si>
   <si>
     <t>Patient.identifier.assigner</t>
@@ -1510,6 +1510,45 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA</t>
+  </si>
+  <si>
+    <t>NSS-NIA</t>
+  </si>
+  <si>
+    <t>National Health Plan Identifier | Le Numéro d'Inscription au Répertoire (NIA) de facturation d'attente permet de faire transiter le numéro de sécurité social de l’ayant droit ou du bénéfiaire (patient) / le numéro de sécurité sociale d'attente de l’ouvrant droit (assuré).</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.use</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.type</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.system</t>
+  </si>
+  <si>
+    <t>Autorité d’affectation du NIA utilisé en tant que numéro de sécurité sociale</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.250.1.213.1.4.14</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.value</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.period</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.assigner</t>
   </si>
   <si>
     <t>Patient.identifier:INS-C</t>
@@ -1548,6 +1587,9 @@
     <t>Patient.identifier:INS-C.system</t>
   </si>
   <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
     <t>urn:oid:1.2.250.1.213.1.4.2</t>
   </si>
   <si>
@@ -1743,6 +1785,9 @@
   </si>
   <si>
     <t>Autorité d'affectation des INS-NIR</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.250.1.213.1.4.8</t>
   </si>
   <si>
     <t>Patient.identifier:INS-NIR.value</t>
@@ -3320,7 +3365,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO231"/>
+  <dimension ref="A1:AO240"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.65625" customWidth="true" bestFit="true"/>
@@ -12812,7 +12857,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -13195,7 +13240,7 @@
         <v>82</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>485</v>
+        <v>427</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>82</v>
@@ -13266,7 +13311,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>433</v>
@@ -13314,7 +13359,7 @@
         <v>82</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>487</v>
+        <v>439</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>82</v>
@@ -13383,7 +13428,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>444</v>
@@ -13412,7 +13457,7 @@
         <v>132</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>445</v>
+        <v>487</v>
       </c>
       <c r="M87" t="s" s="2">
         <v>446</v>
@@ -13431,7 +13476,7 @@
         <v>82</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>450</v>
@@ -13502,7 +13547,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>455</v>
@@ -13619,7 +13664,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>464</v>
@@ -13734,7 +13779,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>471</v>
@@ -13851,13 +13896,13 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>403</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>82</v>
@@ -13867,7 +13912,7 @@
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -13882,7 +13927,7 @@
         <v>404</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="M91" t="s" s="2">
         <v>406</v>
@@ -13970,7 +14015,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>418</v>
@@ -14085,7 +14130,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>420</v>
@@ -14202,7 +14247,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>422</v>
@@ -14250,7 +14295,7 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>82</v>
@@ -14467,7 +14512,7 @@
         <v>132</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>445</v>
+        <v>502</v>
       </c>
       <c r="M96" t="s" s="2">
         <v>446</v>
@@ -14486,7 +14531,7 @@
         <v>82</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>450</v>
@@ -14557,7 +14602,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>455</v>
@@ -14674,7 +14719,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>464</v>
@@ -14789,7 +14834,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>471</v>
@@ -14906,13 +14951,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>403</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>82</v>
@@ -14922,7 +14967,7 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
@@ -14937,7 +14982,7 @@
         <v>404</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>406</v>
@@ -15025,7 +15070,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>418</v>
@@ -15140,7 +15185,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>420</v>
@@ -15257,7 +15302,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>422</v>
@@ -15292,7 +15337,7 @@
         <v>424</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>512</v>
+        <v>425</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>426</v>
@@ -15305,7 +15350,7 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>82</v>
@@ -15322,9 +15367,11 @@
       <c r="X103" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y103" s="2"/>
+      <c r="Y103" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="Z103" t="s" s="2">
-        <v>513</v>
+        <v>429</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -15374,7 +15421,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>433</v>
@@ -15422,7 +15469,7 @@
         <v>82</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>82</v>
@@ -15491,7 +15538,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>444</v>
@@ -15520,7 +15567,7 @@
         <v>132</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>445</v>
+        <v>502</v>
       </c>
       <c r="M105" t="s" s="2">
         <v>446</v>
@@ -15539,7 +15586,7 @@
         <v>82</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>450</v>
@@ -16345,7 +16392,7 @@
         <v>424</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>425</v>
+        <v>526</v>
       </c>
       <c r="O112" t="s" s="2">
         <v>426</v>
@@ -16358,7 +16405,7 @@
         <v>82</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>82</v>
@@ -16375,11 +16422,9 @@
       <c r="X112" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y112" t="s" s="2">
-        <v>428</v>
-      </c>
+      <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>429</v>
+        <v>527</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -16429,7 +16474,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>433</v>
@@ -16477,7 +16522,7 @@
         <v>82</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>82</v>
@@ -16546,7 +16591,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>444</v>
@@ -16575,7 +16620,7 @@
         <v>132</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>445</v>
+        <v>502</v>
       </c>
       <c r="M114" t="s" s="2">
         <v>446</v>
@@ -16665,7 +16710,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>455</v>
@@ -16782,7 +16827,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>464</v>
@@ -16897,7 +16942,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>471</v>
@@ -17012,15 +17057,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>403</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>82</v>
@@ -17033,7 +17078,7 @@
         <v>81</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>82</v>
@@ -17045,7 +17090,7 @@
         <v>404</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>406</v>
@@ -17133,7 +17178,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>418</v>
@@ -17248,7 +17293,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>420</v>
@@ -17365,7 +17410,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>422</v>
@@ -17394,13 +17439,13 @@
         <v>173</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>538</v>
+        <v>423</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>424</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>539</v>
+        <v>425</v>
       </c>
       <c r="O121" t="s" s="2">
         <v>426</v>
@@ -17413,7 +17458,7 @@
         <v>82</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>82</v>
@@ -17430,9 +17475,11 @@
       <c r="X121" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y121" s="2"/>
+      <c r="Y121" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="Z121" t="s" s="2">
-        <v>540</v>
+        <v>429</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -17482,7 +17529,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>433</v>
@@ -17530,7 +17577,7 @@
         <v>82</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>82</v>
@@ -17547,11 +17594,9 @@
       <c r="X122" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="Y122" t="s" s="2">
-        <v>543</v>
-      </c>
+      <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>544</v>
+        <v>440</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -17601,7 +17646,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>444</v>
@@ -17630,7 +17675,7 @@
         <v>132</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>546</v>
+        <v>502</v>
       </c>
       <c r="M123" t="s" s="2">
         <v>446</v>
@@ -17649,7 +17694,7 @@
         <v>82</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>450</v>
@@ -17720,7 +17765,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>455</v>
@@ -17837,7 +17882,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>464</v>
@@ -17952,7 +17997,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>471</v>
@@ -18067,15 +18112,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>403</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>82</v>
@@ -18088,7 +18133,7 @@
         <v>81</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>82</v>
@@ -18100,7 +18145,7 @@
         <v>404</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="M127" t="s" s="2">
         <v>406</v>
@@ -18188,7 +18233,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>418</v>
@@ -18303,7 +18348,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>420</v>
@@ -18420,7 +18465,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>422</v>
@@ -18449,13 +18494,13 @@
         <v>173</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>423</v>
+        <v>552</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>424</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>425</v>
+        <v>553</v>
       </c>
       <c r="O130" t="s" s="2">
         <v>426</v>
@@ -18468,7 +18513,7 @@
         <v>82</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>82</v>
@@ -18485,11 +18530,9 @@
       <c r="X130" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y130" t="s" s="2">
-        <v>428</v>
-      </c>
+      <c r="Y130" s="2"/>
       <c r="Z130" t="s" s="2">
-        <v>429</v>
+        <v>554</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>82</v>
@@ -18539,7 +18582,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>433</v>
@@ -18587,7 +18630,7 @@
         <v>82</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>82</v>
@@ -18605,10 +18648,10 @@
         <v>155</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -18658,7 +18701,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>444</v>
@@ -18687,7 +18730,7 @@
         <v>132</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M132" t="s" s="2">
         <v>446</v>
@@ -18706,7 +18749,7 @@
         <v>82</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>450</v>
@@ -18777,7 +18820,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>455</v>
@@ -18894,7 +18937,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>464</v>
@@ -19009,7 +19052,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>471</v>
@@ -19126,13 +19169,13 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>403</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>82</v>
@@ -19157,7 +19200,7 @@
         <v>404</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M136" t="s" s="2">
         <v>406</v>
@@ -19245,7 +19288,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>418</v>
@@ -19360,7 +19403,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>420</v>
@@ -19477,7 +19520,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>422</v>
@@ -19596,7 +19639,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>433</v>
@@ -19644,7 +19687,7 @@
         <v>82</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>82</v>
@@ -19662,10 +19705,10 @@
         <v>155</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>82</v>
@@ -19715,7 +19758,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>444</v>
@@ -19744,7 +19787,7 @@
         <v>132</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M141" t="s" s="2">
         <v>446</v>
@@ -19763,7 +19806,7 @@
         <v>82</v>
       </c>
       <c r="S141" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="T141" t="s" s="2">
         <v>450</v>
@@ -19834,7 +19877,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>455</v>
@@ -19951,7 +19994,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>464</v>
@@ -20066,7 +20109,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>471</v>
@@ -20181,15 +20224,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>403</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>82</v>
@@ -20202,7 +20245,7 @@
         <v>81</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>82</v>
@@ -20214,7 +20257,7 @@
         <v>404</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>406</v>
@@ -20302,7 +20345,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>418</v>
@@ -20417,7 +20460,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>420</v>
@@ -20534,7 +20577,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>422</v>
@@ -20563,13 +20606,13 @@
         <v>173</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>538</v>
+        <v>423</v>
       </c>
       <c r="M148" t="s" s="2">
         <v>424</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>584</v>
+        <v>425</v>
       </c>
       <c r="O148" t="s" s="2">
         <v>426</v>
@@ -20582,7 +20625,7 @@
         <v>82</v>
       </c>
       <c r="S148" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="T148" t="s" s="2">
         <v>82</v>
@@ -20599,9 +20642,11 @@
       <c r="X148" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y148" s="2"/>
+      <c r="Y148" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="Z148" t="s" s="2">
-        <v>540</v>
+        <v>429</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>82</v>
@@ -20717,10 +20762,10 @@
         <v>155</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>82</v>
@@ -21236,14 +21281,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="154" hidden="true">
+    <row r="154">
       <c r="A154" t="s" s="2">
         <v>593</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="C154" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>594</v>
+      </c>
       <c r="D154" t="s" s="2">
         <v>82</v>
       </c>
@@ -21252,38 +21299,34 @@
         <v>80</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I154" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J154" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>594</v>
+        <v>404</v>
       </c>
       <c r="L154" t="s" s="2">
         <v>595</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>598</v>
+        <v>407</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q154" t="s" s="2">
-        <v>599</v>
-      </c>
+      <c r="Q154" s="2"/>
       <c r="R154" t="s" s="2">
         <v>82</v>
       </c>
@@ -21327,13 +21370,13 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>593</v>
+        <v>403</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>82</v>
@@ -21342,16 +21385,16 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>600</v>
+        <v>410</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>108</v>
+        <v>411</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>601</v>
+        <v>412</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -21359,10 +21402,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>602</v>
+        <v>418</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21370,10 +21413,10 @@
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>82</v>
@@ -21382,23 +21425,19 @@
         <v>82</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>603</v>
+        <v>104</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>604</v>
+        <v>105</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>607</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N155" s="2"/>
+      <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>82</v>
       </c>
@@ -21434,41 +21473,43 @@
         <v>82</v>
       </c>
       <c r="AB155" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="AC155" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD155" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE155" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>602</v>
+        <v>107</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>609</v>
+        <v>108</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>611</v>
+        <v>82</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -21476,16 +21517,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>612</v>
+        <v>597</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C156" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21501,23 +21540,21 @@
         <v>82</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>614</v>
+        <v>111</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>615</v>
+        <v>112</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>616</v>
+        <v>113</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>607</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>82</v>
       </c>
@@ -21553,19 +21590,19 @@
         <v>82</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>602</v>
+        <v>118</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21577,19 +21614,19 @@
         <v>82</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>609</v>
+        <v>108</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>611</v>
+        <v>82</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>82</v>
@@ -21597,10 +21634,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>617</v>
+        <v>598</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>618</v>
+        <v>422</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21608,7 +21645,7 @@
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G157" t="s" s="2">
         <v>90</v>
@@ -21617,22 +21654,26 @@
         <v>82</v>
       </c>
       <c r="I157" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>105</v>
+        <v>552</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N157" s="2"/>
-      <c r="O157" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="O157" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="P157" t="s" s="2">
         <v>82</v>
       </c>
@@ -21656,13 +21697,11 @@
         <v>82</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y157" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="Y157" s="2"/>
       <c r="Z157" t="s" s="2">
-        <v>82</v>
+        <v>554</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>82</v>
@@ -21680,7 +21719,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>107</v>
+        <v>430</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21692,10 +21731,10 @@
         <v>82</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>108</v>
+        <v>431</v>
       </c>
       <c r="AL157" t="s" s="2">
         <v>82</v>
@@ -21704,7 +21743,7 @@
         <v>82</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>82</v>
@@ -21712,21 +21751,21 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>619</v>
+        <v>600</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>620</v>
+        <v>433</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>82</v>
@@ -21735,21 +21774,23 @@
         <v>82</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>111</v>
+        <v>434</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>112</v>
+        <v>435</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>113</v>
+        <v>436</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O158" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="P158" t="s" s="2">
         <v>82</v>
       </c>
@@ -21758,7 +21799,7 @@
         <v>82</v>
       </c>
       <c r="S158" t="s" s="2">
-        <v>82</v>
+        <v>601</v>
       </c>
       <c r="T158" t="s" s="2">
         <v>82</v>
@@ -21773,46 +21814,46 @@
         <v>82</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>82</v>
+        <v>557</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>82</v>
+        <v>558</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB158" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC158" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD158" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE158" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>118</v>
+        <v>441</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>108</v>
+        <v>431</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>82</v>
@@ -21821,7 +21862,7 @@
         <v>82</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>82</v>
@@ -21829,10 +21870,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>621</v>
+        <v>602</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>622</v>
+        <v>444</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21849,25 +21890,25 @@
         <v>82</v>
       </c>
       <c r="I159" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J159" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>624</v>
+        <v>446</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>625</v>
+        <v>447</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>626</v>
+        <v>448</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
@@ -21877,10 +21918,10 @@
         <v>82</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>627</v>
+        <v>604</v>
       </c>
       <c r="T159" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="U159" t="s" s="2">
         <v>82</v>
@@ -21892,13 +21933,13 @@
         <v>82</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>628</v>
+        <v>82</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>629</v>
+        <v>82</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>82</v>
@@ -21916,7 +21957,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>630</v>
+        <v>451</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21931,7 +21972,7 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>314</v>
+        <v>452</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>82</v>
@@ -21940,7 +21981,7 @@
         <v>82</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>631</v>
+        <v>453</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>82</v>
@@ -21948,10 +21989,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>633</v>
+        <v>455</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21959,7 +22000,7 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>90</v>
@@ -21977,17 +22018,15 @@
         <v>104</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>634</v>
+        <v>456</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>635</v>
+        <v>457</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>82</v>
       </c>
@@ -21999,7 +22038,7 @@
         <v>82</v>
       </c>
       <c r="T160" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="U160" t="s" s="2">
         <v>82</v>
@@ -22035,7 +22074,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>637</v>
+        <v>460</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -22050,7 +22089,7 @@
         <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>334</v>
+        <v>461</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>82</v>
@@ -22059,7 +22098,7 @@
         <v>82</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>638</v>
+        <v>462</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>82</v>
@@ -22067,14 +22106,14 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>639</v>
+        <v>606</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>640</v>
+        <v>464</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>641</v>
+        <v>82</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -22093,17 +22132,15 @@
         <v>91</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>104</v>
+        <v>390</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>642</v>
+        <v>465</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>644</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>82</v>
@@ -22152,7 +22189,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>645</v>
+        <v>467</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -22167,7 +22204,7 @@
         <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>646</v>
+        <v>468</v>
       </c>
       <c r="AL161" t="s" s="2">
         <v>82</v>
@@ -22176,7 +22213,7 @@
         <v>82</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>647</v>
+        <v>469</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>82</v>
@@ -22184,21 +22221,21 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>648</v>
+        <v>607</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>649</v>
+        <v>471</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>650</v>
+        <v>82</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>82</v>
@@ -22210,16 +22247,16 @@
         <v>91</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>104</v>
+        <v>472</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>651</v>
+        <v>473</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>652</v>
+        <v>474</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>653</v>
+        <v>475</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -22269,13 +22306,13 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>654</v>
+        <v>476</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH162" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI162" t="s" s="2">
         <v>82</v>
@@ -22284,7 +22321,7 @@
         <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>655</v>
+        <v>477</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>82</v>
@@ -22293,7 +22330,7 @@
         <v>82</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>656</v>
+        <v>478</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
@@ -22301,10 +22338,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>657</v>
+        <v>608</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>658</v>
+        <v>608</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22315,32 +22352,38 @@
         <v>80</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I163" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J163" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>104</v>
+        <v>609</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>659</v>
+        <v>610</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="N163" s="2"/>
-      <c r="O163" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>613</v>
+      </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q163" s="2"/>
+      <c r="Q163" t="s" s="2">
+        <v>614</v>
+      </c>
       <c r="R163" t="s" s="2">
         <v>82</v>
       </c>
@@ -22384,13 +22427,13 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>661</v>
+        <v>608</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI163" t="s" s="2">
         <v>82</v>
@@ -22399,16 +22442,16 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>662</v>
+        <v>615</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>82</v>
+        <v>616</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>663</v>
+        <v>82</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -22416,10 +22459,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>664</v>
+        <v>617</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>665</v>
+        <v>617</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22427,7 +22470,7 @@
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G164" t="s" s="2">
         <v>81</v>
@@ -22442,16 +22485,20 @@
         <v>91</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>104</v>
+        <v>618</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>666</v>
+        <v>619</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="N164" s="2"/>
-      <c r="O164" s="2"/>
+        <v>620</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>622</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
       </c>
@@ -22487,19 +22534,17 @@
         <v>82</v>
       </c>
       <c r="AB164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC164" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="AC164" s="2"/>
       <c r="AD164" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE164" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>668</v>
+        <v>617</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22514,16 +22559,16 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>669</v>
+        <v>624</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>670</v>
+        <v>626</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -22531,12 +22576,14 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>671</v>
+        <v>627</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="C165" s="2"/>
+        <v>617</v>
+      </c>
+      <c r="C165" t="s" s="2">
+        <v>628</v>
+      </c>
       <c r="D165" t="s" s="2">
         <v>82</v>
       </c>
@@ -22545,7 +22592,7 @@
         <v>80</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>82</v>
@@ -22557,17 +22604,19 @@
         <v>91</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>390</v>
+        <v>629</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="N165" s="2"/>
+        <v>631</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>621</v>
+      </c>
       <c r="O165" t="s" s="2">
-        <v>675</v>
+        <v>622</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>82</v>
@@ -22616,13 +22665,13 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>676</v>
+        <v>617</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH165" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI165" t="s" s="2">
         <v>82</v>
@@ -22631,65 +22680,59 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>396</v>
+        <v>624</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>677</v>
+        <v>626</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>678</v>
+        <v>632</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C166" t="s" s="2">
-        <v>679</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G166" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>614</v>
+        <v>104</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>680</v>
+        <v>105</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>607</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N166" s="2"/>
+      <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>82</v>
       </c>
@@ -22737,31 +22780,31 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>602</v>
+        <v>107</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>609</v>
+        <v>108</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>611</v>
+        <v>82</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -22769,21 +22812,21 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>682</v>
+        <v>634</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>82</v>
@@ -22795,15 +22838,17 @@
         <v>82</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N167" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N167" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>82</v>
@@ -22840,31 +22885,31 @@
         <v>82</v>
       </c>
       <c r="AB167" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC167" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE167" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>108</v>
@@ -22884,10 +22929,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>683</v>
+        <v>636</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>620</v>
+        <v>637</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22898,28 +22943,32 @@
         <v>90</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I168" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>198</v>
+        <v>638</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N168" s="2"/>
-      <c r="O168" s="2"/>
+        <v>639</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="O168" t="s" s="2">
+        <v>641</v>
+      </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
       </c>
@@ -22928,7 +22977,7 @@
         <v>82</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>82</v>
+        <v>642</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>82</v>
@@ -22943,46 +22992,46 @@
         <v>82</v>
       </c>
       <c r="X168" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>82</v>
+        <v>643</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>82</v>
+        <v>644</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC168" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>118</v>
+        <v>645</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>82</v>
@@ -22991,52 +23040,54 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>82</v>
+        <v>646</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>684</v>
+        <v>647</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="C169" t="s" s="2">
-        <v>685</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G169" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J169" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J169" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K169" t="s" s="2">
-        <v>686</v>
+        <v>104</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>687</v>
+        <v>649</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="N169" s="2"/>
-      <c r="O169" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="N169" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="O169" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P169" t="s" s="2">
         <v>82</v>
       </c>
@@ -23084,22 +23135,22 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>118</v>
+        <v>652</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>82</v>
@@ -23108,7 +23159,7 @@
         <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>82</v>
+        <v>653</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
@@ -23116,18 +23167,18 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>689</v>
+        <v>654</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>622</v>
+        <v>655</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>82</v>
+        <v>656</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G170" t="s" s="2">
         <v>90</v>
@@ -23136,26 +23187,24 @@
         <v>82</v>
       </c>
       <c r="I170" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J170" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>173</v>
+        <v>104</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>623</v>
+        <v>657</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>624</v>
+        <v>658</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>626</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>82</v>
       </c>
@@ -23164,7 +23213,7 @@
         <v>82</v>
       </c>
       <c r="S170" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="T170" t="s" s="2">
         <v>82</v>
@@ -23179,13 +23228,13 @@
         <v>82</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>628</v>
+        <v>82</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>629</v>
+        <v>82</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>82</v>
@@ -23203,7 +23252,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -23218,7 +23267,7 @@
         <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>314</v>
+        <v>661</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>82</v>
@@ -23227,7 +23276,7 @@
         <v>82</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>631</v>
+        <v>662</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>82</v>
@@ -23235,21 +23284,21 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>690</v>
+        <v>663</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>633</v>
+        <v>664</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>82</v>
+        <v>665</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>82</v>
@@ -23264,17 +23313,15 @@
         <v>104</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>634</v>
+        <v>666</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>635</v>
+        <v>667</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>668</v>
+      </c>
+      <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>82</v>
       </c>
@@ -23322,13 +23369,13 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>637</v>
+        <v>669</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>82</v>
@@ -23337,7 +23384,7 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>334</v>
+        <v>670</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>82</v>
@@ -23346,7 +23393,7 @@
         <v>82</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>638</v>
+        <v>671</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>82</v>
@@ -23354,21 +23401,21 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>691</v>
+        <v>672</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>640</v>
+        <v>673</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>641</v>
+        <v>82</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>82</v>
@@ -23383,14 +23430,12 @@
         <v>104</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>642</v>
+        <v>674</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>644</v>
-      </c>
+        <v>675</v>
+      </c>
+      <c r="N172" s="2"/>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>82</v>
@@ -23439,13 +23484,13 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>645</v>
+        <v>676</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI172" t="s" s="2">
         <v>82</v>
@@ -23454,7 +23499,7 @@
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>646</v>
+        <v>677</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>82</v>
@@ -23463,7 +23508,7 @@
         <v>82</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>647</v>
+        <v>678</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>82</v>
@@ -23471,21 +23516,21 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>649</v>
+        <v>680</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>650</v>
+        <v>82</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>82</v>
@@ -23500,14 +23545,12 @@
         <v>104</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>653</v>
-      </c>
+        <v>682</v>
+      </c>
+      <c r="N173" s="2"/>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>82</v>
@@ -23556,7 +23599,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>654</v>
+        <v>683</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23571,7 +23614,7 @@
         <v>102</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>655</v>
+        <v>684</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>82</v>
@@ -23580,7 +23623,7 @@
         <v>82</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>656</v>
+        <v>685</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>82</v>
@@ -23588,10 +23631,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>658</v>
+        <v>687</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23602,7 +23645,7 @@
         <v>80</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>82</v>
@@ -23614,16 +23657,18 @@
         <v>91</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>104</v>
+        <v>390</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>659</v>
+        <v>688</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>660</v>
+        <v>689</v>
       </c>
       <c r="N174" s="2"/>
-      <c r="O174" s="2"/>
+      <c r="O174" t="s" s="2">
+        <v>690</v>
+      </c>
       <c r="P174" t="s" s="2">
         <v>82</v>
       </c>
@@ -23671,13 +23716,13 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>661</v>
+        <v>691</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI174" t="s" s="2">
         <v>82</v>
@@ -23686,7 +23731,7 @@
         <v>102</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>662</v>
+        <v>396</v>
       </c>
       <c r="AL174" t="s" s="2">
         <v>82</v>
@@ -23695,32 +23740,34 @@
         <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>663</v>
+        <v>692</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="175" hidden="true">
+    <row r="175">
       <c r="A175" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="C175" s="2"/>
+        <v>617</v>
+      </c>
+      <c r="C175" t="s" s="2">
+        <v>694</v>
+      </c>
       <c r="D175" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H175" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I175" t="s" s="2">
         <v>82</v>
@@ -23729,16 +23776,20 @@
         <v>91</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>104</v>
+        <v>629</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>666</v>
+        <v>695</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="N175" s="2"/>
-      <c r="O175" s="2"/>
+        <v>696</v>
+      </c>
+      <c r="N175" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="O175" t="s" s="2">
+        <v>622</v>
+      </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
       </c>
@@ -23786,7 +23837,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>668</v>
+        <v>617</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23801,16 +23852,16 @@
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>669</v>
+        <v>624</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>670</v>
+        <v>626</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>82</v>
@@ -23818,10 +23869,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>672</v>
+        <v>633</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23841,21 +23892,19 @@
         <v>82</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>390</v>
+        <v>104</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>673</v>
+        <v>105</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>674</v>
+        <v>106</v>
       </c>
       <c r="N176" s="2"/>
-      <c r="O176" t="s" s="2">
-        <v>675</v>
-      </c>
+      <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
         <v>82</v>
       </c>
@@ -23903,7 +23952,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>676</v>
+        <v>107</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23915,10 +23964,10 @@
         <v>82</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>396</v>
+        <v>108</v>
       </c>
       <c r="AL176" t="s" s="2">
         <v>82</v>
@@ -23927,7 +23976,7 @@
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>677</v>
+        <v>82</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>82</v>
@@ -23935,10 +23984,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>697</v>
+        <v>635</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23946,7 +23995,7 @@
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G177" t="s" s="2">
         <v>81</v>
@@ -23958,23 +24007,19 @@
         <v>82</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>698</v>
+        <v>111</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>699</v>
+        <v>198</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>702</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N177" s="2"/>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>82</v>
       </c>
@@ -24010,19 +24055,19 @@
         <v>82</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC177" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD177" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>697</v>
+        <v>118</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -24034,19 +24079,19 @@
         <v>82</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>703</v>
+        <v>82</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>704</v>
+        <v>82</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>705</v>
+        <v>82</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>82</v>
@@ -24054,12 +24099,14 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="C178" s="2"/>
+        <v>635</v>
+      </c>
+      <c r="C178" t="s" s="2">
+        <v>700</v>
+      </c>
       <c r="D178" t="s" s="2">
         <v>82</v>
       </c>
@@ -24077,23 +24124,19 @@
         <v>82</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>173</v>
+        <v>701</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>710</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="N178" s="2"/>
+      <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>82</v>
       </c>
@@ -24117,11 +24160,13 @@
         <v>82</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="Y178" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y178" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z178" t="s" s="2">
-        <v>711</v>
+        <v>82</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>82</v>
@@ -24139,42 +24184,42 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>706</v>
+        <v>118</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>712</v>
+        <v>82</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>713</v>
+        <v>82</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>714</v>
+        <v>82</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>715</v>
+        <v>637</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24188,28 +24233,28 @@
         <v>90</v>
       </c>
       <c r="H179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I179" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I179" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J179" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>242</v>
+        <v>173</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>716</v>
+        <v>638</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>717</v>
+        <v>639</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>718</v>
+        <v>640</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>719</v>
+        <v>641</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>82</v>
@@ -24219,7 +24264,7 @@
         <v>82</v>
       </c>
       <c r="S179" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="T179" t="s" s="2">
         <v>82</v>
@@ -24234,13 +24279,13 @@
         <v>82</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>82</v>
+        <v>643</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>82</v>
+        <v>644</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>82</v>
@@ -24258,7 +24303,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>715</v>
+        <v>645</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24273,27 +24318,27 @@
         <v>102</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>720</v>
+        <v>314</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>721</v>
+        <v>82</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>722</v>
+        <v>646</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>723</v>
+        <v>82</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>724</v>
+        <v>705</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>724</v>
+        <v>648</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24310,25 +24355,25 @@
         <v>82</v>
       </c>
       <c r="I180" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J180" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>725</v>
+        <v>104</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>726</v>
+        <v>649</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>727</v>
+        <v>650</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>728</v>
+        <v>651</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>729</v>
+        <v>331</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -24377,7 +24422,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>724</v>
+        <v>652</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -24392,16 +24437,16 @@
         <v>102</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>730</v>
+        <v>334</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>731</v>
+        <v>653</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>82</v>
@@ -24409,21 +24454,21 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>732</v>
+        <v>706</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>732</v>
+        <v>655</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>82</v>
+        <v>656</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>82</v>
@@ -24435,20 +24480,18 @@
         <v>91</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>292</v>
+        <v>104</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>733</v>
+        <v>657</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>734</v>
+        <v>658</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>736</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
         <v>82</v>
       </c>
@@ -24496,13 +24539,13 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>732</v>
+        <v>660</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>82</v>
@@ -24511,16 +24554,16 @@
         <v>102</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>737</v>
+        <v>661</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>738</v>
+        <v>82</v>
       </c>
       <c r="AM181" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>739</v>
+        <v>662</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>82</v>
@@ -24528,18 +24571,18 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>740</v>
+        <v>707</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>740</v>
+        <v>664</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>82</v>
+        <v>665</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G182" t="s" s="2">
         <v>90</v>
@@ -24551,21 +24594,21 @@
         <v>82</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>434</v>
+        <v>104</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>741</v>
+        <v>708</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="N182" s="2"/>
-      <c r="O182" t="s" s="2">
-        <v>743</v>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
         <v>82</v>
       </c>
@@ -24589,11 +24632,13 @@
         <v>82</v>
       </c>
       <c r="X182" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y182" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y182" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z182" t="s" s="2">
-        <v>744</v>
+        <v>82</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>82</v>
@@ -24611,13 +24656,13 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>740</v>
+        <v>669</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI182" t="s" s="2">
         <v>82</v>
@@ -24626,16 +24671,16 @@
         <v>102</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>745</v>
+        <v>670</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>746</v>
+        <v>82</v>
       </c>
       <c r="AM182" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>747</v>
+        <v>671</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>82</v>
@@ -24643,10 +24688,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>748</v>
+        <v>709</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>748</v>
+        <v>673</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24657,7 +24702,7 @@
         <v>80</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>82</v>
@@ -24666,23 +24711,19 @@
         <v>82</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>749</v>
+        <v>104</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>750</v>
+        <v>674</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>753</v>
-      </c>
+        <v>675</v>
+      </c>
+      <c r="N183" s="2"/>
+      <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>82</v>
       </c>
@@ -24730,13 +24771,13 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>748</v>
+        <v>676</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI183" t="s" s="2">
         <v>82</v>
@@ -24745,16 +24786,16 @@
         <v>102</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>754</v>
+        <v>677</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>755</v>
+        <v>678</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>
@@ -24762,10 +24803,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>756</v>
+        <v>710</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>756</v>
+        <v>680</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24785,23 +24826,19 @@
         <v>82</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>757</v>
+        <v>104</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>758</v>
+        <v>681</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>761</v>
-      </c>
+        <v>682</v>
+      </c>
+      <c r="N184" s="2"/>
+      <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
         <v>82</v>
       </c>
@@ -24849,7 +24886,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>756</v>
+        <v>683</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -24864,16 +24901,16 @@
         <v>102</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>762</v>
+        <v>684</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>763</v>
+        <v>685</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>82</v>
@@ -24881,10 +24918,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>764</v>
+        <v>711</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>764</v>
+        <v>687</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24895,7 +24932,7 @@
         <v>80</v>
       </c>
       <c r="G185" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H185" t="s" s="2">
         <v>82</v>
@@ -24904,22 +24941,20 @@
         <v>82</v>
       </c>
       <c r="J185" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>765</v>
+        <v>390</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>766</v>
+        <v>688</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>768</v>
-      </c>
+        <v>689</v>
+      </c>
+      <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>769</v>
+        <v>690</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>82</v>
@@ -24968,31 +25003,31 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>764</v>
+        <v>691</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH185" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI185" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ185" t="s" s="2">
-        <v>770</v>
+        <v>102</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>771</v>
+        <v>396</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM185" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>82</v>
+        <v>692</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>82</v>
@@ -25000,10 +25035,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>772</v>
+        <v>712</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>772</v>
+        <v>712</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25014,7 +25049,7 @@
         <v>80</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H186" t="s" s="2">
         <v>82</v>
@@ -25023,19 +25058,23 @@
         <v>82</v>
       </c>
       <c r="J186" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>104</v>
+        <v>713</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>105</v>
+        <v>714</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N186" s="2"/>
-      <c r="O186" s="2"/>
+        <v>715</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="O186" t="s" s="2">
+        <v>717</v>
+      </c>
       <c r="P186" t="s" s="2">
         <v>82</v>
       </c>
@@ -25083,42 +25122,42 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>107</v>
+        <v>712</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH186" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI186" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ186" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK186" t="s" s="2">
-        <v>108</v>
+        <v>718</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>82</v>
+        <v>719</v>
       </c>
       <c r="AM186" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>82</v>
+        <v>720</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="187" hidden="true">
+    <row r="187">
       <c r="A187" t="s" s="2">
-        <v>773</v>
+        <v>721</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>773</v>
+        <v>721</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25126,31 +25165,35 @@
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H187" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I187" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J187" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>198</v>
+        <v>722</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N187" s="2"/>
-      <c r="O187" s="2"/>
+        <v>723</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="O187" t="s" s="2">
+        <v>725</v>
+      </c>
       <c r="P187" t="s" s="2">
         <v>82</v>
       </c>
@@ -25174,98 +25217,100 @@
         <v>82</v>
       </c>
       <c r="X187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y187" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="Y187" s="2"/>
       <c r="Z187" t="s" s="2">
-        <v>82</v>
+        <v>726</v>
       </c>
       <c r="AA187" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB187" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC187" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD187" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE187" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>118</v>
+        <v>721</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH187" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI187" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>82</v>
+        <v>727</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>82</v>
+        <v>728</v>
       </c>
       <c r="AM187" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>82</v>
+        <v>729</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="188" hidden="true">
+    <row r="188">
       <c r="A188" t="s" s="2">
-        <v>774</v>
+        <v>730</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="C188" t="s" s="2">
-        <v>775</v>
-      </c>
+        <v>730</v>
+      </c>
+      <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G188" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H188" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>776</v>
+        <v>242</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>777</v>
+        <v>731</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="N188" s="2"/>
-      <c r="O188" s="2"/>
+        <v>732</v>
+      </c>
+      <c r="N188" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="O188" t="s" s="2">
+        <v>734</v>
+      </c>
       <c r="P188" t="s" s="2">
         <v>82</v>
       </c>
@@ -25313,46 +25358,44 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>118</v>
+        <v>730</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH188" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>82</v>
+        <v>735</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>82</v>
+        <v>736</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>82</v>
+        <v>737</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>82</v>
+        <v>738</v>
       </c>
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>779</v>
+        <v>739</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="C189" t="s" s="2">
-        <v>780</v>
-      </c>
+        <v>739</v>
+      </c>
+      <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
         <v>82</v>
       </c>
@@ -25367,22 +25410,26 @@
         <v>82</v>
       </c>
       <c r="I189" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J189" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="N189" s="2"/>
-      <c r="O189" s="2"/>
+        <v>742</v>
+      </c>
+      <c r="N189" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="O189" t="s" s="2">
+        <v>744</v>
+      </c>
       <c r="P189" t="s" s="2">
         <v>82</v>
       </c>
@@ -25430,31 +25477,31 @@
         <v>82</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>118</v>
+        <v>739</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>82</v>
+        <v>745</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM189" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>82</v>
+        <v>746</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>82</v>
@@ -25462,14 +25509,14 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>784</v>
+        <v>747</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>784</v>
+        <v>747</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>785</v>
+        <v>82</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
@@ -25482,25 +25529,25 @@
         <v>82</v>
       </c>
       <c r="I190" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J190" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>111</v>
+        <v>292</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>786</v>
+        <v>748</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>787</v>
+        <v>749</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>114</v>
+        <v>750</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>401</v>
+        <v>751</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>82</v>
@@ -25549,7 +25596,7 @@
         <v>82</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>788</v>
+        <v>747</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -25561,19 +25608,19 @@
         <v>82</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>196</v>
+        <v>752</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>82</v>
+        <v>753</v>
       </c>
       <c r="AM190" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>82</v>
+        <v>754</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>82</v>
@@ -25581,10 +25628,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>789</v>
+        <v>755</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>789</v>
+        <v>755</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25595,7 +25642,7 @@
         <v>80</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H191" t="s" s="2">
         <v>82</v>
@@ -25610,14 +25657,14 @@
         <v>434</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>790</v>
+        <v>756</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>791</v>
+        <v>757</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" t="s" s="2">
-        <v>792</v>
+        <v>758</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>82</v>
@@ -25644,33 +25691,33 @@
       <c r="X191" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="Y191" t="s" s="2">
-        <v>793</v>
-      </c>
+      <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>794</v>
+        <v>759</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="AC191" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC191" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD191" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE191" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>789</v>
+        <v>755</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>82</v>
@@ -25679,16 +25726,16 @@
         <v>102</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>796</v>
+        <v>760</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>108</v>
+        <v>761</v>
       </c>
       <c r="AM191" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>797</v>
+        <v>762</v>
       </c>
       <c r="AO191" t="s" s="2">
         <v>82</v>
@@ -25696,14 +25743,12 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>798</v>
+        <v>763</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="C192" t="s" s="2">
-        <v>799</v>
-      </c>
+        <v>763</v>
+      </c>
+      <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
         <v>82</v>
       </c>
@@ -25724,17 +25769,19 @@
         <v>82</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>434</v>
+        <v>764</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>800</v>
+        <v>765</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="N192" s="2"/>
+        <v>766</v>
+      </c>
+      <c r="N192" t="s" s="2">
+        <v>767</v>
+      </c>
       <c r="O192" t="s" s="2">
-        <v>792</v>
+        <v>768</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>82</v>
@@ -25759,11 +25806,13 @@
         <v>82</v>
       </c>
       <c r="X192" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y192" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y192" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z192" t="s" s="2">
-        <v>801</v>
+        <v>82</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>82</v>
@@ -25781,13 +25830,13 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>789</v>
+        <v>763</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI192" t="s" s="2">
         <v>82</v>
@@ -25796,7 +25845,7 @@
         <v>102</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>796</v>
+        <v>769</v>
       </c>
       <c r="AL192" t="s" s="2">
         <v>108</v>
@@ -25805,7 +25854,7 @@
         <v>82</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>82</v>
@@ -25813,10 +25862,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>802</v>
+        <v>771</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>803</v>
+        <v>771</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25827,7 +25876,7 @@
         <v>80</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H193" t="s" s="2">
         <v>82</v>
@@ -25839,16 +25888,20 @@
         <v>82</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>104</v>
+        <v>772</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>105</v>
+        <v>773</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N193" s="2"/>
-      <c r="O193" s="2"/>
+        <v>774</v>
+      </c>
+      <c r="N193" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="O193" t="s" s="2">
+        <v>776</v>
+      </c>
       <c r="P193" t="s" s="2">
         <v>82</v>
       </c>
@@ -25896,31 +25949,31 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>107</v>
+        <v>771</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI193" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK193" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="AL193" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AL193" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM193" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>82</v>
+        <v>778</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>82</v>
@@ -25928,10 +25981,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>804</v>
+        <v>779</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>805</v>
+        <v>779</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25939,7 +25992,7 @@
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G194" t="s" s="2">
         <v>81</v>
@@ -25954,16 +26007,20 @@
         <v>82</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>111</v>
+        <v>780</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>198</v>
+        <v>781</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N194" s="2"/>
-      <c r="O194" s="2"/>
+        <v>782</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>784</v>
+      </c>
       <c r="P194" t="s" s="2">
         <v>82</v>
       </c>
@@ -25999,19 +26056,19 @@
         <v>82</v>
       </c>
       <c r="AB194" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC194" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD194" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE194" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>118</v>
+        <v>779</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -26023,13 +26080,13 @@
         <v>82</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>119</v>
+        <v>785</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>82</v>
+        <v>786</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>82</v>
@@ -26043,20 +26100,18 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C195" t="s" s="2">
-        <v>807</v>
-      </c>
+        <v>787</v>
+      </c>
+      <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G195" t="s" s="2">
         <v>90</v>
@@ -26071,13 +26126,13 @@
         <v>82</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>808</v>
+        <v>104</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>809</v>
+        <v>105</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>810</v>
+        <v>106</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -26128,22 +26183,22 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI195" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>82</v>
@@ -26160,10 +26215,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>811</v>
+        <v>788</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>812</v>
+        <v>788</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26174,7 +26229,7 @@
         <v>80</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>82</v>
@@ -26186,13 +26241,13 @@
         <v>82</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>106</v>
+        <v>199</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -26231,34 +26286,32 @@
         <v>82</v>
       </c>
       <c r="AB196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC196" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="AC196" s="2"/>
       <c r="AD196" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE196" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI196" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AL196" t="s" s="2">
         <v>82</v>
@@ -26275,12 +26328,14 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>813</v>
+        <v>789</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="C197" s="2"/>
+        <v>788</v>
+      </c>
+      <c r="C197" t="s" s="2">
+        <v>790</v>
+      </c>
       <c r="D197" t="s" s="2">
         <v>82</v>
       </c>
@@ -26289,7 +26344,7 @@
         <v>80</v>
       </c>
       <c r="G197" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H197" t="s" s="2">
         <v>82</v>
@@ -26301,13 +26356,13 @@
         <v>82</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>111</v>
+        <v>791</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>198</v>
+        <v>792</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>199</v>
+        <v>793</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -26346,16 +26401,16 @@
         <v>82</v>
       </c>
       <c r="AB197" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC197" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD197" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE197" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
         <v>118</v>
@@ -26367,7 +26422,7 @@
         <v>81</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>119</v>
@@ -26390,18 +26445,20 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="C198" s="2"/>
+        <v>788</v>
+      </c>
+      <c r="C198" t="s" s="2">
+        <v>795</v>
+      </c>
       <c r="D198" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G198" t="s" s="2">
         <v>90</v>
@@ -26416,24 +26473,22 @@
         <v>82</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>132</v>
+        <v>796</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>225</v>
+        <v>797</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N198" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>798</v>
+      </c>
+      <c r="N198" s="2"/>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q198" s="2"/>
       <c r="R198" t="s" s="2">
-        <v>817</v>
+        <v>82</v>
       </c>
       <c r="S198" t="s" s="2">
         <v>82</v>
@@ -26475,22 +26530,22 @@
         <v>82</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>228</v>
+        <v>118</v>
       </c>
       <c r="AG198" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH198" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI198" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="AJ198" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AK198" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AL198" t="s" s="2">
         <v>82</v>
@@ -26507,42 +26562,46 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>818</v>
+        <v>799</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>819</v>
+        <v>799</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
-        <v>82</v>
+        <v>800</v>
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G199" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H199" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I199" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J199" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>173</v>
+        <v>111</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>231</v>
+        <v>801</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N199" s="2"/>
-      <c r="O199" s="2"/>
+        <v>802</v>
+      </c>
+      <c r="N199" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O199" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="P199" t="s" s="2">
         <v>82</v>
       </c>
@@ -26551,7 +26610,7 @@
         <v>82</v>
       </c>
       <c r="S199" t="s" s="2">
-        <v>799</v>
+        <v>82</v>
       </c>
       <c r="T199" t="s" s="2">
         <v>82</v>
@@ -26566,11 +26625,13 @@
         <v>82</v>
       </c>
       <c r="X199" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="Y199" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y199" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z199" t="s" s="2">
-        <v>820</v>
+        <v>82</v>
       </c>
       <c r="AA199" t="s" s="2">
         <v>82</v>
@@ -26588,19 +26649,19 @@
         <v>82</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>234</v>
+        <v>803</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH199" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI199" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK199" t="s" s="2">
         <v>196</v>
@@ -26620,10 +26681,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>821</v>
+        <v>804</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>822</v>
+        <v>804</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26643,22 +26704,20 @@
         <v>82</v>
       </c>
       <c r="J200" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>151</v>
+        <v>434</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>823</v>
+        <v>805</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>825</v>
-      </c>
+        <v>806</v>
+      </c>
+      <c r="N200" s="2"/>
       <c r="O200" t="s" s="2">
-        <v>826</v>
+        <v>807</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>82</v>
@@ -26683,31 +26742,29 @@
         <v>82</v>
       </c>
       <c r="X200" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y200" t="s" s="2">
-        <v>82</v>
+        <v>808</v>
       </c>
       <c r="Z200" t="s" s="2">
-        <v>82</v>
+        <v>809</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC200" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>810</v>
+      </c>
+      <c r="AC200" s="2"/>
       <c r="AD200" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE200" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>827</v>
+        <v>804</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -26722,16 +26779,16 @@
         <v>102</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>828</v>
+        <v>811</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>829</v>
+        <v>812</v>
       </c>
       <c r="AO200" t="s" s="2">
         <v>82</v>
@@ -26739,12 +26796,14 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>830</v>
+        <v>813</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="C201" s="2"/>
+        <v>804</v>
+      </c>
+      <c r="C201" t="s" s="2">
+        <v>814</v>
+      </c>
       <c r="D201" t="s" s="2">
         <v>82</v>
       </c>
@@ -26762,22 +26821,20 @@
         <v>82</v>
       </c>
       <c r="J201" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>104</v>
+        <v>434</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>832</v>
+        <v>815</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>834</v>
-      </c>
+        <v>806</v>
+      </c>
+      <c r="N201" s="2"/>
       <c r="O201" t="s" s="2">
-        <v>835</v>
+        <v>807</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>82</v>
@@ -26802,13 +26859,11 @@
         <v>82</v>
       </c>
       <c r="X201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y201" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y201" s="2"/>
       <c r="Z201" t="s" s="2">
-        <v>82</v>
+        <v>816</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>82</v>
@@ -26826,13 +26881,13 @@
         <v>82</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>836</v>
+        <v>804</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH201" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI201" t="s" s="2">
         <v>82</v>
@@ -26841,16 +26896,16 @@
         <v>102</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>837</v>
+        <v>811</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>838</v>
+        <v>812</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>82</v>
@@ -26858,14 +26913,12 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>839</v>
+        <v>817</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="C202" t="s" s="2">
-        <v>840</v>
-      </c>
+        <v>818</v>
+      </c>
+      <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
         <v>82</v>
       </c>
@@ -26886,18 +26939,16 @@
         <v>82</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>434</v>
+        <v>104</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>841</v>
+        <v>105</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>791</v>
+        <v>106</v>
       </c>
       <c r="N202" s="2"/>
-      <c r="O202" t="s" s="2">
-        <v>792</v>
-      </c>
+      <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
         <v>82</v>
       </c>
@@ -26921,11 +26972,13 @@
         <v>82</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y202" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y202" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z202" t="s" s="2">
-        <v>842</v>
+        <v>82</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>82</v>
@@ -26943,31 +26996,31 @@
         <v>82</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>789</v>
+        <v>107</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH202" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI202" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ202" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>796</v>
+        <v>108</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM202" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>797</v>
+        <v>82</v>
       </c>
       <c r="AO202" t="s" s="2">
         <v>82</v>
@@ -26975,10 +27028,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>843</v>
+        <v>819</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>803</v>
+        <v>820</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26986,10 +27039,10 @@
       </c>
       <c r="E203" s="2"/>
       <c r="F203" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G203" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H203" t="s" s="2">
         <v>82</v>
@@ -27001,13 +27054,13 @@
         <v>82</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>106</v>
+        <v>199</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -27046,34 +27099,34 @@
         <v>82</v>
       </c>
       <c r="AB203" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC203" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD203" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE203" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH203" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI203" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AL203" t="s" s="2">
         <v>82</v>
@@ -27090,12 +27143,14 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>844</v>
+        <v>821</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C204" s="2"/>
+        <v>820</v>
+      </c>
+      <c r="C204" t="s" s="2">
+        <v>822</v>
+      </c>
       <c r="D204" t="s" s="2">
         <v>82</v>
       </c>
@@ -27104,7 +27159,7 @@
         <v>90</v>
       </c>
       <c r="G204" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H204" t="s" s="2">
         <v>82</v>
@@ -27116,13 +27171,13 @@
         <v>82</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>111</v>
+        <v>823</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>198</v>
+        <v>824</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>199</v>
+        <v>825</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -27161,16 +27216,16 @@
         <v>82</v>
       </c>
       <c r="AB204" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC204" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD204" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE204" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF204" t="s" s="2">
         <v>118</v>
@@ -27205,20 +27260,18 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>845</v>
+        <v>826</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C205" t="s" s="2">
-        <v>807</v>
-      </c>
+        <v>827</v>
+      </c>
+      <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E205" s="2"/>
       <c r="F205" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G205" t="s" s="2">
         <v>90</v>
@@ -27233,13 +27286,13 @@
         <v>82</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>808</v>
+        <v>104</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>809</v>
+        <v>105</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>810</v>
+        <v>106</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -27290,22 +27343,22 @@
         <v>82</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI205" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ205" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AL205" t="s" s="2">
         <v>82</v>
@@ -27322,10 +27375,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>846</v>
+        <v>828</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>812</v>
+        <v>829</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27336,7 +27389,7 @@
         <v>80</v>
       </c>
       <c r="G206" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H206" t="s" s="2">
         <v>82</v>
@@ -27348,13 +27401,13 @@
         <v>82</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>106</v>
+        <v>199</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -27393,34 +27446,34 @@
         <v>82</v>
       </c>
       <c r="AB206" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC206" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD206" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE206" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI206" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AL206" t="s" s="2">
         <v>82</v>
@@ -27437,10 +27490,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>847</v>
+        <v>830</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>814</v>
+        <v>831</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27448,10 +27501,10 @@
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G207" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H207" t="s" s="2">
         <v>82</v>
@@ -27463,22 +27516,24 @@
         <v>82</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N207" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N207" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q207" s="2"/>
       <c r="R207" t="s" s="2">
-        <v>82</v>
+        <v>832</v>
       </c>
       <c r="S207" t="s" s="2">
         <v>82</v>
@@ -27508,34 +27563,34 @@
         <v>82</v>
       </c>
       <c r="AB207" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC207" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD207" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE207" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>118</v>
+        <v>228</v>
       </c>
       <c r="AG207" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH207" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI207" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AL207" t="s" s="2">
         <v>82</v>
@@ -27552,10 +27607,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>816</v>
+        <v>834</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27563,7 +27618,7 @@
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G208" t="s" s="2">
         <v>90</v>
@@ -27578,27 +27633,25 @@
         <v>82</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q208" s="2"/>
       <c r="R208" t="s" s="2">
-        <v>817</v>
+        <v>82</v>
       </c>
       <c r="S208" t="s" s="2">
-        <v>82</v>
+        <v>814</v>
       </c>
       <c r="T208" t="s" s="2">
         <v>82</v>
@@ -27613,13 +27666,11 @@
         <v>82</v>
       </c>
       <c r="X208" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y208" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="Y208" s="2"/>
       <c r="Z208" t="s" s="2">
-        <v>82</v>
+        <v>835</v>
       </c>
       <c r="AA208" t="s" s="2">
         <v>82</v>
@@ -27637,10 +27688,10 @@
         <v>82</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>90</v>
@@ -27649,7 +27700,7 @@
         <v>82</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>196</v>
@@ -27669,10 +27720,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>849</v>
+        <v>836</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>819</v>
+        <v>837</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27683,7 +27734,7 @@
         <v>80</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>82</v>
@@ -27692,19 +27743,23 @@
         <v>82</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>231</v>
+        <v>838</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N209" s="2"/>
-      <c r="O209" s="2"/>
+        <v>839</v>
+      </c>
+      <c r="N209" t="s" s="2">
+        <v>840</v>
+      </c>
+      <c r="O209" t="s" s="2">
+        <v>841</v>
+      </c>
       <c r="P209" t="s" s="2">
         <v>82</v>
       </c>
@@ -27713,7 +27768,7 @@
         <v>82</v>
       </c>
       <c r="S209" t="s" s="2">
-        <v>840</v>
+        <v>82</v>
       </c>
       <c r="T209" t="s" s="2">
         <v>82</v>
@@ -27728,11 +27783,13 @@
         <v>82</v>
       </c>
       <c r="X209" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="Y209" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y209" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z209" t="s" s="2">
-        <v>820</v>
+        <v>82</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>82</v>
@@ -27750,13 +27807,13 @@
         <v>82</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>234</v>
+        <v>842</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>82</v>
@@ -27765,7 +27822,7 @@
         <v>102</v>
       </c>
       <c r="AK209" t="s" s="2">
-        <v>196</v>
+        <v>843</v>
       </c>
       <c r="AL209" t="s" s="2">
         <v>82</v>
@@ -27774,7 +27831,7 @@
         <v>82</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>82</v>
+        <v>844</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>82</v>
@@ -27782,10 +27839,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>822</v>
+        <v>846</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27796,7 +27853,7 @@
         <v>80</v>
       </c>
       <c r="G210" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H210" t="s" s="2">
         <v>82</v>
@@ -27808,19 +27865,19 @@
         <v>91</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>823</v>
+        <v>847</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>824</v>
+        <v>848</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>825</v>
+        <v>849</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>826</v>
+        <v>850</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>82</v>
@@ -27869,13 +27926,13 @@
         <v>82</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>827</v>
+        <v>851</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI210" t="s" s="2">
         <v>82</v>
@@ -27884,7 +27941,7 @@
         <v>102</v>
       </c>
       <c r="AK210" t="s" s="2">
-        <v>828</v>
+        <v>852</v>
       </c>
       <c r="AL210" t="s" s="2">
         <v>82</v>
@@ -27893,7 +27950,7 @@
         <v>82</v>
       </c>
       <c r="AN210" t="s" s="2">
-        <v>829</v>
+        <v>853</v>
       </c>
       <c r="AO210" t="s" s="2">
         <v>82</v>
@@ -27901,12 +27958,14 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="C211" s="2"/>
+        <v>804</v>
+      </c>
+      <c r="C211" t="s" s="2">
+        <v>855</v>
+      </c>
       <c r="D211" t="s" s="2">
         <v>82</v>
       </c>
@@ -27924,22 +27983,20 @@
         <v>82</v>
       </c>
       <c r="J211" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>104</v>
+        <v>434</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>832</v>
+        <v>856</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="N211" t="s" s="2">
-        <v>834</v>
-      </c>
+        <v>806</v>
+      </c>
+      <c r="N211" s="2"/>
       <c r="O211" t="s" s="2">
-        <v>835</v>
+        <v>807</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>82</v>
@@ -27964,13 +28021,11 @@
         <v>82</v>
       </c>
       <c r="X211" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y211" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y211" s="2"/>
       <c r="Z211" t="s" s="2">
-        <v>82</v>
+        <v>857</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>82</v>
@@ -27988,13 +28043,13 @@
         <v>82</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>836</v>
+        <v>804</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>82</v>
@@ -28003,16 +28058,16 @@
         <v>102</v>
       </c>
       <c r="AK211" t="s" s="2">
-        <v>837</v>
+        <v>811</v>
       </c>
       <c r="AL211" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM211" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>838</v>
+        <v>812</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>82</v>
@@ -28020,10 +28075,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>852</v>
+        <v>818</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28046,18 +28101,16 @@
         <v>82</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>603</v>
+        <v>104</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>853</v>
+        <v>105</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>854</v>
+        <v>106</v>
       </c>
       <c r="N212" s="2"/>
-      <c r="O212" t="s" s="2">
-        <v>855</v>
-      </c>
+      <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>82</v>
       </c>
@@ -28105,7 +28158,7 @@
         <v>82</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>852</v>
+        <v>107</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -28117,19 +28170,19 @@
         <v>82</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>609</v>
+        <v>108</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM212" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>856</v>
+        <v>82</v>
       </c>
       <c r="AO212" t="s" s="2">
         <v>82</v>
@@ -28137,10 +28190,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>857</v>
+        <v>820</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28148,7 +28201,7 @@
       </c>
       <c r="E213" s="2"/>
       <c r="F213" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G213" t="s" s="2">
         <v>81</v>
@@ -28163,20 +28216,16 @@
         <v>82</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>698</v>
+        <v>111</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>858</v>
+        <v>198</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N213" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="O213" t="s" s="2">
-        <v>702</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N213" s="2"/>
+      <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
         <v>82</v>
       </c>
@@ -28212,19 +28261,19 @@
         <v>82</v>
       </c>
       <c r="AB213" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC213" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD213" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE213" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>857</v>
+        <v>118</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -28236,19 +28285,19 @@
         <v>82</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>703</v>
+        <v>82</v>
       </c>
       <c r="AL213" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM213" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>861</v>
+        <v>82</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>82</v>
@@ -28256,18 +28305,20 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="C214" s="2"/>
+        <v>820</v>
+      </c>
+      <c r="C214" t="s" s="2">
+        <v>822</v>
+      </c>
       <c r="D214" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G214" t="s" s="2">
         <v>90</v>
@@ -28282,18 +28333,16 @@
         <v>82</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>863</v>
+        <v>823</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>864</v>
+        <v>824</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>865</v>
+        <v>825</v>
       </c>
       <c r="N214" s="2"/>
-      <c r="O214" t="s" s="2">
-        <v>866</v>
-      </c>
+      <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>82</v>
       </c>
@@ -28341,31 +28390,31 @@
         <v>82</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>862</v>
+        <v>118</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH214" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI214" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ214" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK214" t="s" s="2">
-        <v>737</v>
+        <v>82</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM214" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>867</v>
+        <v>82</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>82</v>
@@ -28373,10 +28422,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>868</v>
+        <v>827</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28399,18 +28448,16 @@
         <v>82</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>173</v>
+        <v>104</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>869</v>
+        <v>105</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>870</v>
+        <v>106</v>
       </c>
       <c r="N215" s="2"/>
-      <c r="O215" t="s" s="2">
-        <v>871</v>
-      </c>
+      <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>82</v>
       </c>
@@ -28434,13 +28481,13 @@
         <v>82</v>
       </c>
       <c r="X215" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="Y215" t="s" s="2">
-        <v>872</v>
+        <v>82</v>
       </c>
       <c r="Z215" t="s" s="2">
-        <v>873</v>
+        <v>82</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>82</v>
@@ -28458,7 +28505,7 @@
         <v>82</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>868</v>
+        <v>107</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
@@ -28470,19 +28517,19 @@
         <v>82</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK215" t="s" s="2">
-        <v>712</v>
+        <v>108</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM215" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>874</v>
+        <v>82</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>82</v>
@@ -28490,10 +28537,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>875</v>
+        <v>829</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28504,7 +28551,7 @@
         <v>80</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>82</v>
@@ -28516,18 +28563,16 @@
         <v>82</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>472</v>
+        <v>111</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>876</v>
+        <v>198</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>877</v>
+        <v>199</v>
       </c>
       <c r="N216" s="2"/>
-      <c r="O216" t="s" s="2">
-        <v>878</v>
-      </c>
+      <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
         <v>82</v>
       </c>
@@ -28563,43 +28608,43 @@
         <v>82</v>
       </c>
       <c r="AB216" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC216" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD216" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE216" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>875</v>
+        <v>118</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>879</v>
+        <v>82</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK216" t="s" s="2">
-        <v>880</v>
+        <v>82</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM216" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>881</v>
+        <v>82</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>82</v>
@@ -28607,10 +28652,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>882</v>
+        <v>863</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>882</v>
+        <v>831</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28618,7 +28663,7 @@
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G217" t="s" s="2">
         <v>90</v>
@@ -28633,22 +28678,24 @@
         <v>82</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>390</v>
+        <v>132</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>883</v>
+        <v>225</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="N217" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N217" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q217" s="2"/>
       <c r="R217" t="s" s="2">
-        <v>82</v>
+        <v>832</v>
       </c>
       <c r="S217" t="s" s="2">
         <v>82</v>
@@ -28690,10 +28737,10 @@
         <v>82</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>882</v>
+        <v>228</v>
       </c>
       <c r="AG217" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH217" t="s" s="2">
         <v>90</v>
@@ -28702,13 +28749,13 @@
         <v>82</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK217" t="s" s="2">
-        <v>885</v>
+        <v>196</v>
       </c>
       <c r="AL217" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM217" t="s" s="2">
         <v>82</v>
@@ -28722,10 +28769,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>886</v>
+        <v>864</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>886</v>
+        <v>834</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28736,7 +28783,7 @@
         <v>80</v>
       </c>
       <c r="G218" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H218" t="s" s="2">
         <v>82</v>
@@ -28748,20 +28795,16 @@
         <v>82</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>765</v>
+        <v>173</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>887</v>
+        <v>231</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="N218" t="s" s="2">
-        <v>889</v>
-      </c>
-      <c r="O218" t="s" s="2">
-        <v>890</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N218" s="2"/>
+      <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
         <v>82</v>
       </c>
@@ -28770,7 +28813,7 @@
         <v>82</v>
       </c>
       <c r="S218" t="s" s="2">
-        <v>82</v>
+        <v>855</v>
       </c>
       <c r="T218" t="s" s="2">
         <v>82</v>
@@ -28785,13 +28828,11 @@
         <v>82</v>
       </c>
       <c r="X218" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y218" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="Y218" s="2"/>
       <c r="Z218" t="s" s="2">
-        <v>82</v>
+        <v>835</v>
       </c>
       <c r="AA218" t="s" s="2">
         <v>82</v>
@@ -28809,13 +28850,13 @@
         <v>82</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>886</v>
+        <v>234</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH218" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI218" t="s" s="2">
         <v>82</v>
@@ -28824,10 +28865,10 @@
         <v>102</v>
       </c>
       <c r="AK218" t="s" s="2">
-        <v>891</v>
+        <v>196</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>892</v>
+        <v>82</v>
       </c>
       <c r="AM218" t="s" s="2">
         <v>82</v>
@@ -28841,10 +28882,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>893</v>
+        <v>865</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>893</v>
+        <v>837</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -28855,7 +28896,7 @@
         <v>80</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H219" t="s" s="2">
         <v>82</v>
@@ -28864,19 +28905,23 @@
         <v>82</v>
       </c>
       <c r="J219" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>105</v>
+        <v>838</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N219" s="2"/>
-      <c r="O219" s="2"/>
+        <v>839</v>
+      </c>
+      <c r="N219" t="s" s="2">
+        <v>840</v>
+      </c>
+      <c r="O219" t="s" s="2">
+        <v>841</v>
+      </c>
       <c r="P219" t="s" s="2">
         <v>82</v>
       </c>
@@ -28924,22 +28969,22 @@
         <v>82</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>107</v>
+        <v>842</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI219" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK219" t="s" s="2">
-        <v>108</v>
+        <v>843</v>
       </c>
       <c r="AL219" t="s" s="2">
         <v>82</v>
@@ -28948,7 +28993,7 @@
         <v>82</v>
       </c>
       <c r="AN219" t="s" s="2">
-        <v>82</v>
+        <v>844</v>
       </c>
       <c r="AO219" t="s" s="2">
         <v>82</v>
@@ -28956,21 +29001,21 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>894</v>
+        <v>866</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>894</v>
+        <v>846</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E220" s="2"/>
       <c r="F220" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G220" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H220" t="s" s="2">
         <v>82</v>
@@ -28979,21 +29024,23 @@
         <v>82</v>
       </c>
       <c r="J220" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>112</v>
+        <v>847</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>113</v>
+        <v>848</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O220" s="2"/>
+        <v>849</v>
+      </c>
+      <c r="O220" t="s" s="2">
+        <v>850</v>
+      </c>
       <c r="P220" t="s" s="2">
         <v>82</v>
       </c>
@@ -29041,22 +29088,22 @@
         <v>82</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>118</v>
+        <v>851</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI220" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>108</v>
+        <v>852</v>
       </c>
       <c r="AL220" t="s" s="2">
         <v>82</v>
@@ -29065,7 +29112,7 @@
         <v>82</v>
       </c>
       <c r="AN220" t="s" s="2">
-        <v>82</v>
+        <v>853</v>
       </c>
       <c r="AO220" t="s" s="2">
         <v>82</v>
@@ -29073,45 +29120,43 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>895</v>
+        <v>867</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>895</v>
+        <v>867</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
-        <v>785</v>
+        <v>82</v>
       </c>
       <c r="E221" s="2"/>
       <c r="F221" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H221" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I221" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J221" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>111</v>
+        <v>618</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>786</v>
+        <v>868</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="N221" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>869</v>
+      </c>
+      <c r="N221" s="2"/>
       <c r="O221" t="s" s="2">
-        <v>401</v>
+        <v>870</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>82</v>
@@ -29160,31 +29205,31 @@
         <v>82</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>788</v>
+        <v>867</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH221" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI221" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK221" t="s" s="2">
-        <v>196</v>
+        <v>624</v>
       </c>
       <c r="AL221" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM221" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN221" t="s" s="2">
-        <v>82</v>
+        <v>871</v>
       </c>
       <c r="AO221" t="s" s="2">
         <v>82</v>
@@ -29192,10 +29237,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>896</v>
+        <v>872</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>896</v>
+        <v>872</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29203,10 +29248,10 @@
       </c>
       <c r="E222" s="2"/>
       <c r="F222" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H222" t="s" s="2">
         <v>82</v>
@@ -29218,19 +29263,19 @@
         <v>82</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>434</v>
+        <v>713</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>897</v>
+        <v>873</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>898</v>
+        <v>874</v>
       </c>
       <c r="N222" t="s" s="2">
-        <v>899</v>
+        <v>875</v>
       </c>
       <c r="O222" t="s" s="2">
-        <v>900</v>
+        <v>717</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>82</v>
@@ -29255,13 +29300,13 @@
         <v>82</v>
       </c>
       <c r="X222" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y222" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="Z222" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AA222" t="s" s="2">
         <v>82</v>
@@ -29279,13 +29324,13 @@
         <v>82</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>896</v>
+        <v>872</v>
       </c>
       <c r="AG222" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH222" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI222" t="s" s="2">
         <v>82</v>
@@ -29294,16 +29339,16 @@
         <v>102</v>
       </c>
       <c r="AK222" t="s" s="2">
-        <v>901</v>
+        <v>718</v>
       </c>
       <c r="AL222" t="s" s="2">
-        <v>902</v>
+        <v>108</v>
       </c>
       <c r="AM222" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN222" t="s" s="2">
-        <v>903</v>
+        <v>876</v>
       </c>
       <c r="AO222" t="s" s="2">
         <v>82</v>
@@ -29311,10 +29356,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>904</v>
+        <v>877</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>904</v>
+        <v>877</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29337,19 +29382,17 @@
         <v>82</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>594</v>
+        <v>878</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>905</v>
+        <v>879</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>906</v>
-      </c>
-      <c r="N223" t="s" s="2">
-        <v>907</v>
-      </c>
+        <v>880</v>
+      </c>
+      <c r="N223" s="2"/>
       <c r="O223" t="s" s="2">
-        <v>908</v>
+        <v>881</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>82</v>
@@ -29398,7 +29441,7 @@
         <v>82</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>904</v>
+        <v>877</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>80</v>
@@ -29413,16 +29456,16 @@
         <v>102</v>
       </c>
       <c r="AK223" t="s" s="2">
-        <v>909</v>
+        <v>752</v>
       </c>
       <c r="AL223" t="s" s="2">
-        <v>910</v>
+        <v>108</v>
       </c>
       <c r="AM223" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>911</v>
+        <v>882</v>
       </c>
       <c r="AO223" t="s" s="2">
         <v>82</v>
@@ -29430,21 +29473,21 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>912</v>
+        <v>883</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>912</v>
+        <v>883</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
-        <v>913</v>
+        <v>82</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G224" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H224" t="s" s="2">
         <v>82</v>
@@ -29456,18 +29499,18 @@
         <v>82</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>914</v>
+        <v>173</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>915</v>
+        <v>884</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>916</v>
-      </c>
-      <c r="N224" t="s" s="2">
-        <v>917</v>
-      </c>
-      <c r="O224" s="2"/>
+        <v>885</v>
+      </c>
+      <c r="N224" s="2"/>
+      <c r="O224" t="s" s="2">
+        <v>886</v>
+      </c>
       <c r="P224" t="s" s="2">
         <v>82</v>
       </c>
@@ -29491,13 +29534,13 @@
         <v>82</v>
       </c>
       <c r="X224" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="Y224" t="s" s="2">
-        <v>82</v>
+        <v>887</v>
       </c>
       <c r="Z224" t="s" s="2">
-        <v>82</v>
+        <v>888</v>
       </c>
       <c r="AA224" t="s" s="2">
         <v>82</v>
@@ -29515,13 +29558,13 @@
         <v>82</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>912</v>
+        <v>883</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH224" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI224" t="s" s="2">
         <v>82</v>
@@ -29530,7 +29573,7 @@
         <v>102</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>918</v>
+        <v>727</v>
       </c>
       <c r="AL224" t="s" s="2">
         <v>108</v>
@@ -29539,7 +29582,7 @@
         <v>82</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>919</v>
+        <v>889</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>82</v>
@@ -29547,10 +29590,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>920</v>
+        <v>890</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>920</v>
+        <v>890</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29570,22 +29613,20 @@
         <v>82</v>
       </c>
       <c r="J225" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>921</v>
+        <v>472</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>922</v>
+        <v>891</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>923</v>
-      </c>
-      <c r="N225" t="s" s="2">
-        <v>924</v>
-      </c>
+        <v>892</v>
+      </c>
+      <c r="N225" s="2"/>
       <c r="O225" t="s" s="2">
-        <v>925</v>
+        <v>893</v>
       </c>
       <c r="P225" t="s" s="2">
         <v>82</v>
@@ -29634,7 +29675,7 @@
         <v>82</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>920</v>
+        <v>890</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>80</v>
@@ -29643,22 +29684,22 @@
         <v>90</v>
       </c>
       <c r="AI225" t="s" s="2">
-        <v>82</v>
+        <v>894</v>
       </c>
       <c r="AJ225" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK225" t="s" s="2">
-        <v>880</v>
+        <v>895</v>
       </c>
       <c r="AL225" t="s" s="2">
-        <v>926</v>
+        <v>108</v>
       </c>
       <c r="AM225" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN225" t="s" s="2">
-        <v>82</v>
+        <v>896</v>
       </c>
       <c r="AO225" t="s" s="2">
         <v>82</v>
@@ -29666,10 +29707,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>927</v>
+        <v>897</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>927</v>
+        <v>897</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -29680,32 +29721,28 @@
         <v>80</v>
       </c>
       <c r="G226" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H226" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I226" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J226" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>765</v>
+        <v>390</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>928</v>
+        <v>898</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>929</v>
-      </c>
-      <c r="N226" t="s" s="2">
-        <v>930</v>
-      </c>
-      <c r="O226" t="s" s="2">
-        <v>931</v>
-      </c>
+        <v>899</v>
+      </c>
+      <c r="N226" s="2"/>
+      <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
         <v>82</v>
       </c>
@@ -29753,13 +29790,13 @@
         <v>82</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>927</v>
+        <v>897</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH226" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI226" t="s" s="2">
         <v>82</v>
@@ -29768,7 +29805,7 @@
         <v>102</v>
       </c>
       <c r="AK226" t="s" s="2">
-        <v>932</v>
+        <v>900</v>
       </c>
       <c r="AL226" t="s" s="2">
         <v>108</v>
@@ -29785,10 +29822,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>933</v>
+        <v>901</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>933</v>
+        <v>901</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29799,7 +29836,7 @@
         <v>80</v>
       </c>
       <c r="G227" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H227" t="s" s="2">
         <v>82</v>
@@ -29811,16 +29848,20 @@
         <v>82</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>104</v>
+        <v>780</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>105</v>
+        <v>902</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N227" s="2"/>
-      <c r="O227" s="2"/>
+        <v>903</v>
+      </c>
+      <c r="N227" t="s" s="2">
+        <v>904</v>
+      </c>
+      <c r="O227" t="s" s="2">
+        <v>905</v>
+      </c>
       <c r="P227" t="s" s="2">
         <v>82</v>
       </c>
@@ -29868,25 +29909,25 @@
         <v>82</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>107</v>
+        <v>901</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH227" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI227" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ227" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK227" t="s" s="2">
-        <v>108</v>
+        <v>906</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>82</v>
+        <v>907</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>82</v>
@@ -29900,21 +29941,21 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>934</v>
+        <v>908</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>934</v>
+        <v>908</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G228" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H228" t="s" s="2">
         <v>82</v>
@@ -29926,17 +29967,15 @@
         <v>82</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N228" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N228" s="2"/>
       <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
         <v>82</v>
@@ -29985,19 +30024,19 @@
         <v>82</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH228" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI228" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ228" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AK228" t="s" s="2">
         <v>108</v>
@@ -30017,14 +30056,14 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>935</v>
+        <v>909</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>935</v>
+        <v>909</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
-        <v>785</v>
+        <v>110</v>
       </c>
       <c r="E229" s="2"/>
       <c r="F229" t="s" s="2">
@@ -30037,26 +30076,24 @@
         <v>82</v>
       </c>
       <c r="I229" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J229" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K229" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>786</v>
+        <v>112</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>787</v>
+        <v>113</v>
       </c>
       <c r="N229" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O229" t="s" s="2">
-        <v>401</v>
-      </c>
+      <c r="O229" s="2"/>
       <c r="P229" t="s" s="2">
         <v>82</v>
       </c>
@@ -30104,7 +30141,7 @@
         <v>82</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>788</v>
+        <v>118</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>80</v>
@@ -30119,7 +30156,7 @@
         <v>119</v>
       </c>
       <c r="AK229" t="s" s="2">
-        <v>196</v>
+        <v>108</v>
       </c>
       <c r="AL229" t="s" s="2">
         <v>82</v>
@@ -30136,44 +30173,46 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>936</v>
+        <v>910</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>936</v>
+        <v>910</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
-        <v>82</v>
+        <v>800</v>
       </c>
       <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G230" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H230" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I230" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J230" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>937</v>
+        <v>111</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>938</v>
+        <v>801</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>939</v>
+        <v>802</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>940</v>
-      </c>
-      <c r="O230" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O230" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="P230" t="s" s="2">
         <v>82</v>
       </c>
@@ -30221,31 +30260,31 @@
         <v>82</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>936</v>
+        <v>803</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI230" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ230" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK230" t="s" s="2">
-        <v>410</v>
+        <v>196</v>
       </c>
       <c r="AL230" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM230" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN230" t="s" s="2">
-        <v>941</v>
+        <v>82</v>
       </c>
       <c r="AO230" t="s" s="2">
         <v>82</v>
@@ -30253,10 +30292,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>942</v>
+        <v>911</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>942</v>
+        <v>911</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30276,19 +30315,23 @@
         <v>82</v>
       </c>
       <c r="J231" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>173</v>
+        <v>434</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>943</v>
+        <v>912</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>944</v>
-      </c>
-      <c r="N231" s="2"/>
-      <c r="O231" s="2"/>
+        <v>913</v>
+      </c>
+      <c r="N231" t="s" s="2">
+        <v>914</v>
+      </c>
+      <c r="O231" t="s" s="2">
+        <v>915</v>
+      </c>
       <c r="P231" t="s" s="2">
         <v>82</v>
       </c>
@@ -30312,13 +30355,13 @@
         <v>82</v>
       </c>
       <c r="X231" t="s" s="2">
-        <v>264</v>
+        <v>177</v>
       </c>
       <c r="Y231" t="s" s="2">
-        <v>944</v>
+        <v>178</v>
       </c>
       <c r="Z231" t="s" s="2">
-        <v>945</v>
+        <v>179</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>82</v>
@@ -30336,7 +30379,7 @@
         <v>82</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>942</v>
+        <v>911</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>90</v>
@@ -30351,23 +30394,1080 @@
         <v>102</v>
       </c>
       <c r="AK231" t="s" s="2">
+        <v>916</v>
+      </c>
+      <c r="AL231" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="AM231" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN231" t="s" s="2">
+        <v>918</v>
+      </c>
+      <c r="AO231" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="232" hidden="true">
+      <c r="A232" t="s" s="2">
+        <v>919</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>919</v>
+      </c>
+      <c r="C232" s="2"/>
+      <c r="D232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E232" s="2"/>
+      <c r="F232" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G232" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K232" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="L232" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="M232" t="s" s="2">
+        <v>921</v>
+      </c>
+      <c r="N232" t="s" s="2">
+        <v>922</v>
+      </c>
+      <c r="O232" t="s" s="2">
+        <v>923</v>
+      </c>
+      <c r="P232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q232" s="2"/>
+      <c r="R232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF232" t="s" s="2">
+        <v>919</v>
+      </c>
+      <c r="AG232" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH232" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ232" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK232" t="s" s="2">
+        <v>924</v>
+      </c>
+      <c r="AL232" t="s" s="2">
+        <v>925</v>
+      </c>
+      <c r="AM232" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN232" t="s" s="2">
+        <v>926</v>
+      </c>
+      <c r="AO232" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="233" hidden="true">
+      <c r="A233" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="C233" s="2"/>
+      <c r="D233" t="s" s="2">
+        <v>928</v>
+      </c>
+      <c r="E233" s="2"/>
+      <c r="F233" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G233" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K233" t="s" s="2">
+        <v>929</v>
+      </c>
+      <c r="L233" t="s" s="2">
+        <v>930</v>
+      </c>
+      <c r="M233" t="s" s="2">
+        <v>931</v>
+      </c>
+      <c r="N233" t="s" s="2">
+        <v>932</v>
+      </c>
+      <c r="O233" s="2"/>
+      <c r="P233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q233" s="2"/>
+      <c r="R233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF233" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="AG233" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH233" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ233" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK233" t="s" s="2">
+        <v>933</v>
+      </c>
+      <c r="AL233" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM233" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN233" t="s" s="2">
+        <v>934</v>
+      </c>
+      <c r="AO233" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="234" hidden="true">
+      <c r="A234" t="s" s="2">
+        <v>935</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>935</v>
+      </c>
+      <c r="C234" s="2"/>
+      <c r="D234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E234" s="2"/>
+      <c r="F234" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G234" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J234" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K234" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="L234" t="s" s="2">
+        <v>937</v>
+      </c>
+      <c r="M234" t="s" s="2">
+        <v>938</v>
+      </c>
+      <c r="N234" t="s" s="2">
+        <v>939</v>
+      </c>
+      <c r="O234" t="s" s="2">
+        <v>940</v>
+      </c>
+      <c r="P234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q234" s="2"/>
+      <c r="R234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF234" t="s" s="2">
+        <v>935</v>
+      </c>
+      <c r="AG234" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH234" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ234" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK234" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="AL234" t="s" s="2">
+        <v>941</v>
+      </c>
+      <c r="AM234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN234" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO234" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="235" hidden="true">
+      <c r="A235" t="s" s="2">
+        <v>942</v>
+      </c>
+      <c r="B235" t="s" s="2">
+        <v>942</v>
+      </c>
+      <c r="C235" s="2"/>
+      <c r="D235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E235" s="2"/>
+      <c r="F235" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G235" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I235" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J235" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K235" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="L235" t="s" s="2">
+        <v>943</v>
+      </c>
+      <c r="M235" t="s" s="2">
+        <v>944</v>
+      </c>
+      <c r="N235" t="s" s="2">
+        <v>945</v>
+      </c>
+      <c r="O235" t="s" s="2">
         <v>946</v>
       </c>
-      <c r="AL231" t="s" s="2">
+      <c r="P235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q235" s="2"/>
+      <c r="R235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF235" t="s" s="2">
+        <v>942</v>
+      </c>
+      <c r="AG235" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH235" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ235" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK235" t="s" s="2">
+        <v>947</v>
+      </c>
+      <c r="AL235" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AM231" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN231" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO231" t="s" s="2">
+      <c r="AM235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN235" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO235" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="236" hidden="true">
+      <c r="A236" t="s" s="2">
+        <v>948</v>
+      </c>
+      <c r="B236" t="s" s="2">
+        <v>948</v>
+      </c>
+      <c r="C236" s="2"/>
+      <c r="D236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E236" s="2"/>
+      <c r="F236" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G236" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K236" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L236" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M236" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N236" s="2"/>
+      <c r="O236" s="2"/>
+      <c r="P236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q236" s="2"/>
+      <c r="R236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF236" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG236" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH236" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK236" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO236" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="237" hidden="true">
+      <c r="A237" t="s" s="2">
+        <v>949</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>949</v>
+      </c>
+      <c r="C237" s="2"/>
+      <c r="D237" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E237" s="2"/>
+      <c r="F237" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G237" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K237" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L237" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M237" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N237" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O237" s="2"/>
+      <c r="P237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q237" s="2"/>
+      <c r="R237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF237" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG237" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH237" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ237" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK237" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN237" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO237" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="238" hidden="true">
+      <c r="A238" t="s" s="2">
+        <v>950</v>
+      </c>
+      <c r="B238" t="s" s="2">
+        <v>950</v>
+      </c>
+      <c r="C238" s="2"/>
+      <c r="D238" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="E238" s="2"/>
+      <c r="F238" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G238" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I238" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J238" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K238" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L238" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="M238" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="N238" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O238" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="P238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q238" s="2"/>
+      <c r="R238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF238" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="AG238" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH238" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ238" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK238" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AL238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN238" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO238" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="239" hidden="true">
+      <c r="A239" t="s" s="2">
+        <v>951</v>
+      </c>
+      <c r="B239" t="s" s="2">
+        <v>951</v>
+      </c>
+      <c r="C239" s="2"/>
+      <c r="D239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E239" s="2"/>
+      <c r="F239" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G239" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J239" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K239" t="s" s="2">
+        <v>952</v>
+      </c>
+      <c r="L239" t="s" s="2">
+        <v>953</v>
+      </c>
+      <c r="M239" t="s" s="2">
+        <v>954</v>
+      </c>
+      <c r="N239" t="s" s="2">
+        <v>955</v>
+      </c>
+      <c r="O239" s="2"/>
+      <c r="P239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q239" s="2"/>
+      <c r="R239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF239" t="s" s="2">
+        <v>951</v>
+      </c>
+      <c r="AG239" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH239" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ239" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK239" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AL239" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM239" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN239" t="s" s="2">
+        <v>956</v>
+      </c>
+      <c r="AO239" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="240" hidden="true">
+      <c r="A240" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="B240" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="C240" s="2"/>
+      <c r="D240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E240" s="2"/>
+      <c r="F240" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G240" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J240" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K240" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L240" t="s" s="2">
+        <v>958</v>
+      </c>
+      <c r="M240" t="s" s="2">
+        <v>959</v>
+      </c>
+      <c r="N240" s="2"/>
+      <c r="O240" s="2"/>
+      <c r="P240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q240" s="2"/>
+      <c r="R240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X240" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Y240" t="s" s="2">
+        <v>959</v>
+      </c>
+      <c r="Z240" t="s" s="2">
+        <v>960</v>
+      </c>
+      <c r="AA240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF240" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="AG240" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH240" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ240" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK240" t="s" s="2">
+        <v>961</v>
+      </c>
+      <c r="AL240" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN240" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO240" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO231">
+  <autoFilter ref="A1:AO240">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -30377,7 +31477,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI230">
+  <conditionalFormatting sqref="A2:AI239">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -958,8 +958,8 @@
     <t>FR Core Address Insee Code Extension</t>
   </si>
   <si>
-    <t>Extension d'ajout du code insee (5 chiffres) à l'adresse postale.
-This extension adds the insee code (5 digits) to the address</t>
+    <t>Extension d'ajout du code insee (5 chiffres) à l'adresse postale. Dans le cas d'une ville étrangère, le code département devient "99" et le code commune est renseigné avec le code pays. Pour plus de détails, consultez le référentiel national d'identitovigilance (RNIV).
+This extension adds the insee code (5 digits) to the address. In the case of a foreign city, the department code becomes "99", and the municipality code is populated with the country code.</t>
   </si>
   <si>
     <t>Patient.extension:birthPlace.value[x].use</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
